--- a/графики/график Ташкент.xlsx
+++ b/графики/график Ташкент.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26387144-8074-4479-893C-FE1DB69CFAC1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6628DC-9823-452B-801E-4E56E5454765}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="80">
   <si>
     <t>Контракт</t>
   </si>
@@ -333,7 +333,10 @@
     <t>Заказы и отгрузки после НГ</t>
   </si>
   <si>
-    <t>Шувалова сама отправит заказ на завод</t>
+    <t>без расчета</t>
+  </si>
+  <si>
+    <t>погрузки на 14,01,26 не будет (письмо от Шуваловой)</t>
   </si>
 </sst>
 </file>
@@ -343,12 +346,20 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -467,7 +478,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -507,6 +518,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -612,7 +629,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -648,125 +665,143 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -783,40 +818,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1123,7 +1158,7 @@
   <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H257"/>
+  <dimension ref="A1:H258"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="3" customWidth="1"/>
@@ -1138,19 +1173,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="63"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="70" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="46" t="s">
@@ -1171,12 +1206,12 @@
       <c r="G2" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="67" t="s">
+      <c r="H2" s="73" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="65"/>
+      <c r="A3" s="71"/>
       <c r="B3" s="46" t="s">
         <v>5</v>
       </c>
@@ -1193,10 +1228,10 @@
       <c r="G3" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="68"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="65"/>
+      <c r="A4" s="71"/>
       <c r="B4" s="46" t="s">
         <v>6</v>
       </c>
@@ -1213,10 +1248,10 @@
       <c r="G4" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="68"/>
+      <c r="H4" s="74"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="65"/>
+      <c r="A5" s="71"/>
       <c r="B5" s="46" t="s">
         <v>19</v>
       </c>
@@ -1227,14 +1262,14 @@
         <v>9</v>
       </c>
       <c r="E5" s="48"/>
-      <c r="F5" s="58" t="s">
+      <c r="F5" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="59"/>
-      <c r="H5" s="68"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="74"/>
     </row>
     <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="65"/>
+      <c r="A6" s="71"/>
       <c r="B6" s="46" t="s">
         <v>15</v>
       </c>
@@ -1251,10 +1286,10 @@
       <c r="G6" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="68"/>
+      <c r="H6" s="74"/>
     </row>
     <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="66"/>
+      <c r="A7" s="72"/>
       <c r="B7" s="46" t="s">
         <v>26</v>
       </c>
@@ -1271,7 +1306,7 @@
       <c r="G7" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="69"/>
+      <c r="H7" s="75"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
@@ -1412,16 +1447,16 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="56"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="62"/>
     </row>
     <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -1565,16 +1600,16 @@
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="53" t="s">
+      <c r="A20" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="57"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="63"/>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -1717,16 +1752,16 @@
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="53" t="s">
+      <c r="A26" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="54"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="57"/>
+      <c r="B26" s="60"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="63"/>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -1927,16 +1962,16 @@
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="53" t="s">
+      <c r="A34" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="54"/>
-      <c r="C34" s="54"/>
-      <c r="D34" s="54"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="54"/>
-      <c r="G34" s="54"/>
-      <c r="H34" s="57"/>
+      <c r="B34" s="60"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="60"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="60"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="63"/>
     </row>
     <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -2121,16 +2156,16 @@
       </c>
     </row>
     <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="53" t="s">
+      <c r="A41" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="54"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="54"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="54"/>
-      <c r="H41" s="57"/>
+      <c r="B41" s="60"/>
+      <c r="C41" s="60"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="61"/>
+      <c r="F41" s="60"/>
+      <c r="G41" s="60"/>
+      <c r="H41" s="63"/>
     </row>
     <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
@@ -2332,16 +2367,16 @@
       <c r="H48" s="12"/>
     </row>
     <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="53" t="s">
+      <c r="A49" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B49" s="54"/>
-      <c r="C49" s="54"/>
-      <c r="D49" s="54"/>
-      <c r="E49" s="55"/>
-      <c r="F49" s="54"/>
-      <c r="G49" s="54"/>
-      <c r="H49" s="57"/>
+      <c r="B49" s="60"/>
+      <c r="C49" s="60"/>
+      <c r="D49" s="60"/>
+      <c r="E49" s="61"/>
+      <c r="F49" s="60"/>
+      <c r="G49" s="60"/>
+      <c r="H49" s="63"/>
     </row>
     <row r="50" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
@@ -2456,16 +2491,16 @@
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="53" t="s">
+      <c r="A54" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B54" s="54"/>
-      <c r="C54" s="54"/>
-      <c r="D54" s="54"/>
-      <c r="E54" s="55"/>
-      <c r="F54" s="54"/>
-      <c r="G54" s="54"/>
-      <c r="H54" s="57"/>
+      <c r="B54" s="60"/>
+      <c r="C54" s="60"/>
+      <c r="D54" s="60"/>
+      <c r="E54" s="61"/>
+      <c r="F54" s="60"/>
+      <c r="G54" s="60"/>
+      <c r="H54" s="63"/>
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
@@ -2614,16 +2649,16 @@
       </c>
     </row>
     <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="53" t="s">
+      <c r="A61" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B61" s="54"/>
-      <c r="C61" s="54"/>
-      <c r="D61" s="54"/>
-      <c r="E61" s="54"/>
-      <c r="F61" s="54"/>
-      <c r="G61" s="54"/>
-      <c r="H61" s="56"/>
+      <c r="B61" s="60"/>
+      <c r="C61" s="60"/>
+      <c r="D61" s="60"/>
+      <c r="E61" s="60"/>
+      <c r="F61" s="60"/>
+      <c r="G61" s="60"/>
+      <c r="H61" s="62"/>
     </row>
     <row r="62" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
@@ -2738,16 +2773,16 @@
       <c r="H65" s="10"/>
     </row>
     <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="53" t="s">
+      <c r="A66" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B66" s="54"/>
-      <c r="C66" s="54"/>
-      <c r="D66" s="54"/>
-      <c r="E66" s="54"/>
-      <c r="F66" s="54"/>
-      <c r="G66" s="54"/>
-      <c r="H66" s="56"/>
+      <c r="B66" s="60"/>
+      <c r="C66" s="60"/>
+      <c r="D66" s="60"/>
+      <c r="E66" s="60"/>
+      <c r="F66" s="60"/>
+      <c r="G66" s="60"/>
+      <c r="H66" s="62"/>
     </row>
     <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
@@ -2922,16 +2957,16 @@
       </c>
     </row>
     <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="53" t="s">
+      <c r="A73" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B73" s="54"/>
-      <c r="C73" s="54"/>
-      <c r="D73" s="54"/>
-      <c r="E73" s="54"/>
-      <c r="F73" s="54"/>
-      <c r="G73" s="54"/>
-      <c r="H73" s="56"/>
+      <c r="B73" s="60"/>
+      <c r="C73" s="60"/>
+      <c r="D73" s="60"/>
+      <c r="E73" s="60"/>
+      <c r="F73" s="60"/>
+      <c r="G73" s="60"/>
+      <c r="H73" s="62"/>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
@@ -3050,16 +3085,16 @@
       <c r="H77" s="10"/>
     </row>
     <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="53" t="s">
+      <c r="A78" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B78" s="54"/>
-      <c r="C78" s="54"/>
-      <c r="D78" s="54"/>
-      <c r="E78" s="54"/>
-      <c r="F78" s="54"/>
-      <c r="G78" s="54"/>
-      <c r="H78" s="56"/>
+      <c r="B78" s="60"/>
+      <c r="C78" s="60"/>
+      <c r="D78" s="60"/>
+      <c r="E78" s="60"/>
+      <c r="F78" s="60"/>
+      <c r="G78" s="60"/>
+      <c r="H78" s="62"/>
     </row>
     <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
@@ -3234,16 +3269,16 @@
       </c>
     </row>
     <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="53" t="s">
+      <c r="A85" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B85" s="54"/>
-      <c r="C85" s="54"/>
-      <c r="D85" s="54"/>
-      <c r="E85" s="54"/>
-      <c r="F85" s="54"/>
-      <c r="G85" s="54"/>
-      <c r="H85" s="56"/>
+      <c r="B85" s="60"/>
+      <c r="C85" s="60"/>
+      <c r="D85" s="60"/>
+      <c r="E85" s="60"/>
+      <c r="F85" s="60"/>
+      <c r="G85" s="60"/>
+      <c r="H85" s="62"/>
     </row>
     <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
@@ -3361,16 +3396,16 @@
       <c r="H89" s="10"/>
     </row>
     <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="53" t="s">
+      <c r="A90" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B90" s="54"/>
-      <c r="C90" s="54"/>
-      <c r="D90" s="54"/>
-      <c r="E90" s="54"/>
-      <c r="F90" s="54"/>
-      <c r="G90" s="54"/>
-      <c r="H90" s="56"/>
+      <c r="B90" s="60"/>
+      <c r="C90" s="60"/>
+      <c r="D90" s="60"/>
+      <c r="E90" s="60"/>
+      <c r="F90" s="60"/>
+      <c r="G90" s="60"/>
+      <c r="H90" s="62"/>
     </row>
     <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
@@ -3544,16 +3579,16 @@
       </c>
     </row>
     <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="53" t="s">
+      <c r="A97" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B97" s="54"/>
-      <c r="C97" s="54"/>
-      <c r="D97" s="54"/>
-      <c r="E97" s="54"/>
-      <c r="F97" s="54"/>
-      <c r="G97" s="54"/>
-      <c r="H97" s="56"/>
+      <c r="B97" s="60"/>
+      <c r="C97" s="60"/>
+      <c r="D97" s="60"/>
+      <c r="E97" s="60"/>
+      <c r="F97" s="60"/>
+      <c r="G97" s="60"/>
+      <c r="H97" s="62"/>
     </row>
     <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
@@ -3669,16 +3704,16 @@
       <c r="H101" s="10"/>
     </row>
     <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="53" t="s">
+      <c r="A102" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B102" s="54"/>
-      <c r="C102" s="54"/>
-      <c r="D102" s="54"/>
-      <c r="E102" s="54"/>
-      <c r="F102" s="54"/>
-      <c r="G102" s="54"/>
-      <c r="H102" s="56"/>
+      <c r="B102" s="60"/>
+      <c r="C102" s="60"/>
+      <c r="D102" s="60"/>
+      <c r="E102" s="60"/>
+      <c r="F102" s="60"/>
+      <c r="G102" s="60"/>
+      <c r="H102" s="62"/>
     </row>
     <row r="103" spans="1:8" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
@@ -3856,16 +3891,16 @@
       <c r="H108" s="17"/>
     </row>
     <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="53" t="s">
+      <c r="A109" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B109" s="54"/>
-      <c r="C109" s="54"/>
-      <c r="D109" s="54"/>
-      <c r="E109" s="54"/>
-      <c r="F109" s="54"/>
-      <c r="G109" s="54"/>
-      <c r="H109" s="56"/>
+      <c r="B109" s="60"/>
+      <c r="C109" s="60"/>
+      <c r="D109" s="60"/>
+      <c r="E109" s="60"/>
+      <c r="F109" s="60"/>
+      <c r="G109" s="60"/>
+      <c r="H109" s="62"/>
     </row>
     <row r="110" spans="1:8" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
@@ -4039,16 +4074,16 @@
       <c r="H115" s="10"/>
     </row>
     <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="53" t="s">
+      <c r="A116" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B116" s="54"/>
-      <c r="C116" s="54"/>
-      <c r="D116" s="54"/>
-      <c r="E116" s="54"/>
-      <c r="F116" s="54"/>
-      <c r="G116" s="54"/>
-      <c r="H116" s="56"/>
+      <c r="B116" s="60"/>
+      <c r="C116" s="60"/>
+      <c r="D116" s="60"/>
+      <c r="E116" s="60"/>
+      <c r="F116" s="60"/>
+      <c r="G116" s="60"/>
+      <c r="H116" s="62"/>
     </row>
     <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
@@ -4147,16 +4182,16 @@
       <c r="H120" s="10"/>
     </row>
     <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="53" t="s">
+      <c r="A121" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B121" s="54"/>
-      <c r="C121" s="54"/>
-      <c r="D121" s="54"/>
-      <c r="E121" s="54"/>
-      <c r="F121" s="54"/>
-      <c r="G121" s="54"/>
-      <c r="H121" s="56"/>
+      <c r="B121" s="60"/>
+      <c r="C121" s="60"/>
+      <c r="D121" s="60"/>
+      <c r="E121" s="60"/>
+      <c r="F121" s="60"/>
+      <c r="G121" s="60"/>
+      <c r="H121" s="62"/>
     </row>
     <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
@@ -4330,16 +4365,16 @@
       <c r="H127" s="10"/>
     </row>
     <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="53" t="s">
+      <c r="A128" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B128" s="54"/>
-      <c r="C128" s="54"/>
-      <c r="D128" s="54"/>
-      <c r="E128" s="54"/>
-      <c r="F128" s="54"/>
-      <c r="G128" s="54"/>
-      <c r="H128" s="56"/>
+      <c r="B128" s="60"/>
+      <c r="C128" s="60"/>
+      <c r="D128" s="60"/>
+      <c r="E128" s="60"/>
+      <c r="F128" s="60"/>
+      <c r="G128" s="60"/>
+      <c r="H128" s="62"/>
     </row>
     <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
@@ -4458,16 +4493,16 @@
       <c r="H132" s="10"/>
     </row>
     <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="53" t="s">
+      <c r="A133" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B133" s="54"/>
-      <c r="C133" s="54"/>
-      <c r="D133" s="54"/>
-      <c r="E133" s="54"/>
-      <c r="F133" s="54"/>
-      <c r="G133" s="54"/>
-      <c r="H133" s="56"/>
+      <c r="B133" s="60"/>
+      <c r="C133" s="60"/>
+      <c r="D133" s="60"/>
+      <c r="E133" s="60"/>
+      <c r="F133" s="60"/>
+      <c r="G133" s="60"/>
+      <c r="H133" s="62"/>
     </row>
     <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
@@ -4646,16 +4681,16 @@
       </c>
     </row>
     <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="53" t="s">
+      <c r="A140" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B140" s="54"/>
-      <c r="C140" s="54"/>
-      <c r="D140" s="54"/>
-      <c r="E140" s="54"/>
-      <c r="F140" s="54"/>
-      <c r="G140" s="54"/>
-      <c r="H140" s="56"/>
+      <c r="B140" s="60"/>
+      <c r="C140" s="60"/>
+      <c r="D140" s="60"/>
+      <c r="E140" s="60"/>
+      <c r="F140" s="60"/>
+      <c r="G140" s="60"/>
+      <c r="H140" s="62"/>
     </row>
     <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
@@ -4774,16 +4809,16 @@
       <c r="H144" s="10"/>
     </row>
     <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="53" t="s">
+      <c r="A145" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B145" s="54"/>
-      <c r="C145" s="54"/>
-      <c r="D145" s="54"/>
-      <c r="E145" s="55"/>
-      <c r="F145" s="54"/>
-      <c r="G145" s="54"/>
-      <c r="H145" s="56"/>
+      <c r="B145" s="60"/>
+      <c r="C145" s="60"/>
+      <c r="D145" s="60"/>
+      <c r="E145" s="61"/>
+      <c r="F145" s="60"/>
+      <c r="G145" s="60"/>
+      <c r="H145" s="62"/>
     </row>
     <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
@@ -4962,16 +4997,16 @@
       </c>
     </row>
     <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="53" t="s">
+      <c r="A152" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B152" s="54"/>
-      <c r="C152" s="54"/>
-      <c r="D152" s="54"/>
-      <c r="E152" s="55"/>
-      <c r="F152" s="54"/>
-      <c r="G152" s="54"/>
-      <c r="H152" s="56"/>
+      <c r="B152" s="60"/>
+      <c r="C152" s="60"/>
+      <c r="D152" s="60"/>
+      <c r="E152" s="61"/>
+      <c r="F152" s="60"/>
+      <c r="G152" s="60"/>
+      <c r="H152" s="62"/>
     </row>
     <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
@@ -5061,16 +5096,16 @@
       <c r="H155" s="10"/>
     </row>
     <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="53" t="s">
+      <c r="A156" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B156" s="54"/>
-      <c r="C156" s="54"/>
-      <c r="D156" s="54"/>
-      <c r="E156" s="55"/>
-      <c r="F156" s="54"/>
-      <c r="G156" s="54"/>
-      <c r="H156" s="56"/>
+      <c r="B156" s="60"/>
+      <c r="C156" s="60"/>
+      <c r="D156" s="60"/>
+      <c r="E156" s="61"/>
+      <c r="F156" s="60"/>
+      <c r="G156" s="60"/>
+      <c r="H156" s="62"/>
     </row>
     <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
@@ -5223,16 +5258,16 @@
       </c>
     </row>
     <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="53" t="s">
+      <c r="A162" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B162" s="54"/>
-      <c r="C162" s="54"/>
-      <c r="D162" s="54"/>
-      <c r="E162" s="55"/>
-      <c r="F162" s="54"/>
-      <c r="G162" s="54"/>
-      <c r="H162" s="56"/>
+      <c r="B162" s="60"/>
+      <c r="C162" s="60"/>
+      <c r="D162" s="60"/>
+      <c r="E162" s="61"/>
+      <c r="F162" s="60"/>
+      <c r="G162" s="60"/>
+      <c r="H162" s="62"/>
     </row>
     <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
@@ -5327,16 +5362,16 @@
       <c r="H165" s="10"/>
     </row>
     <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="53" t="s">
+      <c r="A166" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B166" s="54"/>
-      <c r="C166" s="54"/>
-      <c r="D166" s="54"/>
-      <c r="E166" s="55"/>
-      <c r="F166" s="54"/>
-      <c r="G166" s="54"/>
-      <c r="H166" s="56"/>
+      <c r="B166" s="60"/>
+      <c r="C166" s="60"/>
+      <c r="D166" s="60"/>
+      <c r="E166" s="61"/>
+      <c r="F166" s="60"/>
+      <c r="G166" s="60"/>
+      <c r="H166" s="62"/>
     </row>
     <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
@@ -5489,16 +5524,16 @@
       </c>
     </row>
     <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="53" t="s">
+      <c r="A172" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B172" s="54"/>
-      <c r="C172" s="54"/>
-      <c r="D172" s="54"/>
-      <c r="E172" s="55"/>
-      <c r="F172" s="54"/>
-      <c r="G172" s="54"/>
-      <c r="H172" s="56"/>
+      <c r="B172" s="60"/>
+      <c r="C172" s="60"/>
+      <c r="D172" s="60"/>
+      <c r="E172" s="61"/>
+      <c r="F172" s="60"/>
+      <c r="G172" s="60"/>
+      <c r="H172" s="62"/>
     </row>
     <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
@@ -5593,16 +5628,16 @@
       <c r="H175" s="10"/>
     </row>
     <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="53" t="s">
+      <c r="A176" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B176" s="54"/>
-      <c r="C176" s="54"/>
-      <c r="D176" s="54"/>
-      <c r="E176" s="55"/>
-      <c r="F176" s="54"/>
-      <c r="G176" s="54"/>
-      <c r="H176" s="56"/>
+      <c r="B176" s="60"/>
+      <c r="C176" s="60"/>
+      <c r="D176" s="60"/>
+      <c r="E176" s="61"/>
+      <c r="F176" s="60"/>
+      <c r="G176" s="60"/>
+      <c r="H176" s="62"/>
     </row>
     <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
@@ -5756,16 +5791,16 @@
       </c>
     </row>
     <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="53" t="s">
+      <c r="A182" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B182" s="54"/>
-      <c r="C182" s="54"/>
-      <c r="D182" s="54"/>
-      <c r="E182" s="55"/>
-      <c r="F182" s="54"/>
-      <c r="G182" s="54"/>
-      <c r="H182" s="56"/>
+      <c r="B182" s="60"/>
+      <c r="C182" s="60"/>
+      <c r="D182" s="60"/>
+      <c r="E182" s="61"/>
+      <c r="F182" s="60"/>
+      <c r="G182" s="60"/>
+      <c r="H182" s="62"/>
     </row>
     <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
@@ -5857,16 +5892,16 @@
       <c r="H185" s="10"/>
     </row>
     <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="53" t="s">
+      <c r="A186" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B186" s="54"/>
-      <c r="C186" s="54"/>
-      <c r="D186" s="54"/>
-      <c r="E186" s="55"/>
-      <c r="F186" s="54"/>
-      <c r="G186" s="54"/>
-      <c r="H186" s="56"/>
+      <c r="B186" s="60"/>
+      <c r="C186" s="60"/>
+      <c r="D186" s="60"/>
+      <c r="E186" s="61"/>
+      <c r="F186" s="60"/>
+      <c r="G186" s="60"/>
+      <c r="H186" s="62"/>
     </row>
     <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
@@ -6018,16 +6053,16 @@
       </c>
     </row>
     <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="53" t="s">
+      <c r="A192" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B192" s="54"/>
-      <c r="C192" s="54"/>
-      <c r="D192" s="54"/>
-      <c r="E192" s="55"/>
-      <c r="F192" s="54"/>
-      <c r="G192" s="54"/>
-      <c r="H192" s="56"/>
+      <c r="B192" s="60"/>
+      <c r="C192" s="60"/>
+      <c r="D192" s="60"/>
+      <c r="E192" s="61"/>
+      <c r="F192" s="60"/>
+      <c r="G192" s="60"/>
+      <c r="H192" s="62"/>
     </row>
     <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
@@ -6122,16 +6157,16 @@
       <c r="H195" s="10"/>
     </row>
     <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="53" t="s">
+      <c r="A196" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B196" s="54"/>
-      <c r="C196" s="54"/>
-      <c r="D196" s="54"/>
-      <c r="E196" s="55"/>
-      <c r="F196" s="54"/>
-      <c r="G196" s="54"/>
-      <c r="H196" s="56"/>
+      <c r="B196" s="60"/>
+      <c r="C196" s="60"/>
+      <c r="D196" s="60"/>
+      <c r="E196" s="61"/>
+      <c r="F196" s="60"/>
+      <c r="G196" s="60"/>
+      <c r="H196" s="62"/>
     </row>
     <row r="197" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
@@ -6282,16 +6317,16 @@
       <c r="H201" s="30"/>
     </row>
     <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="53" t="s">
+      <c r="A202" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B202" s="54"/>
-      <c r="C202" s="54"/>
-      <c r="D202" s="54"/>
-      <c r="E202" s="55"/>
-      <c r="F202" s="54"/>
-      <c r="G202" s="54"/>
-      <c r="H202" s="56"/>
+      <c r="B202" s="60"/>
+      <c r="C202" s="60"/>
+      <c r="D202" s="60"/>
+      <c r="E202" s="61"/>
+      <c r="F202" s="60"/>
+      <c r="G202" s="60"/>
+      <c r="H202" s="62"/>
     </row>
     <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
@@ -6410,16 +6445,16 @@
       <c r="H206" s="10"/>
     </row>
     <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="53" t="s">
+      <c r="A207" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B207" s="54"/>
-      <c r="C207" s="54"/>
-      <c r="D207" s="54"/>
-      <c r="E207" s="55"/>
-      <c r="F207" s="54"/>
-      <c r="G207" s="54"/>
-      <c r="H207" s="56"/>
+      <c r="B207" s="60"/>
+      <c r="C207" s="60"/>
+      <c r="D207" s="60"/>
+      <c r="E207" s="61"/>
+      <c r="F207" s="60"/>
+      <c r="G207" s="60"/>
+      <c r="H207" s="62"/>
     </row>
     <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
@@ -6513,16 +6548,16 @@
       </c>
     </row>
     <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="53" t="s">
+      <c r="A211" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B211" s="54"/>
-      <c r="C211" s="54"/>
-      <c r="D211" s="54"/>
-      <c r="E211" s="55"/>
-      <c r="F211" s="54"/>
-      <c r="G211" s="54"/>
-      <c r="H211" s="56"/>
+      <c r="B211" s="60"/>
+      <c r="C211" s="60"/>
+      <c r="D211" s="60"/>
+      <c r="E211" s="61"/>
+      <c r="F211" s="60"/>
+      <c r="G211" s="60"/>
+      <c r="H211" s="62"/>
     </row>
     <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
@@ -6650,16 +6685,16 @@
       <c r="H216" s="30"/>
     </row>
     <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="53" t="s">
+      <c r="A217" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B217" s="54"/>
-      <c r="C217" s="54"/>
-      <c r="D217" s="54"/>
-      <c r="E217" s="55"/>
-      <c r="F217" s="54"/>
-      <c r="G217" s="54"/>
-      <c r="H217" s="56"/>
+      <c r="B217" s="60"/>
+      <c r="C217" s="60"/>
+      <c r="D217" s="60"/>
+      <c r="E217" s="61"/>
+      <c r="F217" s="60"/>
+      <c r="G217" s="60"/>
+      <c r="H217" s="62"/>
     </row>
     <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
@@ -6751,16 +6786,16 @@
       </c>
     </row>
     <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="53" t="s">
+      <c r="A221" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B221" s="54"/>
-      <c r="C221" s="54"/>
-      <c r="D221" s="54"/>
-      <c r="E221" s="55"/>
-      <c r="F221" s="54"/>
-      <c r="G221" s="54"/>
-      <c r="H221" s="56"/>
+      <c r="B221" s="60"/>
+      <c r="C221" s="60"/>
+      <c r="D221" s="60"/>
+      <c r="E221" s="61"/>
+      <c r="F221" s="60"/>
+      <c r="G221" s="60"/>
+      <c r="H221" s="62"/>
     </row>
     <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
@@ -6904,16 +6939,16 @@
       <c r="H226" s="30"/>
     </row>
     <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="53" t="s">
+      <c r="A227" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B227" s="54"/>
-      <c r="C227" s="54"/>
-      <c r="D227" s="54"/>
-      <c r="E227" s="55"/>
-      <c r="F227" s="54"/>
-      <c r="G227" s="54"/>
-      <c r="H227" s="56"/>
+      <c r="B227" s="60"/>
+      <c r="C227" s="60"/>
+      <c r="D227" s="60"/>
+      <c r="E227" s="61"/>
+      <c r="F227" s="60"/>
+      <c r="G227" s="60"/>
+      <c r="H227" s="62"/>
     </row>
     <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
@@ -7007,16 +7042,16 @@
       </c>
     </row>
     <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="53" t="s">
+      <c r="A231" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B231" s="54"/>
-      <c r="C231" s="54"/>
-      <c r="D231" s="54"/>
-      <c r="E231" s="55"/>
-      <c r="F231" s="54"/>
-      <c r="G231" s="54"/>
-      <c r="H231" s="56"/>
+      <c r="B231" s="60"/>
+      <c r="C231" s="60"/>
+      <c r="D231" s="60"/>
+      <c r="E231" s="61"/>
+      <c r="F231" s="60"/>
+      <c r="G231" s="60"/>
+      <c r="H231" s="62"/>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
@@ -7161,14 +7196,14 @@
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A237" s="53"/>
-      <c r="B237" s="54"/>
-      <c r="C237" s="54"/>
-      <c r="D237" s="54"/>
-      <c r="E237" s="54"/>
-      <c r="F237" s="54"/>
-      <c r="G237" s="54"/>
-      <c r="H237" s="56"/>
+      <c r="A237" s="59"/>
+      <c r="B237" s="60"/>
+      <c r="C237" s="60"/>
+      <c r="D237" s="60"/>
+      <c r="E237" s="60"/>
+      <c r="F237" s="60"/>
+      <c r="G237" s="60"/>
+      <c r="H237" s="62"/>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="40">
@@ -7259,14 +7294,14 @@
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A241" s="73"/>
-      <c r="B241" s="74"/>
-      <c r="C241" s="74"/>
-      <c r="D241" s="74"/>
-      <c r="E241" s="75"/>
-      <c r="F241" s="74"/>
-      <c r="G241" s="74"/>
-      <c r="H241" s="76"/>
+      <c r="A241" s="79"/>
+      <c r="B241" s="80"/>
+      <c r="C241" s="80"/>
+      <c r="D241" s="80"/>
+      <c r="E241" s="81"/>
+      <c r="F241" s="80"/>
+      <c r="G241" s="80"/>
+      <c r="H241" s="82"/>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="40">
@@ -7343,14 +7378,14 @@
       <c r="H244" s="10"/>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A245" s="53"/>
-      <c r="B245" s="54"/>
-      <c r="C245" s="54"/>
-      <c r="D245" s="54"/>
-      <c r="E245" s="54"/>
-      <c r="F245" s="54"/>
-      <c r="G245" s="54"/>
-      <c r="H245" s="56"/>
+      <c r="A245" s="59"/>
+      <c r="B245" s="60"/>
+      <c r="C245" s="60"/>
+      <c r="D245" s="60"/>
+      <c r="E245" s="60"/>
+      <c r="F245" s="60"/>
+      <c r="G245" s="60"/>
+      <c r="H245" s="62"/>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
@@ -7364,18 +7399,18 @@
         <v>46020</v>
       </c>
       <c r="D246" s="31">
-        <v>46017</v>
-      </c>
-      <c r="E246" s="37"/>
+        <v>46027</v>
+      </c>
+      <c r="E246" s="37">
+        <v>4728</v>
+      </c>
       <c r="F246" s="39">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="G246" s="39">
-        <v>46035</v>
-      </c>
-      <c r="H246" s="44" t="s">
-        <v>78</v>
-      </c>
+        <v>46034</v>
+      </c>
+      <c r="H246" s="45"/>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
@@ -7383,130 +7418,134 @@
         <v>197</v>
       </c>
       <c r="B247" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C247" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="D247" s="36">
+        <v>46027</v>
+      </c>
+      <c r="E247" s="37">
+        <v>2856</v>
+      </c>
+      <c r="F247" s="36">
+        <v>46035</v>
+      </c>
+      <c r="G247" s="36">
+        <v>46035</v>
+      </c>
+      <c r="H247" s="45"/>
+    </row>
+    <row r="248" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A248" s="54">
+        <f>MAX(A236:A247)+1</f>
+        <v>198</v>
+      </c>
+      <c r="B248" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="C247" s="39">
+      <c r="C248" s="56">
         <v>46030</v>
       </c>
-      <c r="D247" s="39">
+      <c r="D248" s="56">
         <v>46031</v>
       </c>
-      <c r="E247" s="37"/>
-      <c r="F247" s="39">
+      <c r="E248" s="57"/>
+      <c r="F248" s="56">
         <v>46036</v>
       </c>
-      <c r="G247" s="39">
+      <c r="G248" s="56">
         <v>46037</v>
       </c>
-      <c r="H247" s="10"/>
-    </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A248" s="53"/>
-      <c r="B248" s="54"/>
-      <c r="C248" s="54"/>
-      <c r="D248" s="54"/>
-      <c r="E248" s="54"/>
-      <c r="F248" s="54"/>
-      <c r="G248" s="54"/>
-      <c r="H248" s="56"/>
+      <c r="H248" s="58" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A249" s="2">
-        <f>MAX(A238:A248)+1</f>
-        <v>198</v>
-      </c>
-      <c r="B249" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C249" s="39">
-        <v>46034</v>
-      </c>
-      <c r="D249" s="39">
-        <v>46035</v>
-      </c>
-      <c r="E249" s="37"/>
-      <c r="F249" s="39">
-        <v>46042</v>
-      </c>
-      <c r="G249" s="39">
-        <v>46042</v>
-      </c>
-      <c r="H249" s="10"/>
+      <c r="A249" s="59"/>
+      <c r="B249" s="60"/>
+      <c r="C249" s="60"/>
+      <c r="D249" s="60"/>
+      <c r="E249" s="60"/>
+      <c r="F249" s="60"/>
+      <c r="G249" s="60"/>
+      <c r="H249" s="62"/>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
-        <f>MAX(A238:A248)+1</f>
-        <v>198</v>
-      </c>
-      <c r="B250" s="38" t="s">
-        <v>15</v>
+        <f>MAX(A238:A249)+1</f>
+        <v>199</v>
+      </c>
+      <c r="B250" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="C250" s="39">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="D250" s="39">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="E250" s="37"/>
       <c r="F250" s="39">
+        <v>46042</v>
+      </c>
+      <c r="G250" s="39">
+        <v>46042</v>
+      </c>
+      <c r="H250" s="10"/>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A251" s="2">
+        <f t="shared" ref="A251:A254" si="264">MAX(A239:A250)+1</f>
+        <v>200</v>
+      </c>
+      <c r="B251" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C251" s="39">
+        <v>46031</v>
+      </c>
+      <c r="D251" s="39">
+        <v>46034</v>
+      </c>
+      <c r="E251" s="37"/>
+      <c r="F251" s="39">
         <v>46041</v>
       </c>
-      <c r="G250" s="39">
+      <c r="G251" s="39">
         <v>46041</v>
       </c>
-      <c r="H250" s="17"/>
-    </row>
-    <row r="251" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A251" s="2">
-        <f>MAX(A237:A247)+1</f>
-        <v>198</v>
-      </c>
-      <c r="B251" s="9" t="s">
+      <c r="H251" s="17"/>
+    </row>
+    <row r="252" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A252" s="2">
+        <f t="shared" si="264"/>
+        <v>201</v>
+      </c>
+      <c r="B252" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C251" s="36" t="s">
+      <c r="C252" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D251" s="36" t="s">
+      <c r="D252" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="E251" s="37"/>
-      <c r="F251" s="36"/>
-      <c r="G251" s="36"/>
-      <c r="H251" s="10" t="s">
+      <c r="E252" s="37"/>
+      <c r="F252" s="36"/>
+      <c r="G252" s="36"/>
+      <c r="H252" s="10" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A252" s="2">
-        <f>MAX(A240:A251)+1</f>
-        <v>199</v>
-      </c>
-      <c r="B252" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C252" s="39">
-        <v>46037</v>
-      </c>
-      <c r="D252" s="39">
-        <v>46038</v>
-      </c>
-      <c r="E252" s="4"/>
-      <c r="F252" s="39">
-        <v>46043</v>
-      </c>
-      <c r="G252" s="39">
-        <v>46044</v>
-      </c>
-      <c r="H252" s="10"/>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
-        <f>MAX(A239:A251)+1</f>
-        <v>199</v>
+        <f t="shared" si="264"/>
+        <v>202</v>
       </c>
       <c r="B253" s="9" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C253" s="39">
         <v>46037</v>
@@ -7514,50 +7553,73 @@
       <c r="D253" s="39">
         <v>46038</v>
       </c>
-      <c r="E253" s="37"/>
+      <c r="E253" s="4"/>
       <c r="F253" s="39">
+        <v>46043</v>
+      </c>
+      <c r="G253" s="39">
+        <v>46044</v>
+      </c>
+      <c r="H253" s="10"/>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A254" s="2">
+        <f t="shared" si="264"/>
+        <v>203</v>
+      </c>
+      <c r="B254" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C254" s="39">
+        <v>46037</v>
+      </c>
+      <c r="D254" s="39">
+        <v>46038</v>
+      </c>
+      <c r="E254" s="37"/>
+      <c r="F254" s="39">
         <v>46048</v>
       </c>
-      <c r="G253" s="39">
+      <c r="G254" s="39">
         <v>46048</v>
       </c>
-      <c r="H253" s="10"/>
-    </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A255" s="70" t="s">
+      <c r="H254" s="10"/>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A256" s="76" t="s">
         <v>75</v>
       </c>
-      <c r="B255" s="70"/>
-      <c r="C255" s="70"/>
-      <c r="D255" s="70"/>
-      <c r="E255" s="70"/>
-      <c r="F255" s="70"/>
-      <c r="G255" s="70"/>
-      <c r="H255" s="70"/>
-    </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A256" s="71" t="s">
+      <c r="B256" s="76"/>
+      <c r="C256" s="76"/>
+      <c r="D256" s="76"/>
+      <c r="E256" s="76"/>
+      <c r="F256" s="76"/>
+      <c r="G256" s="76"/>
+      <c r="H256" s="76"/>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A257" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="B256" s="71"/>
-      <c r="C256" s="71"/>
-      <c r="D256" s="71"/>
-      <c r="E256" s="71"/>
-      <c r="F256" s="71"/>
-      <c r="G256" s="71"/>
-      <c r="H256" s="71"/>
-    </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A257" s="72" t="s">
+      <c r="B257" s="77"/>
+      <c r="C257" s="77"/>
+      <c r="D257" s="77"/>
+      <c r="E257" s="77"/>
+      <c r="F257" s="77"/>
+      <c r="G257" s="77"/>
+      <c r="H257" s="77"/>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A258" s="78" t="s">
         <v>77</v>
       </c>
-      <c r="B257" s="72"/>
-      <c r="C257" s="72"/>
-      <c r="D257" s="72"/>
-      <c r="E257" s="72"/>
-      <c r="F257" s="72"/>
-      <c r="G257" s="72"/>
-      <c r="H257" s="72"/>
+      <c r="B258" s="78"/>
+      <c r="C258" s="78"/>
+      <c r="D258" s="78"/>
+      <c r="E258" s="78"/>
+      <c r="F258" s="78"/>
+      <c r="G258" s="78"/>
+      <c r="H258" s="78"/>
     </row>
   </sheetData>
   <autoFilter ref="A8:H236" xr:uid="{9D5F3532-A341-428E-AFDB-DF9AAA83E1F5}">
@@ -7572,10 +7634,10 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="50">
-    <mergeCell ref="A248:H248"/>
-    <mergeCell ref="A255:H255"/>
+    <mergeCell ref="A249:H249"/>
     <mergeCell ref="A256:H256"/>
     <mergeCell ref="A257:H257"/>
+    <mergeCell ref="A258:H258"/>
     <mergeCell ref="A152:H152"/>
     <mergeCell ref="A202:H202"/>
     <mergeCell ref="A245:H245"/>

--- a/графики/график Ташкент.xlsx
+++ b/графики/график Ташкент.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6628DC-9823-452B-801E-4E56E5454765}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{852B7F7D-AE72-4D44-94C7-A935BC40E009}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="81">
   <si>
     <t>Контракт</t>
   </si>
@@ -338,6 +338,9 @@
   <si>
     <t>погрузки на 14,01,26 не будет (письмо от Шуваловой)</t>
   </si>
+  <si>
+    <t>07,01,26 сделали дозаказ</t>
+  </si>
 </sst>
 </file>
 
@@ -346,12 +349,20 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -629,7 +640,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -665,127 +676,127 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -809,71 +820,74 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1173,19 +1187,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="69"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="73"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="74" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="46" t="s">
@@ -1206,12 +1220,12 @@
       <c r="G2" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="73" t="s">
+      <c r="H2" s="77" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="71"/>
+      <c r="A3" s="75"/>
       <c r="B3" s="46" t="s">
         <v>5</v>
       </c>
@@ -1228,10 +1242,10 @@
       <c r="G3" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="74"/>
+      <c r="H3" s="78"/>
     </row>
     <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="71"/>
+      <c r="A4" s="75"/>
       <c r="B4" s="46" t="s">
         <v>6</v>
       </c>
@@ -1248,10 +1262,10 @@
       <c r="G4" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="74"/>
+      <c r="H4" s="78"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="71"/>
+      <c r="A5" s="75"/>
       <c r="B5" s="46" t="s">
         <v>19</v>
       </c>
@@ -1262,14 +1276,14 @@
         <v>9</v>
       </c>
       <c r="E5" s="48"/>
-      <c r="F5" s="64" t="s">
+      <c r="F5" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="65"/>
-      <c r="H5" s="74"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="78"/>
     </row>
     <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="71"/>
+      <c r="A6" s="75"/>
       <c r="B6" s="46" t="s">
         <v>15</v>
       </c>
@@ -1286,10 +1300,10 @@
       <c r="G6" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="74"/>
+      <c r="H6" s="78"/>
     </row>
     <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
+      <c r="A7" s="76"/>
       <c r="B7" s="46" t="s">
         <v>26</v>
       </c>
@@ -1306,7 +1320,7 @@
       <c r="G7" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="75"/>
+      <c r="H7" s="79"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
@@ -1456,7 +1470,7 @@
       <c r="E14" s="60"/>
       <c r="F14" s="60"/>
       <c r="G14" s="60"/>
-      <c r="H14" s="62"/>
+      <c r="H14" s="61"/>
     </row>
     <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -1606,10 +1620,10 @@
       <c r="B20" s="60"/>
       <c r="C20" s="60"/>
       <c r="D20" s="60"/>
-      <c r="E20" s="61"/>
+      <c r="E20" s="65"/>
       <c r="F20" s="60"/>
       <c r="G20" s="60"/>
-      <c r="H20" s="63"/>
+      <c r="H20" s="80"/>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -1758,10 +1772,10 @@
       <c r="B26" s="60"/>
       <c r="C26" s="60"/>
       <c r="D26" s="60"/>
-      <c r="E26" s="61"/>
+      <c r="E26" s="65"/>
       <c r="F26" s="60"/>
       <c r="G26" s="60"/>
-      <c r="H26" s="63"/>
+      <c r="H26" s="80"/>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -1968,10 +1982,10 @@
       <c r="B34" s="60"/>
       <c r="C34" s="60"/>
       <c r="D34" s="60"/>
-      <c r="E34" s="61"/>
+      <c r="E34" s="65"/>
       <c r="F34" s="60"/>
       <c r="G34" s="60"/>
-      <c r="H34" s="63"/>
+      <c r="H34" s="80"/>
     </row>
     <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -2162,10 +2176,10 @@
       <c r="B41" s="60"/>
       <c r="C41" s="60"/>
       <c r="D41" s="60"/>
-      <c r="E41" s="61"/>
+      <c r="E41" s="65"/>
       <c r="F41" s="60"/>
       <c r="G41" s="60"/>
-      <c r="H41" s="63"/>
+      <c r="H41" s="80"/>
     </row>
     <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
@@ -2373,10 +2387,10 @@
       <c r="B49" s="60"/>
       <c r="C49" s="60"/>
       <c r="D49" s="60"/>
-      <c r="E49" s="61"/>
+      <c r="E49" s="65"/>
       <c r="F49" s="60"/>
       <c r="G49" s="60"/>
-      <c r="H49" s="63"/>
+      <c r="H49" s="80"/>
     </row>
     <row r="50" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
@@ -2497,10 +2511,10 @@
       <c r="B54" s="60"/>
       <c r="C54" s="60"/>
       <c r="D54" s="60"/>
-      <c r="E54" s="61"/>
+      <c r="E54" s="65"/>
       <c r="F54" s="60"/>
       <c r="G54" s="60"/>
-      <c r="H54" s="63"/>
+      <c r="H54" s="80"/>
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
@@ -2658,7 +2672,7 @@
       <c r="E61" s="60"/>
       <c r="F61" s="60"/>
       <c r="G61" s="60"/>
-      <c r="H61" s="62"/>
+      <c r="H61" s="61"/>
     </row>
     <row r="62" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
@@ -2782,7 +2796,7 @@
       <c r="E66" s="60"/>
       <c r="F66" s="60"/>
       <c r="G66" s="60"/>
-      <c r="H66" s="62"/>
+      <c r="H66" s="61"/>
     </row>
     <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
@@ -2966,7 +2980,7 @@
       <c r="E73" s="60"/>
       <c r="F73" s="60"/>
       <c r="G73" s="60"/>
-      <c r="H73" s="62"/>
+      <c r="H73" s="61"/>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
@@ -3094,7 +3108,7 @@
       <c r="E78" s="60"/>
       <c r="F78" s="60"/>
       <c r="G78" s="60"/>
-      <c r="H78" s="62"/>
+      <c r="H78" s="61"/>
     </row>
     <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
@@ -3278,7 +3292,7 @@
       <c r="E85" s="60"/>
       <c r="F85" s="60"/>
       <c r="G85" s="60"/>
-      <c r="H85" s="62"/>
+      <c r="H85" s="61"/>
     </row>
     <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
@@ -3405,7 +3419,7 @@
       <c r="E90" s="60"/>
       <c r="F90" s="60"/>
       <c r="G90" s="60"/>
-      <c r="H90" s="62"/>
+      <c r="H90" s="61"/>
     </row>
     <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
@@ -3588,7 +3602,7 @@
       <c r="E97" s="60"/>
       <c r="F97" s="60"/>
       <c r="G97" s="60"/>
-      <c r="H97" s="62"/>
+      <c r="H97" s="61"/>
     </row>
     <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
@@ -3713,7 +3727,7 @@
       <c r="E102" s="60"/>
       <c r="F102" s="60"/>
       <c r="G102" s="60"/>
-      <c r="H102" s="62"/>
+      <c r="H102" s="61"/>
     </row>
     <row r="103" spans="1:8" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
@@ -3900,7 +3914,7 @@
       <c r="E109" s="60"/>
       <c r="F109" s="60"/>
       <c r="G109" s="60"/>
-      <c r="H109" s="62"/>
+      <c r="H109" s="61"/>
     </row>
     <row r="110" spans="1:8" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
@@ -4083,7 +4097,7 @@
       <c r="E116" s="60"/>
       <c r="F116" s="60"/>
       <c r="G116" s="60"/>
-      <c r="H116" s="62"/>
+      <c r="H116" s="61"/>
     </row>
     <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
@@ -4191,7 +4205,7 @@
       <c r="E121" s="60"/>
       <c r="F121" s="60"/>
       <c r="G121" s="60"/>
-      <c r="H121" s="62"/>
+      <c r="H121" s="61"/>
     </row>
     <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
@@ -4374,7 +4388,7 @@
       <c r="E128" s="60"/>
       <c r="F128" s="60"/>
       <c r="G128" s="60"/>
-      <c r="H128" s="62"/>
+      <c r="H128" s="61"/>
     </row>
     <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
@@ -4502,7 +4516,7 @@
       <c r="E133" s="60"/>
       <c r="F133" s="60"/>
       <c r="G133" s="60"/>
-      <c r="H133" s="62"/>
+      <c r="H133" s="61"/>
     </row>
     <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
@@ -4690,7 +4704,7 @@
       <c r="E140" s="60"/>
       <c r="F140" s="60"/>
       <c r="G140" s="60"/>
-      <c r="H140" s="62"/>
+      <c r="H140" s="61"/>
     </row>
     <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
@@ -4815,10 +4829,10 @@
       <c r="B145" s="60"/>
       <c r="C145" s="60"/>
       <c r="D145" s="60"/>
-      <c r="E145" s="61"/>
+      <c r="E145" s="65"/>
       <c r="F145" s="60"/>
       <c r="G145" s="60"/>
-      <c r="H145" s="62"/>
+      <c r="H145" s="61"/>
     </row>
     <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
@@ -5003,10 +5017,10 @@
       <c r="B152" s="60"/>
       <c r="C152" s="60"/>
       <c r="D152" s="60"/>
-      <c r="E152" s="61"/>
+      <c r="E152" s="65"/>
       <c r="F152" s="60"/>
       <c r="G152" s="60"/>
-      <c r="H152" s="62"/>
+      <c r="H152" s="61"/>
     </row>
     <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
@@ -5102,10 +5116,10 @@
       <c r="B156" s="60"/>
       <c r="C156" s="60"/>
       <c r="D156" s="60"/>
-      <c r="E156" s="61"/>
+      <c r="E156" s="65"/>
       <c r="F156" s="60"/>
       <c r="G156" s="60"/>
-      <c r="H156" s="62"/>
+      <c r="H156" s="61"/>
     </row>
     <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
@@ -5264,10 +5278,10 @@
       <c r="B162" s="60"/>
       <c r="C162" s="60"/>
       <c r="D162" s="60"/>
-      <c r="E162" s="61"/>
+      <c r="E162" s="65"/>
       <c r="F162" s="60"/>
       <c r="G162" s="60"/>
-      <c r="H162" s="62"/>
+      <c r="H162" s="61"/>
     </row>
     <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
@@ -5368,10 +5382,10 @@
       <c r="B166" s="60"/>
       <c r="C166" s="60"/>
       <c r="D166" s="60"/>
-      <c r="E166" s="61"/>
+      <c r="E166" s="65"/>
       <c r="F166" s="60"/>
       <c r="G166" s="60"/>
-      <c r="H166" s="62"/>
+      <c r="H166" s="61"/>
     </row>
     <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
@@ -5530,10 +5544,10 @@
       <c r="B172" s="60"/>
       <c r="C172" s="60"/>
       <c r="D172" s="60"/>
-      <c r="E172" s="61"/>
+      <c r="E172" s="65"/>
       <c r="F172" s="60"/>
       <c r="G172" s="60"/>
-      <c r="H172" s="62"/>
+      <c r="H172" s="61"/>
     </row>
     <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
@@ -5634,10 +5648,10 @@
       <c r="B176" s="60"/>
       <c r="C176" s="60"/>
       <c r="D176" s="60"/>
-      <c r="E176" s="61"/>
+      <c r="E176" s="65"/>
       <c r="F176" s="60"/>
       <c r="G176" s="60"/>
-      <c r="H176" s="62"/>
+      <c r="H176" s="61"/>
     </row>
     <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
@@ -5797,10 +5811,10 @@
       <c r="B182" s="60"/>
       <c r="C182" s="60"/>
       <c r="D182" s="60"/>
-      <c r="E182" s="61"/>
+      <c r="E182" s="65"/>
       <c r="F182" s="60"/>
       <c r="G182" s="60"/>
-      <c r="H182" s="62"/>
+      <c r="H182" s="61"/>
     </row>
     <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
@@ -5898,10 +5912,10 @@
       <c r="B186" s="60"/>
       <c r="C186" s="60"/>
       <c r="D186" s="60"/>
-      <c r="E186" s="61"/>
+      <c r="E186" s="65"/>
       <c r="F186" s="60"/>
       <c r="G186" s="60"/>
-      <c r="H186" s="62"/>
+      <c r="H186" s="61"/>
     </row>
     <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
@@ -6059,10 +6073,10 @@
       <c r="B192" s="60"/>
       <c r="C192" s="60"/>
       <c r="D192" s="60"/>
-      <c r="E192" s="61"/>
+      <c r="E192" s="65"/>
       <c r="F192" s="60"/>
       <c r="G192" s="60"/>
-      <c r="H192" s="62"/>
+      <c r="H192" s="61"/>
     </row>
     <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
@@ -6163,10 +6177,10 @@
       <c r="B196" s="60"/>
       <c r="C196" s="60"/>
       <c r="D196" s="60"/>
-      <c r="E196" s="61"/>
+      <c r="E196" s="65"/>
       <c r="F196" s="60"/>
       <c r="G196" s="60"/>
-      <c r="H196" s="62"/>
+      <c r="H196" s="61"/>
     </row>
     <row r="197" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
@@ -6323,10 +6337,10 @@
       <c r="B202" s="60"/>
       <c r="C202" s="60"/>
       <c r="D202" s="60"/>
-      <c r="E202" s="61"/>
+      <c r="E202" s="65"/>
       <c r="F202" s="60"/>
       <c r="G202" s="60"/>
-      <c r="H202" s="62"/>
+      <c r="H202" s="61"/>
     </row>
     <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
@@ -6451,10 +6465,10 @@
       <c r="B207" s="60"/>
       <c r="C207" s="60"/>
       <c r="D207" s="60"/>
-      <c r="E207" s="61"/>
+      <c r="E207" s="65"/>
       <c r="F207" s="60"/>
       <c r="G207" s="60"/>
-      <c r="H207" s="62"/>
+      <c r="H207" s="61"/>
     </row>
     <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
@@ -6554,10 +6568,10 @@
       <c r="B211" s="60"/>
       <c r="C211" s="60"/>
       <c r="D211" s="60"/>
-      <c r="E211" s="61"/>
+      <c r="E211" s="65"/>
       <c r="F211" s="60"/>
       <c r="G211" s="60"/>
-      <c r="H211" s="62"/>
+      <c r="H211" s="61"/>
     </row>
     <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
@@ -6691,10 +6705,10 @@
       <c r="B217" s="60"/>
       <c r="C217" s="60"/>
       <c r="D217" s="60"/>
-      <c r="E217" s="61"/>
+      <c r="E217" s="65"/>
       <c r="F217" s="60"/>
       <c r="G217" s="60"/>
-      <c r="H217" s="62"/>
+      <c r="H217" s="61"/>
     </row>
     <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
@@ -6792,10 +6806,10 @@
       <c r="B221" s="60"/>
       <c r="C221" s="60"/>
       <c r="D221" s="60"/>
-      <c r="E221" s="61"/>
+      <c r="E221" s="65"/>
       <c r="F221" s="60"/>
       <c r="G221" s="60"/>
-      <c r="H221" s="62"/>
+      <c r="H221" s="61"/>
     </row>
     <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
@@ -6945,10 +6959,10 @@
       <c r="B227" s="60"/>
       <c r="C227" s="60"/>
       <c r="D227" s="60"/>
-      <c r="E227" s="61"/>
+      <c r="E227" s="65"/>
       <c r="F227" s="60"/>
       <c r="G227" s="60"/>
-      <c r="H227" s="62"/>
+      <c r="H227" s="61"/>
     </row>
     <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
@@ -7048,10 +7062,10 @@
       <c r="B231" s="60"/>
       <c r="C231" s="60"/>
       <c r="D231" s="60"/>
-      <c r="E231" s="61"/>
+      <c r="E231" s="65"/>
       <c r="F231" s="60"/>
       <c r="G231" s="60"/>
-      <c r="H231" s="62"/>
+      <c r="H231" s="61"/>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
@@ -7203,7 +7217,7 @@
       <c r="E237" s="60"/>
       <c r="F237" s="60"/>
       <c r="G237" s="60"/>
-      <c r="H237" s="62"/>
+      <c r="H237" s="61"/>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="40">
@@ -7294,14 +7308,14 @@
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A241" s="79"/>
-      <c r="B241" s="80"/>
-      <c r="C241" s="80"/>
-      <c r="D241" s="80"/>
-      <c r="E241" s="81"/>
-      <c r="F241" s="80"/>
-      <c r="G241" s="80"/>
-      <c r="H241" s="82"/>
+      <c r="A241" s="66"/>
+      <c r="B241" s="67"/>
+      <c r="C241" s="67"/>
+      <c r="D241" s="67"/>
+      <c r="E241" s="68"/>
+      <c r="F241" s="67"/>
+      <c r="G241" s="67"/>
+      <c r="H241" s="69"/>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="40">
@@ -7385,7 +7399,7 @@
       <c r="E245" s="60"/>
       <c r="F245" s="60"/>
       <c r="G245" s="60"/>
-      <c r="H245" s="62"/>
+      <c r="H245" s="61"/>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
@@ -7402,7 +7416,8 @@
         <v>46027</v>
       </c>
       <c r="E246" s="37">
-        <v>4728</v>
+        <f>4728+2633</f>
+        <v>7361</v>
       </c>
       <c r="F246" s="39">
         <v>46034</v>
@@ -7410,7 +7425,9 @@
       <c r="G246" s="39">
         <v>46034</v>
       </c>
-      <c r="H246" s="45"/>
+      <c r="H246" s="83" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
@@ -7470,7 +7487,7 @@
       <c r="E249" s="60"/>
       <c r="F249" s="60"/>
       <c r="G249" s="60"/>
-      <c r="H249" s="62"/>
+      <c r="H249" s="61"/>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
@@ -7586,40 +7603,40 @@
       <c r="H254" s="10"/>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A256" s="76" t="s">
+      <c r="A256" s="62" t="s">
         <v>75</v>
       </c>
-      <c r="B256" s="76"/>
-      <c r="C256" s="76"/>
-      <c r="D256" s="76"/>
-      <c r="E256" s="76"/>
-      <c r="F256" s="76"/>
-      <c r="G256" s="76"/>
-      <c r="H256" s="76"/>
+      <c r="B256" s="62"/>
+      <c r="C256" s="62"/>
+      <c r="D256" s="62"/>
+      <c r="E256" s="62"/>
+      <c r="F256" s="62"/>
+      <c r="G256" s="62"/>
+      <c r="H256" s="62"/>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A257" s="77" t="s">
+      <c r="A257" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="B257" s="77"/>
-      <c r="C257" s="77"/>
-      <c r="D257" s="77"/>
-      <c r="E257" s="77"/>
-      <c r="F257" s="77"/>
-      <c r="G257" s="77"/>
-      <c r="H257" s="77"/>
+      <c r="B257" s="63"/>
+      <c r="C257" s="63"/>
+      <c r="D257" s="63"/>
+      <c r="E257" s="63"/>
+      <c r="F257" s="63"/>
+      <c r="G257" s="63"/>
+      <c r="H257" s="63"/>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A258" s="78" t="s">
+      <c r="A258" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="B258" s="78"/>
-      <c r="C258" s="78"/>
-      <c r="D258" s="78"/>
-      <c r="E258" s="78"/>
-      <c r="F258" s="78"/>
-      <c r="G258" s="78"/>
-      <c r="H258" s="78"/>
+      <c r="B258" s="64"/>
+      <c r="C258" s="64"/>
+      <c r="D258" s="64"/>
+      <c r="E258" s="64"/>
+      <c r="F258" s="64"/>
+      <c r="G258" s="64"/>
+      <c r="H258" s="64"/>
     </row>
   </sheetData>
   <autoFilter ref="A8:H236" xr:uid="{9D5F3532-A341-428E-AFDB-DF9AAA83E1F5}">
@@ -7634,6 +7651,40 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="50">
+    <mergeCell ref="A207:H207"/>
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A156:H156"/>
+    <mergeCell ref="A186:H186"/>
+    <mergeCell ref="A182:H182"/>
+    <mergeCell ref="A176:H176"/>
+    <mergeCell ref="A172:H172"/>
+    <mergeCell ref="A166:H166"/>
+    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A85:H85"/>
+    <mergeCell ref="A128:H128"/>
+    <mergeCell ref="A133:H133"/>
+    <mergeCell ref="A140:H140"/>
+    <mergeCell ref="A109:H109"/>
+    <mergeCell ref="A162:H162"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A116:H116"/>
+    <mergeCell ref="A145:H145"/>
+    <mergeCell ref="A97:H97"/>
+    <mergeCell ref="A121:H121"/>
+    <mergeCell ref="A102:H102"/>
     <mergeCell ref="A249:H249"/>
     <mergeCell ref="A256:H256"/>
     <mergeCell ref="A257:H257"/>
@@ -7650,40 +7701,6 @@
     <mergeCell ref="A237:H237"/>
     <mergeCell ref="A231:H231"/>
     <mergeCell ref="A227:H227"/>
-    <mergeCell ref="A116:H116"/>
-    <mergeCell ref="A145:H145"/>
-    <mergeCell ref="A97:H97"/>
-    <mergeCell ref="A121:H121"/>
-    <mergeCell ref="A102:H102"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A207:H207"/>
-    <mergeCell ref="A73:H73"/>
-    <mergeCell ref="A156:H156"/>
-    <mergeCell ref="A186:H186"/>
-    <mergeCell ref="A182:H182"/>
-    <mergeCell ref="A176:H176"/>
-    <mergeCell ref="A172:H172"/>
-    <mergeCell ref="A166:H166"/>
-    <mergeCell ref="A90:H90"/>
-    <mergeCell ref="A85:H85"/>
-    <mergeCell ref="A128:H128"/>
-    <mergeCell ref="A133:H133"/>
-    <mergeCell ref="A140:H140"/>
-    <mergeCell ref="A109:H109"/>
-    <mergeCell ref="A162:H162"/>
-    <mergeCell ref="A78:H78"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="93" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/графики/график Ташкент.xlsx
+++ b/графики/график Ташкент.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{852B7F7D-AE72-4D44-94C7-A935BC40E009}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66C2EA8-8CDE-48B6-B50B-3C38D911E32E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="79">
   <si>
     <t>Контракт</t>
   </si>
@@ -324,15 +324,6 @@
     <t>еще не отправляли</t>
   </si>
   <si>
-    <t>Заказы, которые должны забрать перед НГ</t>
-  </si>
-  <si>
-    <t>Заказы, которые нужно отправить на заводы до НГ, а получение товара после НГ</t>
-  </si>
-  <si>
-    <t>Заказы и отгрузки после НГ</t>
-  </si>
-  <si>
     <t>без расчета</t>
   </si>
   <si>
@@ -340,6 +331,9 @@
   </si>
   <si>
     <t>07,01,26 сделали дозаказ</t>
+  </si>
+  <si>
+    <t>Шувалова перенсла погрузку с 19,01 на 26,01</t>
   </si>
 </sst>
 </file>
@@ -640,7 +634,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -754,9 +748,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -767,9 +758,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -793,9 +781,6 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -814,6 +799,9 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -822,15 +810,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -886,8 +865,8 @@
     <xf numFmtId="164" fontId="16" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1172,7 +1151,7 @@
   <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H258"/>
+  <dimension ref="A1:H254"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="3" customWidth="1"/>
@@ -1187,164 +1166,164 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="73"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="68"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="48" t="s">
+      <c r="E2" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="47" t="s">
+      <c r="F2" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="77" t="s">
+      <c r="H2" s="72" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="75"/>
-      <c r="B3" s="46" t="s">
+      <c r="A3" s="70"/>
+      <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="47" t="s">
+      <c r="D3" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="48"/>
-      <c r="F3" s="47" t="s">
+      <c r="E3" s="46"/>
+      <c r="F3" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="47" t="s">
+      <c r="G3" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="78"/>
+      <c r="H3" s="73"/>
     </row>
     <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="75"/>
-      <c r="B4" s="46" t="s">
+      <c r="A4" s="70"/>
+      <c r="B4" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="48"/>
-      <c r="F4" s="47" t="s">
+      <c r="E4" s="46"/>
+      <c r="F4" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="47" t="s">
+      <c r="G4" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="78"/>
+      <c r="H4" s="73"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="75"/>
-      <c r="B5" s="46" t="s">
+      <c r="A5" s="70"/>
+      <c r="B5" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="48"/>
-      <c r="F5" s="81" t="s">
+      <c r="E5" s="46"/>
+      <c r="F5" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="82"/>
-      <c r="H5" s="78"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="73"/>
     </row>
     <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="75"/>
-      <c r="B6" s="46" t="s">
+      <c r="A6" s="70"/>
+      <c r="B6" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="48"/>
-      <c r="F6" s="47" t="s">
+      <c r="E6" s="46"/>
+      <c r="F6" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="47" t="s">
+      <c r="G6" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="78"/>
+      <c r="H6" s="73"/>
     </row>
     <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="76"/>
-      <c r="B7" s="46" t="s">
+      <c r="A7" s="71"/>
+      <c r="B7" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="48"/>
-      <c r="F7" s="47" t="s">
+      <c r="E7" s="46"/>
+      <c r="F7" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="79"/>
+      <c r="H7" s="74"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="49">
+      <c r="A8" s="47">
         <v>1</v>
       </c>
-      <c r="B8" s="49">
+      <c r="B8" s="47">
         <v>2</v>
       </c>
-      <c r="C8" s="49">
+      <c r="C8" s="47">
         <v>3</v>
       </c>
-      <c r="D8" s="49">
+      <c r="D8" s="47">
         <v>4</v>
       </c>
-      <c r="E8" s="50">
+      <c r="E8" s="48">
         <v>5</v>
       </c>
-      <c r="F8" s="49">
+      <c r="F8" s="47">
         <v>6</v>
       </c>
-      <c r="G8" s="49">
+      <c r="G8" s="47">
         <v>7</v>
       </c>
-      <c r="H8" s="51">
+      <c r="H8" s="49">
         <v>8</v>
       </c>
     </row>
@@ -1461,16 +1440,16 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="59" t="s">
+      <c r="A14" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="61"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="59"/>
     </row>
     <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -1614,16 +1593,16 @@
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="59" t="s">
+      <c r="A20" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="65"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="80"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="75"/>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -1766,16 +1745,16 @@
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="59" t="s">
+      <c r="A26" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="60"/>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="60"/>
-      <c r="G26" s="60"/>
-      <c r="H26" s="80"/>
+      <c r="B26" s="58"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="75"/>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -1976,16 +1955,16 @@
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="59" t="s">
+      <c r="A34" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="60"/>
-      <c r="C34" s="60"/>
-      <c r="D34" s="60"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="60"/>
-      <c r="G34" s="60"/>
-      <c r="H34" s="80"/>
+      <c r="B34" s="58"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="58"/>
+      <c r="G34" s="58"/>
+      <c r="H34" s="75"/>
     </row>
     <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -2170,16 +2149,16 @@
       </c>
     </row>
     <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="59" t="s">
+      <c r="A41" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="60"/>
-      <c r="C41" s="60"/>
-      <c r="D41" s="60"/>
-      <c r="E41" s="65"/>
-      <c r="F41" s="60"/>
-      <c r="G41" s="60"/>
-      <c r="H41" s="80"/>
+      <c r="B41" s="58"/>
+      <c r="C41" s="58"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="58"/>
+      <c r="H41" s="75"/>
     </row>
     <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
@@ -2381,16 +2360,16 @@
       <c r="H48" s="12"/>
     </row>
     <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="59" t="s">
+      <c r="A49" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B49" s="60"/>
-      <c r="C49" s="60"/>
-      <c r="D49" s="60"/>
-      <c r="E49" s="65"/>
-      <c r="F49" s="60"/>
-      <c r="G49" s="60"/>
-      <c r="H49" s="80"/>
+      <c r="B49" s="58"/>
+      <c r="C49" s="58"/>
+      <c r="D49" s="58"/>
+      <c r="E49" s="60"/>
+      <c r="F49" s="58"/>
+      <c r="G49" s="58"/>
+      <c r="H49" s="75"/>
     </row>
     <row r="50" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
@@ -2505,16 +2484,16 @@
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="59" t="s">
+      <c r="A54" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B54" s="60"/>
-      <c r="C54" s="60"/>
-      <c r="D54" s="60"/>
-      <c r="E54" s="65"/>
-      <c r="F54" s="60"/>
-      <c r="G54" s="60"/>
-      <c r="H54" s="80"/>
+      <c r="B54" s="58"/>
+      <c r="C54" s="58"/>
+      <c r="D54" s="58"/>
+      <c r="E54" s="60"/>
+      <c r="F54" s="58"/>
+      <c r="G54" s="58"/>
+      <c r="H54" s="75"/>
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
@@ -2663,16 +2642,16 @@
       </c>
     </row>
     <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="59" t="s">
+      <c r="A61" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B61" s="60"/>
-      <c r="C61" s="60"/>
-      <c r="D61" s="60"/>
-      <c r="E61" s="60"/>
-      <c r="F61" s="60"/>
-      <c r="G61" s="60"/>
-      <c r="H61" s="61"/>
+      <c r="B61" s="58"/>
+      <c r="C61" s="58"/>
+      <c r="D61" s="58"/>
+      <c r="E61" s="58"/>
+      <c r="F61" s="58"/>
+      <c r="G61" s="58"/>
+      <c r="H61" s="59"/>
     </row>
     <row r="62" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
@@ -2787,16 +2766,16 @@
       <c r="H65" s="10"/>
     </row>
     <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="59" t="s">
+      <c r="A66" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B66" s="60"/>
-      <c r="C66" s="60"/>
-      <c r="D66" s="60"/>
-      <c r="E66" s="60"/>
-      <c r="F66" s="60"/>
-      <c r="G66" s="60"/>
-      <c r="H66" s="61"/>
+      <c r="B66" s="58"/>
+      <c r="C66" s="58"/>
+      <c r="D66" s="58"/>
+      <c r="E66" s="58"/>
+      <c r="F66" s="58"/>
+      <c r="G66" s="58"/>
+      <c r="H66" s="59"/>
     </row>
     <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
@@ -2971,16 +2950,16 @@
       </c>
     </row>
     <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="59" t="s">
+      <c r="A73" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B73" s="60"/>
-      <c r="C73" s="60"/>
-      <c r="D73" s="60"/>
-      <c r="E73" s="60"/>
-      <c r="F73" s="60"/>
-      <c r="G73" s="60"/>
-      <c r="H73" s="61"/>
+      <c r="B73" s="58"/>
+      <c r="C73" s="58"/>
+      <c r="D73" s="58"/>
+      <c r="E73" s="58"/>
+      <c r="F73" s="58"/>
+      <c r="G73" s="58"/>
+      <c r="H73" s="59"/>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
@@ -3099,16 +3078,16 @@
       <c r="H77" s="10"/>
     </row>
     <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="59" t="s">
+      <c r="A78" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B78" s="60"/>
-      <c r="C78" s="60"/>
-      <c r="D78" s="60"/>
-      <c r="E78" s="60"/>
-      <c r="F78" s="60"/>
-      <c r="G78" s="60"/>
-      <c r="H78" s="61"/>
+      <c r="B78" s="58"/>
+      <c r="C78" s="58"/>
+      <c r="D78" s="58"/>
+      <c r="E78" s="58"/>
+      <c r="F78" s="58"/>
+      <c r="G78" s="58"/>
+      <c r="H78" s="59"/>
     </row>
     <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
@@ -3283,16 +3262,16 @@
       </c>
     </row>
     <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="59" t="s">
+      <c r="A85" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B85" s="60"/>
-      <c r="C85" s="60"/>
-      <c r="D85" s="60"/>
-      <c r="E85" s="60"/>
-      <c r="F85" s="60"/>
-      <c r="G85" s="60"/>
-      <c r="H85" s="61"/>
+      <c r="B85" s="58"/>
+      <c r="C85" s="58"/>
+      <c r="D85" s="58"/>
+      <c r="E85" s="58"/>
+      <c r="F85" s="58"/>
+      <c r="G85" s="58"/>
+      <c r="H85" s="59"/>
     </row>
     <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
@@ -3410,16 +3389,16 @@
       <c r="H89" s="10"/>
     </row>
     <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="59" t="s">
+      <c r="A90" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B90" s="60"/>
-      <c r="C90" s="60"/>
-      <c r="D90" s="60"/>
-      <c r="E90" s="60"/>
-      <c r="F90" s="60"/>
-      <c r="G90" s="60"/>
-      <c r="H90" s="61"/>
+      <c r="B90" s="58"/>
+      <c r="C90" s="58"/>
+      <c r="D90" s="58"/>
+      <c r="E90" s="58"/>
+      <c r="F90" s="58"/>
+      <c r="G90" s="58"/>
+      <c r="H90" s="59"/>
     </row>
     <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
@@ -3593,16 +3572,16 @@
       </c>
     </row>
     <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="59" t="s">
+      <c r="A97" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B97" s="60"/>
-      <c r="C97" s="60"/>
-      <c r="D97" s="60"/>
-      <c r="E97" s="60"/>
-      <c r="F97" s="60"/>
-      <c r="G97" s="60"/>
-      <c r="H97" s="61"/>
+      <c r="B97" s="58"/>
+      <c r="C97" s="58"/>
+      <c r="D97" s="58"/>
+      <c r="E97" s="58"/>
+      <c r="F97" s="58"/>
+      <c r="G97" s="58"/>
+      <c r="H97" s="59"/>
     </row>
     <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
@@ -3718,16 +3697,16 @@
       <c r="H101" s="10"/>
     </row>
     <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="59" t="s">
+      <c r="A102" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B102" s="60"/>
-      <c r="C102" s="60"/>
-      <c r="D102" s="60"/>
-      <c r="E102" s="60"/>
-      <c r="F102" s="60"/>
-      <c r="G102" s="60"/>
-      <c r="H102" s="61"/>
+      <c r="B102" s="58"/>
+      <c r="C102" s="58"/>
+      <c r="D102" s="58"/>
+      <c r="E102" s="58"/>
+      <c r="F102" s="58"/>
+      <c r="G102" s="58"/>
+      <c r="H102" s="59"/>
     </row>
     <row r="103" spans="1:8" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
@@ -3905,16 +3884,16 @@
       <c r="H108" s="17"/>
     </row>
     <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="59" t="s">
+      <c r="A109" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B109" s="60"/>
-      <c r="C109" s="60"/>
-      <c r="D109" s="60"/>
-      <c r="E109" s="60"/>
-      <c r="F109" s="60"/>
-      <c r="G109" s="60"/>
-      <c r="H109" s="61"/>
+      <c r="B109" s="58"/>
+      <c r="C109" s="58"/>
+      <c r="D109" s="58"/>
+      <c r="E109" s="58"/>
+      <c r="F109" s="58"/>
+      <c r="G109" s="58"/>
+      <c r="H109" s="59"/>
     </row>
     <row r="110" spans="1:8" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
@@ -4088,16 +4067,16 @@
       <c r="H115" s="10"/>
     </row>
     <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="59" t="s">
+      <c r="A116" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B116" s="60"/>
-      <c r="C116" s="60"/>
-      <c r="D116" s="60"/>
-      <c r="E116" s="60"/>
-      <c r="F116" s="60"/>
-      <c r="G116" s="60"/>
-      <c r="H116" s="61"/>
+      <c r="B116" s="58"/>
+      <c r="C116" s="58"/>
+      <c r="D116" s="58"/>
+      <c r="E116" s="58"/>
+      <c r="F116" s="58"/>
+      <c r="G116" s="58"/>
+      <c r="H116" s="59"/>
     </row>
     <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
@@ -4196,16 +4175,16 @@
       <c r="H120" s="10"/>
     </row>
     <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="59" t="s">
+      <c r="A121" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B121" s="60"/>
-      <c r="C121" s="60"/>
-      <c r="D121" s="60"/>
-      <c r="E121" s="60"/>
-      <c r="F121" s="60"/>
-      <c r="G121" s="60"/>
-      <c r="H121" s="61"/>
+      <c r="B121" s="58"/>
+      <c r="C121" s="58"/>
+      <c r="D121" s="58"/>
+      <c r="E121" s="58"/>
+      <c r="F121" s="58"/>
+      <c r="G121" s="58"/>
+      <c r="H121" s="59"/>
     </row>
     <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
@@ -4379,16 +4358,16 @@
       <c r="H127" s="10"/>
     </row>
     <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="59" t="s">
+      <c r="A128" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B128" s="60"/>
-      <c r="C128" s="60"/>
-      <c r="D128" s="60"/>
-      <c r="E128" s="60"/>
-      <c r="F128" s="60"/>
-      <c r="G128" s="60"/>
-      <c r="H128" s="61"/>
+      <c r="B128" s="58"/>
+      <c r="C128" s="58"/>
+      <c r="D128" s="58"/>
+      <c r="E128" s="58"/>
+      <c r="F128" s="58"/>
+      <c r="G128" s="58"/>
+      <c r="H128" s="59"/>
     </row>
     <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
@@ -4507,16 +4486,16 @@
       <c r="H132" s="10"/>
     </row>
     <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="59" t="s">
+      <c r="A133" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B133" s="60"/>
-      <c r="C133" s="60"/>
-      <c r="D133" s="60"/>
-      <c r="E133" s="60"/>
-      <c r="F133" s="60"/>
-      <c r="G133" s="60"/>
-      <c r="H133" s="61"/>
+      <c r="B133" s="58"/>
+      <c r="C133" s="58"/>
+      <c r="D133" s="58"/>
+      <c r="E133" s="58"/>
+      <c r="F133" s="58"/>
+      <c r="G133" s="58"/>
+      <c r="H133" s="59"/>
     </row>
     <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
@@ -4695,16 +4674,16 @@
       </c>
     </row>
     <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="59" t="s">
+      <c r="A140" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B140" s="60"/>
-      <c r="C140" s="60"/>
-      <c r="D140" s="60"/>
-      <c r="E140" s="60"/>
-      <c r="F140" s="60"/>
-      <c r="G140" s="60"/>
-      <c r="H140" s="61"/>
+      <c r="B140" s="58"/>
+      <c r="C140" s="58"/>
+      <c r="D140" s="58"/>
+      <c r="E140" s="58"/>
+      <c r="F140" s="58"/>
+      <c r="G140" s="58"/>
+      <c r="H140" s="59"/>
     </row>
     <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
@@ -4823,16 +4802,16 @@
       <c r="H144" s="10"/>
     </row>
     <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="59" t="s">
+      <c r="A145" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B145" s="60"/>
-      <c r="C145" s="60"/>
-      <c r="D145" s="60"/>
-      <c r="E145" s="65"/>
-      <c r="F145" s="60"/>
-      <c r="G145" s="60"/>
-      <c r="H145" s="61"/>
+      <c r="B145" s="58"/>
+      <c r="C145" s="58"/>
+      <c r="D145" s="58"/>
+      <c r="E145" s="60"/>
+      <c r="F145" s="58"/>
+      <c r="G145" s="58"/>
+      <c r="H145" s="59"/>
     </row>
     <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
@@ -5011,16 +4990,16 @@
       </c>
     </row>
     <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="59" t="s">
+      <c r="A152" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B152" s="60"/>
-      <c r="C152" s="60"/>
-      <c r="D152" s="60"/>
-      <c r="E152" s="65"/>
-      <c r="F152" s="60"/>
-      <c r="G152" s="60"/>
-      <c r="H152" s="61"/>
+      <c r="B152" s="58"/>
+      <c r="C152" s="58"/>
+      <c r="D152" s="58"/>
+      <c r="E152" s="60"/>
+      <c r="F152" s="58"/>
+      <c r="G152" s="58"/>
+      <c r="H152" s="59"/>
     </row>
     <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
@@ -5110,16 +5089,16 @@
       <c r="H155" s="10"/>
     </row>
     <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="59" t="s">
+      <c r="A156" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B156" s="60"/>
-      <c r="C156" s="60"/>
-      <c r="D156" s="60"/>
-      <c r="E156" s="65"/>
-      <c r="F156" s="60"/>
-      <c r="G156" s="60"/>
-      <c r="H156" s="61"/>
+      <c r="B156" s="58"/>
+      <c r="C156" s="58"/>
+      <c r="D156" s="58"/>
+      <c r="E156" s="60"/>
+      <c r="F156" s="58"/>
+      <c r="G156" s="58"/>
+      <c r="H156" s="59"/>
     </row>
     <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
@@ -5272,16 +5251,16 @@
       </c>
     </row>
     <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="59" t="s">
+      <c r="A162" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B162" s="60"/>
-      <c r="C162" s="60"/>
-      <c r="D162" s="60"/>
-      <c r="E162" s="65"/>
-      <c r="F162" s="60"/>
-      <c r="G162" s="60"/>
-      <c r="H162" s="61"/>
+      <c r="B162" s="58"/>
+      <c r="C162" s="58"/>
+      <c r="D162" s="58"/>
+      <c r="E162" s="60"/>
+      <c r="F162" s="58"/>
+      <c r="G162" s="58"/>
+      <c r="H162" s="59"/>
     </row>
     <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
@@ -5376,16 +5355,16 @@
       <c r="H165" s="10"/>
     </row>
     <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="59" t="s">
+      <c r="A166" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B166" s="60"/>
-      <c r="C166" s="60"/>
-      <c r="D166" s="60"/>
-      <c r="E166" s="65"/>
-      <c r="F166" s="60"/>
-      <c r="G166" s="60"/>
-      <c r="H166" s="61"/>
+      <c r="B166" s="58"/>
+      <c r="C166" s="58"/>
+      <c r="D166" s="58"/>
+      <c r="E166" s="60"/>
+      <c r="F166" s="58"/>
+      <c r="G166" s="58"/>
+      <c r="H166" s="59"/>
     </row>
     <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
@@ -5538,16 +5517,16 @@
       </c>
     </row>
     <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="59" t="s">
+      <c r="A172" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B172" s="60"/>
-      <c r="C172" s="60"/>
-      <c r="D172" s="60"/>
-      <c r="E172" s="65"/>
-      <c r="F172" s="60"/>
-      <c r="G172" s="60"/>
-      <c r="H172" s="61"/>
+      <c r="B172" s="58"/>
+      <c r="C172" s="58"/>
+      <c r="D172" s="58"/>
+      <c r="E172" s="60"/>
+      <c r="F172" s="58"/>
+      <c r="G172" s="58"/>
+      <c r="H172" s="59"/>
     </row>
     <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
@@ -5642,16 +5621,16 @@
       <c r="H175" s="10"/>
     </row>
     <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="59" t="s">
+      <c r="A176" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B176" s="60"/>
-      <c r="C176" s="60"/>
-      <c r="D176" s="60"/>
-      <c r="E176" s="65"/>
-      <c r="F176" s="60"/>
-      <c r="G176" s="60"/>
-      <c r="H176" s="61"/>
+      <c r="B176" s="58"/>
+      <c r="C176" s="58"/>
+      <c r="D176" s="58"/>
+      <c r="E176" s="60"/>
+      <c r="F176" s="58"/>
+      <c r="G176" s="58"/>
+      <c r="H176" s="59"/>
     </row>
     <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
@@ -5805,16 +5784,16 @@
       </c>
     </row>
     <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="59" t="s">
+      <c r="A182" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B182" s="60"/>
-      <c r="C182" s="60"/>
-      <c r="D182" s="60"/>
-      <c r="E182" s="65"/>
-      <c r="F182" s="60"/>
-      <c r="G182" s="60"/>
-      <c r="H182" s="61"/>
+      <c r="B182" s="58"/>
+      <c r="C182" s="58"/>
+      <c r="D182" s="58"/>
+      <c r="E182" s="60"/>
+      <c r="F182" s="58"/>
+      <c r="G182" s="58"/>
+      <c r="H182" s="59"/>
     </row>
     <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
@@ -5906,16 +5885,16 @@
       <c r="H185" s="10"/>
     </row>
     <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="59" t="s">
+      <c r="A186" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B186" s="60"/>
-      <c r="C186" s="60"/>
-      <c r="D186" s="60"/>
-      <c r="E186" s="65"/>
-      <c r="F186" s="60"/>
-      <c r="G186" s="60"/>
-      <c r="H186" s="61"/>
+      <c r="B186" s="58"/>
+      <c r="C186" s="58"/>
+      <c r="D186" s="58"/>
+      <c r="E186" s="60"/>
+      <c r="F186" s="58"/>
+      <c r="G186" s="58"/>
+      <c r="H186" s="59"/>
     </row>
     <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
@@ -6067,16 +6046,16 @@
       </c>
     </row>
     <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="59" t="s">
+      <c r="A192" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B192" s="60"/>
-      <c r="C192" s="60"/>
-      <c r="D192" s="60"/>
-      <c r="E192" s="65"/>
-      <c r="F192" s="60"/>
-      <c r="G192" s="60"/>
-      <c r="H192" s="61"/>
+      <c r="B192" s="58"/>
+      <c r="C192" s="58"/>
+      <c r="D192" s="58"/>
+      <c r="E192" s="60"/>
+      <c r="F192" s="58"/>
+      <c r="G192" s="58"/>
+      <c r="H192" s="59"/>
     </row>
     <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
@@ -6171,16 +6150,16 @@
       <c r="H195" s="10"/>
     </row>
     <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="59" t="s">
+      <c r="A196" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B196" s="60"/>
-      <c r="C196" s="60"/>
-      <c r="D196" s="60"/>
-      <c r="E196" s="65"/>
-      <c r="F196" s="60"/>
-      <c r="G196" s="60"/>
-      <c r="H196" s="61"/>
+      <c r="B196" s="58"/>
+      <c r="C196" s="58"/>
+      <c r="D196" s="58"/>
+      <c r="E196" s="60"/>
+      <c r="F196" s="58"/>
+      <c r="G196" s="58"/>
+      <c r="H196" s="59"/>
     </row>
     <row r="197" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
@@ -6331,16 +6310,16 @@
       <c r="H201" s="30"/>
     </row>
     <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="59" t="s">
+      <c r="A202" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B202" s="60"/>
-      <c r="C202" s="60"/>
-      <c r="D202" s="60"/>
-      <c r="E202" s="65"/>
-      <c r="F202" s="60"/>
-      <c r="G202" s="60"/>
-      <c r="H202" s="61"/>
+      <c r="B202" s="58"/>
+      <c r="C202" s="58"/>
+      <c r="D202" s="58"/>
+      <c r="E202" s="60"/>
+      <c r="F202" s="58"/>
+      <c r="G202" s="58"/>
+      <c r="H202" s="59"/>
     </row>
     <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
@@ -6459,16 +6438,16 @@
       <c r="H206" s="10"/>
     </row>
     <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="59" t="s">
+      <c r="A207" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B207" s="60"/>
-      <c r="C207" s="60"/>
-      <c r="D207" s="60"/>
-      <c r="E207" s="65"/>
-      <c r="F207" s="60"/>
-      <c r="G207" s="60"/>
-      <c r="H207" s="61"/>
+      <c r="B207" s="58"/>
+      <c r="C207" s="58"/>
+      <c r="D207" s="58"/>
+      <c r="E207" s="60"/>
+      <c r="F207" s="58"/>
+      <c r="G207" s="58"/>
+      <c r="H207" s="59"/>
     </row>
     <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
@@ -6562,16 +6541,16 @@
       </c>
     </row>
     <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="59" t="s">
+      <c r="A211" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B211" s="60"/>
-      <c r="C211" s="60"/>
-      <c r="D211" s="60"/>
-      <c r="E211" s="65"/>
-      <c r="F211" s="60"/>
-      <c r="G211" s="60"/>
-      <c r="H211" s="61"/>
+      <c r="B211" s="58"/>
+      <c r="C211" s="58"/>
+      <c r="D211" s="58"/>
+      <c r="E211" s="60"/>
+      <c r="F211" s="58"/>
+      <c r="G211" s="58"/>
+      <c r="H211" s="59"/>
     </row>
     <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
@@ -6699,16 +6678,16 @@
       <c r="H216" s="30"/>
     </row>
     <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="59" t="s">
+      <c r="A217" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B217" s="60"/>
-      <c r="C217" s="60"/>
-      <c r="D217" s="60"/>
-      <c r="E217" s="65"/>
-      <c r="F217" s="60"/>
-      <c r="G217" s="60"/>
-      <c r="H217" s="61"/>
+      <c r="B217" s="58"/>
+      <c r="C217" s="58"/>
+      <c r="D217" s="58"/>
+      <c r="E217" s="60"/>
+      <c r="F217" s="58"/>
+      <c r="G217" s="58"/>
+      <c r="H217" s="59"/>
     </row>
     <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
@@ -6800,16 +6779,16 @@
       </c>
     </row>
     <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="59" t="s">
+      <c r="A221" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B221" s="60"/>
-      <c r="C221" s="60"/>
-      <c r="D221" s="60"/>
-      <c r="E221" s="65"/>
-      <c r="F221" s="60"/>
-      <c r="G221" s="60"/>
-      <c r="H221" s="61"/>
+      <c r="B221" s="58"/>
+      <c r="C221" s="58"/>
+      <c r="D221" s="58"/>
+      <c r="E221" s="60"/>
+      <c r="F221" s="58"/>
+      <c r="G221" s="58"/>
+      <c r="H221" s="59"/>
     </row>
     <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
@@ -6953,16 +6932,16 @@
       <c r="H226" s="30"/>
     </row>
     <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="59" t="s">
+      <c r="A227" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B227" s="60"/>
-      <c r="C227" s="60"/>
-      <c r="D227" s="60"/>
-      <c r="E227" s="65"/>
-      <c r="F227" s="60"/>
-      <c r="G227" s="60"/>
-      <c r="H227" s="61"/>
+      <c r="B227" s="58"/>
+      <c r="C227" s="58"/>
+      <c r="D227" s="58"/>
+      <c r="E227" s="60"/>
+      <c r="F227" s="58"/>
+      <c r="G227" s="58"/>
+      <c r="H227" s="59"/>
     </row>
     <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
@@ -7056,16 +7035,16 @@
       </c>
     </row>
     <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="59" t="s">
+      <c r="A231" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B231" s="60"/>
-      <c r="C231" s="60"/>
-      <c r="D231" s="60"/>
-      <c r="E231" s="65"/>
-      <c r="F231" s="60"/>
-      <c r="G231" s="60"/>
-      <c r="H231" s="61"/>
+      <c r="B231" s="58"/>
+      <c r="C231" s="58"/>
+      <c r="D231" s="58"/>
+      <c r="E231" s="60"/>
+      <c r="F231" s="58"/>
+      <c r="G231" s="58"/>
+      <c r="H231" s="59"/>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
@@ -7182,11 +7161,11 @@
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A236" s="2">
+      <c r="A236" s="39">
         <f>MAX(A225:A235)+1</f>
         <v>189</v>
       </c>
-      <c r="B236" s="9" t="s">
+      <c r="B236" s="38" t="s">
         <v>26</v>
       </c>
       <c r="C236" s="36">
@@ -7199,28 +7178,28 @@
       <c r="E236" s="37">
         <v>1287</v>
       </c>
-      <c r="F236" s="34">
+      <c r="F236" s="36">
         <v>46016</v>
       </c>
-      <c r="G236" s="34">
+      <c r="G236" s="36">
         <v>46016</v>
       </c>
-      <c r="H236" s="44" t="s">
+      <c r="H236" s="43" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A237" s="59"/>
-      <c r="B237" s="60"/>
-      <c r="C237" s="60"/>
-      <c r="D237" s="60"/>
-      <c r="E237" s="60"/>
-      <c r="F237" s="60"/>
-      <c r="G237" s="60"/>
-      <c r="H237" s="61"/>
+      <c r="A237" s="61"/>
+      <c r="B237" s="62"/>
+      <c r="C237" s="62"/>
+      <c r="D237" s="62"/>
+      <c r="E237" s="62"/>
+      <c r="F237" s="62"/>
+      <c r="G237" s="62"/>
+      <c r="H237" s="64"/>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A238" s="40">
+      <c r="A238" s="39">
         <f>MAX(A226:A237)+1</f>
         <v>190</v>
       </c>
@@ -7237,13 +7216,13 @@
       <c r="E238" s="37">
         <v>2870</v>
       </c>
-      <c r="F238" s="34">
+      <c r="F238" s="36">
         <v>46017</v>
       </c>
-      <c r="G238" s="34">
+      <c r="G238" s="36">
         <v>46017</v>
       </c>
-      <c r="H238" s="45" t="s">
+      <c r="H238" s="43" t="s">
         <v>70</v>
       </c>
     </row>
@@ -7272,12 +7251,12 @@
         <f t="shared" si="261"/>
         <v>46016</v>
       </c>
-      <c r="H239" s="43" t="s">
+      <c r="H239" s="42" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="240" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A240" s="40">
+      <c r="A240" s="39">
         <f>MAX(A228:A239)+1</f>
         <v>192</v>
       </c>
@@ -7303,22 +7282,22 @@
         <f t="shared" si="263"/>
         <v/>
       </c>
-      <c r="H240" s="41" t="s">
+      <c r="H240" s="40" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A241" s="66"/>
-      <c r="B241" s="67"/>
-      <c r="C241" s="67"/>
-      <c r="D241" s="67"/>
-      <c r="E241" s="68"/>
-      <c r="F241" s="67"/>
-      <c r="G241" s="67"/>
-      <c r="H241" s="69"/>
+      <c r="A241" s="61"/>
+      <c r="B241" s="62"/>
+      <c r="C241" s="62"/>
+      <c r="D241" s="62"/>
+      <c r="E241" s="63"/>
+      <c r="F241" s="62"/>
+      <c r="G241" s="62"/>
+      <c r="H241" s="64"/>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A242" s="40">
+      <c r="A242" s="39">
         <f>MAX(A232:A241)+1</f>
         <v>193</v>
       </c>
@@ -7328,19 +7307,19 @@
       <c r="C242" s="36">
         <v>46013</v>
       </c>
-      <c r="D242" s="42">
+      <c r="D242" s="41">
         <v>46015</v>
       </c>
       <c r="E242" s="37">
         <v>8039</v>
       </c>
-      <c r="F242" s="34">
+      <c r="F242" s="36">
         <v>46020</v>
       </c>
-      <c r="G242" s="34">
+      <c r="G242" s="36">
         <v>46020</v>
       </c>
-      <c r="H242" s="45" t="s">
+      <c r="H242" s="43" t="s">
         <v>74</v>
       </c>
     </row>
@@ -7366,67 +7345,67 @@
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A244" s="2">
+      <c r="A244" s="39">
         <f>MAX(A235:A243)+1</f>
         <v>195</v>
       </c>
-      <c r="B244" s="9" t="s">
+      <c r="B244" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C244" s="31">
+      <c r="C244" s="36">
         <f>IFERROR(IF(C236,C236+14,""),"")</f>
         <v>46016</v>
       </c>
-      <c r="D244" s="31">
+      <c r="D244" s="36">
         <v>46017</v>
       </c>
       <c r="E244" s="37">
         <v>3133</v>
       </c>
-      <c r="F244" s="39">
+      <c r="F244" s="36">
         <v>46034</v>
       </c>
-      <c r="G244" s="39">
+      <c r="G244" s="36">
         <v>46034</v>
       </c>
-      <c r="H244" s="10"/>
+      <c r="H244" s="40"/>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A245" s="59"/>
-      <c r="B245" s="60"/>
-      <c r="C245" s="60"/>
-      <c r="D245" s="60"/>
-      <c r="E245" s="60"/>
-      <c r="F245" s="60"/>
-      <c r="G245" s="60"/>
-      <c r="H245" s="61"/>
+      <c r="A245" s="61"/>
+      <c r="B245" s="62"/>
+      <c r="C245" s="62"/>
+      <c r="D245" s="62"/>
+      <c r="E245" s="62"/>
+      <c r="F245" s="62"/>
+      <c r="G245" s="62"/>
+      <c r="H245" s="64"/>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A246" s="2">
+      <c r="A246" s="39">
         <f>MAX(A235:A245)+1</f>
         <v>196</v>
       </c>
-      <c r="B246" s="9" t="s">
+      <c r="B246" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C246" s="52">
+      <c r="C246" s="78">
         <v>46020</v>
       </c>
-      <c r="D246" s="31">
+      <c r="D246" s="36">
         <v>46027</v>
       </c>
       <c r="E246" s="37">
         <f>4728+2633</f>
         <v>7361</v>
       </c>
-      <c r="F246" s="39">
+      <c r="F246" s="36">
         <v>46034</v>
       </c>
-      <c r="G246" s="39">
+      <c r="G246" s="36">
         <v>46034</v>
       </c>
-      <c r="H246" s="83" t="s">
-        <v>80</v>
+      <c r="H246" s="56" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
@@ -7437,8 +7416,8 @@
       <c r="B247" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C247" s="53" t="s">
-        <v>78</v>
+      <c r="C247" s="50" t="s">
+        <v>75</v>
       </c>
       <c r="D247" s="36">
         <v>46027</v>
@@ -7452,42 +7431,42 @@
       <c r="G247" s="36">
         <v>46035</v>
       </c>
-      <c r="H247" s="45"/>
+      <c r="H247" s="43"/>
     </row>
     <row r="248" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A248" s="54">
+      <c r="A248" s="51">
         <f>MAX(A236:A247)+1</f>
         <v>198</v>
       </c>
-      <c r="B248" s="55" t="s">
+      <c r="B248" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="C248" s="56">
+      <c r="C248" s="53">
         <v>46030</v>
       </c>
-      <c r="D248" s="56">
+      <c r="D248" s="53">
         <v>46031</v>
       </c>
-      <c r="E248" s="57"/>
-      <c r="F248" s="56">
+      <c r="E248" s="54"/>
+      <c r="F248" s="53">
         <v>46036</v>
       </c>
-      <c r="G248" s="56">
+      <c r="G248" s="53">
         <v>46037</v>
       </c>
-      <c r="H248" s="58" t="s">
-        <v>79</v>
+      <c r="H248" s="55" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A249" s="59"/>
-      <c r="B249" s="60"/>
-      <c r="C249" s="60"/>
-      <c r="D249" s="60"/>
-      <c r="E249" s="60"/>
-      <c r="F249" s="60"/>
-      <c r="G249" s="60"/>
-      <c r="H249" s="61"/>
+      <c r="A249" s="57"/>
+      <c r="B249" s="58"/>
+      <c r="C249" s="58"/>
+      <c r="D249" s="58"/>
+      <c r="E249" s="58"/>
+      <c r="F249" s="58"/>
+      <c r="G249" s="58"/>
+      <c r="H249" s="59"/>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
@@ -7497,22 +7476,24 @@
       <c r="B250" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C250" s="39">
+      <c r="C250" s="36">
         <v>46034</v>
       </c>
-      <c r="D250" s="39">
+      <c r="D250" s="36">
         <v>46035</v>
       </c>
-      <c r="E250" s="37"/>
-      <c r="F250" s="39">
+      <c r="E250" s="37">
+        <v>2943</v>
+      </c>
+      <c r="F250" s="36">
         <v>46042</v>
       </c>
-      <c r="G250" s="39">
+      <c r="G250" s="36">
         <v>46042</v>
       </c>
       <c r="H250" s="10"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
         <f t="shared" ref="A251:A254" si="264">MAX(A239:A250)+1</f>
         <v>200</v>
@@ -7520,20 +7501,24 @@
       <c r="B251" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="C251" s="39">
-        <v>46031</v>
-      </c>
-      <c r="D251" s="39">
+      <c r="C251" s="36">
         <v>46034</v>
       </c>
-      <c r="E251" s="37"/>
-      <c r="F251" s="39">
-        <v>46041</v>
-      </c>
-      <c r="G251" s="39">
-        <v>46041</v>
-      </c>
-      <c r="H251" s="17"/>
+      <c r="D251" s="36">
+        <v>46035</v>
+      </c>
+      <c r="E251" s="37">
+        <v>2085</v>
+      </c>
+      <c r="F251" s="36">
+        <v>46048</v>
+      </c>
+      <c r="G251" s="36">
+        <v>46048</v>
+      </c>
+      <c r="H251" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="252" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
@@ -7546,10 +7531,12 @@
       <c r="C252" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D252" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="E252" s="37"/>
+      <c r="D252" s="36">
+        <v>46035</v>
+      </c>
+      <c r="E252" s="37">
+        <v>1307</v>
+      </c>
       <c r="F252" s="36"/>
       <c r="G252" s="36"/>
       <c r="H252" s="10" t="s">
@@ -7564,17 +7551,17 @@
       <c r="B253" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C253" s="39">
+      <c r="C253" s="36">
         <v>46037</v>
       </c>
-      <c r="D253" s="39">
+      <c r="D253" s="36">
         <v>46038</v>
       </c>
-      <c r="E253" s="4"/>
-      <c r="F253" s="39">
+      <c r="E253" s="37"/>
+      <c r="F253" s="36">
         <v>46043</v>
       </c>
-      <c r="G253" s="39">
+      <c r="G253" s="36">
         <v>46044</v>
       </c>
       <c r="H253" s="10"/>
@@ -7587,56 +7574,22 @@
       <c r="B254" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C254" s="39">
-        <v>46037</v>
-      </c>
-      <c r="D254" s="39">
-        <v>46038</v>
-      </c>
-      <c r="E254" s="37"/>
-      <c r="F254" s="39">
-        <v>46048</v>
-      </c>
-      <c r="G254" s="39">
-        <v>46048</v>
+      <c r="C254" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="D254" s="36">
+        <v>46036</v>
+      </c>
+      <c r="E254" s="37">
+        <v>1247</v>
+      </c>
+      <c r="F254" s="36">
+        <v>46041</v>
+      </c>
+      <c r="G254" s="36">
+        <v>46041</v>
       </c>
       <c r="H254" s="10"/>
-    </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A256" s="62" t="s">
-        <v>75</v>
-      </c>
-      <c r="B256" s="62"/>
-      <c r="C256" s="62"/>
-      <c r="D256" s="62"/>
-      <c r="E256" s="62"/>
-      <c r="F256" s="62"/>
-      <c r="G256" s="62"/>
-      <c r="H256" s="62"/>
-    </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A257" s="63" t="s">
-        <v>76</v>
-      </c>
-      <c r="B257" s="63"/>
-      <c r="C257" s="63"/>
-      <c r="D257" s="63"/>
-      <c r="E257" s="63"/>
-      <c r="F257" s="63"/>
-      <c r="G257" s="63"/>
-      <c r="H257" s="63"/>
-    </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A258" s="64" t="s">
-        <v>77</v>
-      </c>
-      <c r="B258" s="64"/>
-      <c r="C258" s="64"/>
-      <c r="D258" s="64"/>
-      <c r="E258" s="64"/>
-      <c r="F258" s="64"/>
-      <c r="G258" s="64"/>
-      <c r="H258" s="64"/>
     </row>
   </sheetData>
   <autoFilter ref="A8:H236" xr:uid="{9D5F3532-A341-428E-AFDB-DF9AAA83E1F5}">
@@ -7650,7 +7603,7 @@
       </filters>
     </filterColumn>
   </autoFilter>
-  <mergeCells count="50">
+  <mergeCells count="47">
     <mergeCell ref="A207:H207"/>
     <mergeCell ref="A73:H73"/>
     <mergeCell ref="A156:H156"/>
@@ -7686,9 +7639,6 @@
     <mergeCell ref="A121:H121"/>
     <mergeCell ref="A102:H102"/>
     <mergeCell ref="A249:H249"/>
-    <mergeCell ref="A256:H256"/>
-    <mergeCell ref="A257:H257"/>
-    <mergeCell ref="A258:H258"/>
     <mergeCell ref="A152:H152"/>
     <mergeCell ref="A202:H202"/>
     <mergeCell ref="A245:H245"/>
@@ -7703,6 +7653,6 @@
     <mergeCell ref="A227:H227"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="93" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="90" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/графики/график Ташкент.xlsx
+++ b/графики/график Ташкент.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66C2EA8-8CDE-48B6-B50B-3C38D911E32E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D5AE2A-A185-4B18-A766-21F298B11173}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$8:$H$236</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$8:$H$244</definedName>
   </definedNames>
   <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="80">
   <si>
     <t>Контракт</t>
   </si>
@@ -334,6 +334,9 @@
   </si>
   <si>
     <t>Шувалова перенсла погрузку с 19,01 на 26,01</t>
+  </si>
+  <si>
+    <t>отмена + перенос на следующую неделю (Шувалова)</t>
   </si>
 </sst>
 </file>
@@ -634,7 +637,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -802,29 +805,29 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -856,16 +859,19 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1151,7 +1157,7 @@
   <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H254"/>
+  <dimension ref="A1:H259"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="3" customWidth="1"/>
@@ -1255,10 +1261,10 @@
         <v>9</v>
       </c>
       <c r="E5" s="46"/>
-      <c r="F5" s="76" t="s">
+      <c r="F5" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="77"/>
+      <c r="G5" s="64"/>
       <c r="H5" s="73"/>
     </row>
     <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
@@ -1440,16 +1446,16 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="57" t="s">
+      <c r="A14" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="59"/>
+      <c r="B14" s="59"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="61"/>
     </row>
     <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -1593,16 +1599,16 @@
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
       <c r="E20" s="60"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="75"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="62"/>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -1745,16 +1751,16 @@
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="57" t="s">
+      <c r="A26" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
       <c r="E26" s="60"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="75"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="62"/>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -1955,16 +1961,16 @@
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="57" t="s">
+      <c r="A34" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="58"/>
-      <c r="C34" s="58"/>
-      <c r="D34" s="58"/>
+      <c r="B34" s="59"/>
+      <c r="C34" s="59"/>
+      <c r="D34" s="59"/>
       <c r="E34" s="60"/>
-      <c r="F34" s="58"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="75"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="62"/>
     </row>
     <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -2149,16 +2155,16 @@
       </c>
     </row>
     <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="57" t="s">
+      <c r="A41" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="58"/>
-      <c r="C41" s="58"/>
-      <c r="D41" s="58"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="59"/>
       <c r="E41" s="60"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="75"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="62"/>
     </row>
     <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
@@ -2360,16 +2366,16 @@
       <c r="H48" s="12"/>
     </row>
     <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="57" t="s">
+      <c r="A49" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B49" s="58"/>
-      <c r="C49" s="58"/>
-      <c r="D49" s="58"/>
+      <c r="B49" s="59"/>
+      <c r="C49" s="59"/>
+      <c r="D49" s="59"/>
       <c r="E49" s="60"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="58"/>
-      <c r="H49" s="75"/>
+      <c r="F49" s="59"/>
+      <c r="G49" s="59"/>
+      <c r="H49" s="62"/>
     </row>
     <row r="50" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
@@ -2484,16 +2490,16 @@
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="57" t="s">
+      <c r="A54" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B54" s="58"/>
-      <c r="C54" s="58"/>
-      <c r="D54" s="58"/>
+      <c r="B54" s="59"/>
+      <c r="C54" s="59"/>
+      <c r="D54" s="59"/>
       <c r="E54" s="60"/>
-      <c r="F54" s="58"/>
-      <c r="G54" s="58"/>
-      <c r="H54" s="75"/>
+      <c r="F54" s="59"/>
+      <c r="G54" s="59"/>
+      <c r="H54" s="62"/>
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
@@ -2642,16 +2648,16 @@
       </c>
     </row>
     <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="57" t="s">
+      <c r="A61" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B61" s="58"/>
-      <c r="C61" s="58"/>
-      <c r="D61" s="58"/>
-      <c r="E61" s="58"/>
-      <c r="F61" s="58"/>
-      <c r="G61" s="58"/>
-      <c r="H61" s="59"/>
+      <c r="B61" s="59"/>
+      <c r="C61" s="59"/>
+      <c r="D61" s="59"/>
+      <c r="E61" s="59"/>
+      <c r="F61" s="59"/>
+      <c r="G61" s="59"/>
+      <c r="H61" s="61"/>
     </row>
     <row r="62" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
@@ -2766,16 +2772,16 @@
       <c r="H65" s="10"/>
     </row>
     <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="57" t="s">
+      <c r="A66" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B66" s="58"/>
-      <c r="C66" s="58"/>
-      <c r="D66" s="58"/>
-      <c r="E66" s="58"/>
-      <c r="F66" s="58"/>
-      <c r="G66" s="58"/>
-      <c r="H66" s="59"/>
+      <c r="B66" s="59"/>
+      <c r="C66" s="59"/>
+      <c r="D66" s="59"/>
+      <c r="E66" s="59"/>
+      <c r="F66" s="59"/>
+      <c r="G66" s="59"/>
+      <c r="H66" s="61"/>
     </row>
     <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
@@ -2950,16 +2956,16 @@
       </c>
     </row>
     <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="57" t="s">
+      <c r="A73" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B73" s="58"/>
-      <c r="C73" s="58"/>
-      <c r="D73" s="58"/>
-      <c r="E73" s="58"/>
-      <c r="F73" s="58"/>
-      <c r="G73" s="58"/>
-      <c r="H73" s="59"/>
+      <c r="B73" s="59"/>
+      <c r="C73" s="59"/>
+      <c r="D73" s="59"/>
+      <c r="E73" s="59"/>
+      <c r="F73" s="59"/>
+      <c r="G73" s="59"/>
+      <c r="H73" s="61"/>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
@@ -3078,16 +3084,16 @@
       <c r="H77" s="10"/>
     </row>
     <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="57" t="s">
+      <c r="A78" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B78" s="58"/>
-      <c r="C78" s="58"/>
-      <c r="D78" s="58"/>
-      <c r="E78" s="58"/>
-      <c r="F78" s="58"/>
-      <c r="G78" s="58"/>
-      <c r="H78" s="59"/>
+      <c r="B78" s="59"/>
+      <c r="C78" s="59"/>
+      <c r="D78" s="59"/>
+      <c r="E78" s="59"/>
+      <c r="F78" s="59"/>
+      <c r="G78" s="59"/>
+      <c r="H78" s="61"/>
     </row>
     <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
@@ -3262,16 +3268,16 @@
       </c>
     </row>
     <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="57" t="s">
+      <c r="A85" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B85" s="58"/>
-      <c r="C85" s="58"/>
-      <c r="D85" s="58"/>
-      <c r="E85" s="58"/>
-      <c r="F85" s="58"/>
-      <c r="G85" s="58"/>
-      <c r="H85" s="59"/>
+      <c r="B85" s="59"/>
+      <c r="C85" s="59"/>
+      <c r="D85" s="59"/>
+      <c r="E85" s="59"/>
+      <c r="F85" s="59"/>
+      <c r="G85" s="59"/>
+      <c r="H85" s="61"/>
     </row>
     <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
@@ -3389,16 +3395,16 @@
       <c r="H89" s="10"/>
     </row>
     <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="57" t="s">
+      <c r="A90" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B90" s="58"/>
-      <c r="C90" s="58"/>
-      <c r="D90" s="58"/>
-      <c r="E90" s="58"/>
-      <c r="F90" s="58"/>
-      <c r="G90" s="58"/>
-      <c r="H90" s="59"/>
+      <c r="B90" s="59"/>
+      <c r="C90" s="59"/>
+      <c r="D90" s="59"/>
+      <c r="E90" s="59"/>
+      <c r="F90" s="59"/>
+      <c r="G90" s="59"/>
+      <c r="H90" s="61"/>
     </row>
     <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
@@ -3572,16 +3578,16 @@
       </c>
     </row>
     <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="57" t="s">
+      <c r="A97" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B97" s="58"/>
-      <c r="C97" s="58"/>
-      <c r="D97" s="58"/>
-      <c r="E97" s="58"/>
-      <c r="F97" s="58"/>
-      <c r="G97" s="58"/>
-      <c r="H97" s="59"/>
+      <c r="B97" s="59"/>
+      <c r="C97" s="59"/>
+      <c r="D97" s="59"/>
+      <c r="E97" s="59"/>
+      <c r="F97" s="59"/>
+      <c r="G97" s="59"/>
+      <c r="H97" s="61"/>
     </row>
     <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
@@ -3697,16 +3703,16 @@
       <c r="H101" s="10"/>
     </row>
     <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="57" t="s">
+      <c r="A102" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B102" s="58"/>
-      <c r="C102" s="58"/>
-      <c r="D102" s="58"/>
-      <c r="E102" s="58"/>
-      <c r="F102" s="58"/>
-      <c r="G102" s="58"/>
-      <c r="H102" s="59"/>
+      <c r="B102" s="59"/>
+      <c r="C102" s="59"/>
+      <c r="D102" s="59"/>
+      <c r="E102" s="59"/>
+      <c r="F102" s="59"/>
+      <c r="G102" s="59"/>
+      <c r="H102" s="61"/>
     </row>
     <row r="103" spans="1:8" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
@@ -3884,16 +3890,16 @@
       <c r="H108" s="17"/>
     </row>
     <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="57" t="s">
+      <c r="A109" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B109" s="58"/>
-      <c r="C109" s="58"/>
-      <c r="D109" s="58"/>
-      <c r="E109" s="58"/>
-      <c r="F109" s="58"/>
-      <c r="G109" s="58"/>
-      <c r="H109" s="59"/>
+      <c r="B109" s="59"/>
+      <c r="C109" s="59"/>
+      <c r="D109" s="59"/>
+      <c r="E109" s="59"/>
+      <c r="F109" s="59"/>
+      <c r="G109" s="59"/>
+      <c r="H109" s="61"/>
     </row>
     <row r="110" spans="1:8" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
@@ -4067,16 +4073,16 @@
       <c r="H115" s="10"/>
     </row>
     <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="57" t="s">
+      <c r="A116" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B116" s="58"/>
-      <c r="C116" s="58"/>
-      <c r="D116" s="58"/>
-      <c r="E116" s="58"/>
-      <c r="F116" s="58"/>
-      <c r="G116" s="58"/>
-      <c r="H116" s="59"/>
+      <c r="B116" s="59"/>
+      <c r="C116" s="59"/>
+      <c r="D116" s="59"/>
+      <c r="E116" s="59"/>
+      <c r="F116" s="59"/>
+      <c r="G116" s="59"/>
+      <c r="H116" s="61"/>
     </row>
     <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
@@ -4175,16 +4181,16 @@
       <c r="H120" s="10"/>
     </row>
     <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="57" t="s">
+      <c r="A121" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B121" s="58"/>
-      <c r="C121" s="58"/>
-      <c r="D121" s="58"/>
-      <c r="E121" s="58"/>
-      <c r="F121" s="58"/>
-      <c r="G121" s="58"/>
-      <c r="H121" s="59"/>
+      <c r="B121" s="59"/>
+      <c r="C121" s="59"/>
+      <c r="D121" s="59"/>
+      <c r="E121" s="59"/>
+      <c r="F121" s="59"/>
+      <c r="G121" s="59"/>
+      <c r="H121" s="61"/>
     </row>
     <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
@@ -4358,16 +4364,16 @@
       <c r="H127" s="10"/>
     </row>
     <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="57" t="s">
+      <c r="A128" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B128" s="58"/>
-      <c r="C128" s="58"/>
-      <c r="D128" s="58"/>
-      <c r="E128" s="58"/>
-      <c r="F128" s="58"/>
-      <c r="G128" s="58"/>
-      <c r="H128" s="59"/>
+      <c r="B128" s="59"/>
+      <c r="C128" s="59"/>
+      <c r="D128" s="59"/>
+      <c r="E128" s="59"/>
+      <c r="F128" s="59"/>
+      <c r="G128" s="59"/>
+      <c r="H128" s="61"/>
     </row>
     <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
@@ -4486,16 +4492,16 @@
       <c r="H132" s="10"/>
     </row>
     <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="57" t="s">
+      <c r="A133" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B133" s="58"/>
-      <c r="C133" s="58"/>
-      <c r="D133" s="58"/>
-      <c r="E133" s="58"/>
-      <c r="F133" s="58"/>
-      <c r="G133" s="58"/>
-      <c r="H133" s="59"/>
+      <c r="B133" s="59"/>
+      <c r="C133" s="59"/>
+      <c r="D133" s="59"/>
+      <c r="E133" s="59"/>
+      <c r="F133" s="59"/>
+      <c r="G133" s="59"/>
+      <c r="H133" s="61"/>
     </row>
     <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
@@ -4674,16 +4680,16 @@
       </c>
     </row>
     <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="57" t="s">
+      <c r="A140" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B140" s="58"/>
-      <c r="C140" s="58"/>
-      <c r="D140" s="58"/>
-      <c r="E140" s="58"/>
-      <c r="F140" s="58"/>
-      <c r="G140" s="58"/>
-      <c r="H140" s="59"/>
+      <c r="B140" s="59"/>
+      <c r="C140" s="59"/>
+      <c r="D140" s="59"/>
+      <c r="E140" s="59"/>
+      <c r="F140" s="59"/>
+      <c r="G140" s="59"/>
+      <c r="H140" s="61"/>
     </row>
     <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
@@ -4802,16 +4808,16 @@
       <c r="H144" s="10"/>
     </row>
     <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="57" t="s">
+      <c r="A145" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B145" s="58"/>
-      <c r="C145" s="58"/>
-      <c r="D145" s="58"/>
+      <c r="B145" s="59"/>
+      <c r="C145" s="59"/>
+      <c r="D145" s="59"/>
       <c r="E145" s="60"/>
-      <c r="F145" s="58"/>
-      <c r="G145" s="58"/>
-      <c r="H145" s="59"/>
+      <c r="F145" s="59"/>
+      <c r="G145" s="59"/>
+      <c r="H145" s="61"/>
     </row>
     <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
@@ -4990,16 +4996,16 @@
       </c>
     </row>
     <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="57" t="s">
+      <c r="A152" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B152" s="58"/>
-      <c r="C152" s="58"/>
-      <c r="D152" s="58"/>
+      <c r="B152" s="59"/>
+      <c r="C152" s="59"/>
+      <c r="D152" s="59"/>
       <c r="E152" s="60"/>
-      <c r="F152" s="58"/>
-      <c r="G152" s="58"/>
-      <c r="H152" s="59"/>
+      <c r="F152" s="59"/>
+      <c r="G152" s="59"/>
+      <c r="H152" s="61"/>
     </row>
     <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
@@ -5089,16 +5095,16 @@
       <c r="H155" s="10"/>
     </row>
     <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="57" t="s">
+      <c r="A156" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B156" s="58"/>
-      <c r="C156" s="58"/>
-      <c r="D156" s="58"/>
+      <c r="B156" s="59"/>
+      <c r="C156" s="59"/>
+      <c r="D156" s="59"/>
       <c r="E156" s="60"/>
-      <c r="F156" s="58"/>
-      <c r="G156" s="58"/>
-      <c r="H156" s="59"/>
+      <c r="F156" s="59"/>
+      <c r="G156" s="59"/>
+      <c r="H156" s="61"/>
     </row>
     <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
@@ -5251,16 +5257,16 @@
       </c>
     </row>
     <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="57" t="s">
+      <c r="A162" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B162" s="58"/>
-      <c r="C162" s="58"/>
-      <c r="D162" s="58"/>
+      <c r="B162" s="59"/>
+      <c r="C162" s="59"/>
+      <c r="D162" s="59"/>
       <c r="E162" s="60"/>
-      <c r="F162" s="58"/>
-      <c r="G162" s="58"/>
-      <c r="H162" s="59"/>
+      <c r="F162" s="59"/>
+      <c r="G162" s="59"/>
+      <c r="H162" s="61"/>
     </row>
     <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
@@ -5355,16 +5361,16 @@
       <c r="H165" s="10"/>
     </row>
     <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="57" t="s">
+      <c r="A166" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B166" s="58"/>
-      <c r="C166" s="58"/>
-      <c r="D166" s="58"/>
+      <c r="B166" s="59"/>
+      <c r="C166" s="59"/>
+      <c r="D166" s="59"/>
       <c r="E166" s="60"/>
-      <c r="F166" s="58"/>
-      <c r="G166" s="58"/>
-      <c r="H166" s="59"/>
+      <c r="F166" s="59"/>
+      <c r="G166" s="59"/>
+      <c r="H166" s="61"/>
     </row>
     <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
@@ -5517,16 +5523,16 @@
       </c>
     </row>
     <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="57" t="s">
+      <c r="A172" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B172" s="58"/>
-      <c r="C172" s="58"/>
-      <c r="D172" s="58"/>
+      <c r="B172" s="59"/>
+      <c r="C172" s="59"/>
+      <c r="D172" s="59"/>
       <c r="E172" s="60"/>
-      <c r="F172" s="58"/>
-      <c r="G172" s="58"/>
-      <c r="H172" s="59"/>
+      <c r="F172" s="59"/>
+      <c r="G172" s="59"/>
+      <c r="H172" s="61"/>
     </row>
     <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
@@ -5621,16 +5627,16 @@
       <c r="H175" s="10"/>
     </row>
     <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="57" t="s">
+      <c r="A176" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B176" s="58"/>
-      <c r="C176" s="58"/>
-      <c r="D176" s="58"/>
+      <c r="B176" s="59"/>
+      <c r="C176" s="59"/>
+      <c r="D176" s="59"/>
       <c r="E176" s="60"/>
-      <c r="F176" s="58"/>
-      <c r="G176" s="58"/>
-      <c r="H176" s="59"/>
+      <c r="F176" s="59"/>
+      <c r="G176" s="59"/>
+      <c r="H176" s="61"/>
     </row>
     <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
@@ -5784,16 +5790,16 @@
       </c>
     </row>
     <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="57" t="s">
+      <c r="A182" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B182" s="58"/>
-      <c r="C182" s="58"/>
-      <c r="D182" s="58"/>
+      <c r="B182" s="59"/>
+      <c r="C182" s="59"/>
+      <c r="D182" s="59"/>
       <c r="E182" s="60"/>
-      <c r="F182" s="58"/>
-      <c r="G182" s="58"/>
-      <c r="H182" s="59"/>
+      <c r="F182" s="59"/>
+      <c r="G182" s="59"/>
+      <c r="H182" s="61"/>
     </row>
     <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
@@ -5885,16 +5891,16 @@
       <c r="H185" s="10"/>
     </row>
     <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="57" t="s">
+      <c r="A186" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B186" s="58"/>
-      <c r="C186" s="58"/>
-      <c r="D186" s="58"/>
+      <c r="B186" s="59"/>
+      <c r="C186" s="59"/>
+      <c r="D186" s="59"/>
       <c r="E186" s="60"/>
-      <c r="F186" s="58"/>
-      <c r="G186" s="58"/>
-      <c r="H186" s="59"/>
+      <c r="F186" s="59"/>
+      <c r="G186" s="59"/>
+      <c r="H186" s="61"/>
     </row>
     <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
@@ -6046,16 +6052,16 @@
       </c>
     </row>
     <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="57" t="s">
+      <c r="A192" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B192" s="58"/>
-      <c r="C192" s="58"/>
-      <c r="D192" s="58"/>
+      <c r="B192" s="59"/>
+      <c r="C192" s="59"/>
+      <c r="D192" s="59"/>
       <c r="E192" s="60"/>
-      <c r="F192" s="58"/>
-      <c r="G192" s="58"/>
-      <c r="H192" s="59"/>
+      <c r="F192" s="59"/>
+      <c r="G192" s="59"/>
+      <c r="H192" s="61"/>
     </row>
     <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
@@ -6150,16 +6156,16 @@
       <c r="H195" s="10"/>
     </row>
     <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="57" t="s">
+      <c r="A196" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B196" s="58"/>
-      <c r="C196" s="58"/>
-      <c r="D196" s="58"/>
+      <c r="B196" s="59"/>
+      <c r="C196" s="59"/>
+      <c r="D196" s="59"/>
       <c r="E196" s="60"/>
-      <c r="F196" s="58"/>
-      <c r="G196" s="58"/>
-      <c r="H196" s="59"/>
+      <c r="F196" s="59"/>
+      <c r="G196" s="59"/>
+      <c r="H196" s="61"/>
     </row>
     <row r="197" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
@@ -6310,16 +6316,16 @@
       <c r="H201" s="30"/>
     </row>
     <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="57" t="s">
+      <c r="A202" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B202" s="58"/>
-      <c r="C202" s="58"/>
-      <c r="D202" s="58"/>
+      <c r="B202" s="59"/>
+      <c r="C202" s="59"/>
+      <c r="D202" s="59"/>
       <c r="E202" s="60"/>
-      <c r="F202" s="58"/>
-      <c r="G202" s="58"/>
-      <c r="H202" s="59"/>
+      <c r="F202" s="59"/>
+      <c r="G202" s="59"/>
+      <c r="H202" s="61"/>
     </row>
     <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
@@ -6438,16 +6444,16 @@
       <c r="H206" s="10"/>
     </row>
     <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="57" t="s">
+      <c r="A207" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B207" s="58"/>
-      <c r="C207" s="58"/>
-      <c r="D207" s="58"/>
+      <c r="B207" s="59"/>
+      <c r="C207" s="59"/>
+      <c r="D207" s="59"/>
       <c r="E207" s="60"/>
-      <c r="F207" s="58"/>
-      <c r="G207" s="58"/>
-      <c r="H207" s="59"/>
+      <c r="F207" s="59"/>
+      <c r="G207" s="59"/>
+      <c r="H207" s="61"/>
     </row>
     <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
@@ -6541,16 +6547,16 @@
       </c>
     </row>
     <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="57" t="s">
+      <c r="A211" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B211" s="58"/>
-      <c r="C211" s="58"/>
-      <c r="D211" s="58"/>
+      <c r="B211" s="59"/>
+      <c r="C211" s="59"/>
+      <c r="D211" s="59"/>
       <c r="E211" s="60"/>
-      <c r="F211" s="58"/>
-      <c r="G211" s="58"/>
-      <c r="H211" s="59"/>
+      <c r="F211" s="59"/>
+      <c r="G211" s="59"/>
+      <c r="H211" s="61"/>
     </row>
     <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
@@ -6678,16 +6684,16 @@
       <c r="H216" s="30"/>
     </row>
     <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="57" t="s">
+      <c r="A217" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B217" s="58"/>
-      <c r="C217" s="58"/>
-      <c r="D217" s="58"/>
+      <c r="B217" s="59"/>
+      <c r="C217" s="59"/>
+      <c r="D217" s="59"/>
       <c r="E217" s="60"/>
-      <c r="F217" s="58"/>
-      <c r="G217" s="58"/>
-      <c r="H217" s="59"/>
+      <c r="F217" s="59"/>
+      <c r="G217" s="59"/>
+      <c r="H217" s="61"/>
     </row>
     <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
@@ -6779,16 +6785,16 @@
       </c>
     </row>
     <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="57" t="s">
+      <c r="A221" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B221" s="58"/>
-      <c r="C221" s="58"/>
-      <c r="D221" s="58"/>
+      <c r="B221" s="59"/>
+      <c r="C221" s="59"/>
+      <c r="D221" s="59"/>
       <c r="E221" s="60"/>
-      <c r="F221" s="58"/>
-      <c r="G221" s="58"/>
-      <c r="H221" s="59"/>
+      <c r="F221" s="59"/>
+      <c r="G221" s="59"/>
+      <c r="H221" s="61"/>
     </row>
     <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
@@ -6932,16 +6938,16 @@
       <c r="H226" s="30"/>
     </row>
     <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="57" t="s">
+      <c r="A227" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B227" s="58"/>
-      <c r="C227" s="58"/>
-      <c r="D227" s="58"/>
+      <c r="B227" s="59"/>
+      <c r="C227" s="59"/>
+      <c r="D227" s="59"/>
       <c r="E227" s="60"/>
-      <c r="F227" s="58"/>
-      <c r="G227" s="58"/>
-      <c r="H227" s="59"/>
+      <c r="F227" s="59"/>
+      <c r="G227" s="59"/>
+      <c r="H227" s="61"/>
     </row>
     <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
@@ -7035,18 +7041,18 @@
       </c>
     </row>
     <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="57" t="s">
+      <c r="A231" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B231" s="58"/>
-      <c r="C231" s="58"/>
-      <c r="D231" s="58"/>
+      <c r="B231" s="59"/>
+      <c r="C231" s="59"/>
+      <c r="D231" s="59"/>
       <c r="E231" s="60"/>
-      <c r="F231" s="58"/>
-      <c r="G231" s="58"/>
-      <c r="H231" s="59"/>
-    </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F231" s="59"/>
+      <c r="G231" s="59"/>
+      <c r="H231" s="61"/>
+    </row>
+    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
         <f t="shared" ref="A232:A235" si="254">MAX(A220:A231)+1</f>
         <v>185</v>
@@ -7078,7 +7084,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
         <f t="shared" si="254"/>
         <v>186</v>
@@ -7108,7 +7114,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <f t="shared" si="254"/>
         <v>187</v>
@@ -7137,7 +7143,7 @@
       </c>
       <c r="H234" s="10"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
         <f t="shared" si="254"/>
         <v>188</v>
@@ -7160,7 +7166,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="39">
         <f>MAX(A225:A235)+1</f>
         <v>189</v>
@@ -7188,17 +7194,19 @@
         <v>68</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A237" s="61"/>
-      <c r="B237" s="62"/>
-      <c r="C237" s="62"/>
-      <c r="D237" s="62"/>
-      <c r="E237" s="62"/>
-      <c r="F237" s="62"/>
-      <c r="G237" s="62"/>
-      <c r="H237" s="64"/>
-    </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="75" t="s">
+        <v>25</v>
+      </c>
+      <c r="B237" s="76"/>
+      <c r="C237" s="76"/>
+      <c r="D237" s="76"/>
+      <c r="E237" s="76"/>
+      <c r="F237" s="76"/>
+      <c r="G237" s="76"/>
+      <c r="H237" s="77"/>
+    </row>
+    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="39">
         <f>MAX(A226:A237)+1</f>
         <v>190</v>
@@ -7226,7 +7234,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="23">
         <f>MAX(A227:A238)+1</f>
         <v>191</v>
@@ -7255,7 +7263,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="39">
         <f>MAX(A228:A239)+1</f>
         <v>192</v>
@@ -7286,15 +7294,17 @@
         <v>67</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A241" s="61"/>
-      <c r="B241" s="62"/>
-      <c r="C241" s="62"/>
-      <c r="D241" s="62"/>
-      <c r="E241" s="63"/>
-      <c r="F241" s="62"/>
-      <c r="G241" s="62"/>
-      <c r="H241" s="64"/>
+    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A241" s="75" t="s">
+        <v>25</v>
+      </c>
+      <c r="B241" s="76"/>
+      <c r="C241" s="76"/>
+      <c r="D241" s="76"/>
+      <c r="E241" s="78"/>
+      <c r="F241" s="76"/>
+      <c r="G241" s="76"/>
+      <c r="H241" s="77"/>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="39">
@@ -7371,14 +7381,14 @@
       <c r="H244" s="40"/>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A245" s="61"/>
-      <c r="B245" s="62"/>
-      <c r="C245" s="62"/>
-      <c r="D245" s="62"/>
-      <c r="E245" s="62"/>
-      <c r="F245" s="62"/>
-      <c r="G245" s="62"/>
-      <c r="H245" s="64"/>
+      <c r="A245" s="75"/>
+      <c r="B245" s="76"/>
+      <c r="C245" s="76"/>
+      <c r="D245" s="76"/>
+      <c r="E245" s="76"/>
+      <c r="F245" s="76"/>
+      <c r="G245" s="76"/>
+      <c r="H245" s="77"/>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="39">
@@ -7388,7 +7398,7 @@
       <c r="B246" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C246" s="78">
+      <c r="C246" s="57">
         <v>46020</v>
       </c>
       <c r="D246" s="36">
@@ -7459,14 +7469,14 @@
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A249" s="57"/>
-      <c r="B249" s="58"/>
-      <c r="C249" s="58"/>
-      <c r="D249" s="58"/>
-      <c r="E249" s="58"/>
-      <c r="F249" s="58"/>
-      <c r="G249" s="58"/>
-      <c r="H249" s="59"/>
+      <c r="A249" s="58"/>
+      <c r="B249" s="59"/>
+      <c r="C249" s="59"/>
+      <c r="D249" s="59"/>
+      <c r="E249" s="59"/>
+      <c r="F249" s="59"/>
+      <c r="G249" s="59"/>
+      <c r="H249" s="61"/>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
@@ -7510,7 +7520,7 @@
       <c r="E251" s="37">
         <v>2085</v>
       </c>
-      <c r="F251" s="36">
+      <c r="F251" s="15">
         <v>46048</v>
       </c>
       <c r="G251" s="36">
@@ -7557,7 +7567,9 @@
       <c r="D253" s="36">
         <v>46038</v>
       </c>
-      <c r="E253" s="37"/>
+      <c r="E253" s="37">
+        <v>11471</v>
+      </c>
       <c r="F253" s="36">
         <v>46043</v>
       </c>
@@ -7566,44 +7578,174 @@
       </c>
       <c r="H253" s="10"/>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A254" s="2">
+    <row r="254" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A254" s="51">
         <f t="shared" si="264"/>
         <v>203</v>
       </c>
-      <c r="B254" s="9" t="s">
+      <c r="B254" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="C254" s="50" t="s">
+      <c r="C254" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="D254" s="36">
+      <c r="D254" s="53">
         <v>46036</v>
       </c>
-      <c r="E254" s="37">
-        <v>1247</v>
-      </c>
-      <c r="F254" s="36">
+      <c r="E254" s="54"/>
+      <c r="F254" s="53">
         <v>46041</v>
       </c>
-      <c r="G254" s="36">
+      <c r="G254" s="53">
         <v>46041</v>
       </c>
-      <c r="H254" s="10"/>
+      <c r="H254" s="55" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A255" s="58"/>
+      <c r="B255" s="59"/>
+      <c r="C255" s="59"/>
+      <c r="D255" s="59"/>
+      <c r="E255" s="59"/>
+      <c r="F255" s="59"/>
+      <c r="G255" s="59"/>
+      <c r="H255" s="61"/>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A256" s="2">
+        <f>MAX(A244:A255)+1</f>
+        <v>204</v>
+      </c>
+      <c r="B256" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C256" s="36">
+        <v>46041</v>
+      </c>
+      <c r="D256" s="36">
+        <v>46042</v>
+      </c>
+      <c r="E256" s="37"/>
+      <c r="F256" s="36">
+        <v>46042</v>
+      </c>
+      <c r="G256" s="36">
+        <v>46042</v>
+      </c>
+      <c r="H256" s="10"/>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A257" s="2">
+        <f>MAX(A246:A256)+1</f>
+        <v>205</v>
+      </c>
+      <c r="B257" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C257" s="36">
+        <v>46041</v>
+      </c>
+      <c r="D257" s="36">
+        <v>46042</v>
+      </c>
+      <c r="E257" s="37"/>
+      <c r="F257" s="36"/>
+      <c r="G257" s="36"/>
+      <c r="H257" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A258" s="2">
+        <f>MAX(A247:A257)+1</f>
+        <v>206</v>
+      </c>
+      <c r="B258" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C258" s="36">
+        <v>46044</v>
+      </c>
+      <c r="D258" s="36">
+        <v>46045</v>
+      </c>
+      <c r="E258" s="37"/>
+      <c r="F258" s="36">
+        <v>46050</v>
+      </c>
+      <c r="G258" s="36">
+        <v>46051</v>
+      </c>
+      <c r="H258" s="10"/>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A259" s="2">
+        <f>MAX(A248:A258)+1</f>
+        <v>207</v>
+      </c>
+      <c r="B259" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C259" s="36">
+        <v>46044</v>
+      </c>
+      <c r="D259" s="36">
+        <v>46045</v>
+      </c>
+      <c r="E259" s="37"/>
+      <c r="F259" s="36">
+        <v>46055</v>
+      </c>
+      <c r="G259" s="36">
+        <v>46056</v>
+      </c>
+      <c r="H259" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A8:H236" xr:uid="{9D5F3532-A341-428E-AFDB-DF9AAA83E1F5}">
+  <autoFilter ref="A8:H244" xr:uid="{9D5F3532-A341-428E-AFDB-DF9AAA83E1F5}">
     <filterColumn colId="0">
       <filters>
-        <filter val="185"/>
-        <filter val="186"/>
-        <filter val="187"/>
-        <filter val="188"/>
-        <filter val="189"/>
+        <filter val="193"/>
+        <filter val="194"/>
+        <filter val="195"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <mergeCells count="47">
+  <mergeCells count="48">
+    <mergeCell ref="A255:H255"/>
+    <mergeCell ref="A249:H249"/>
+    <mergeCell ref="A152:H152"/>
+    <mergeCell ref="A202:H202"/>
+    <mergeCell ref="A245:H245"/>
+    <mergeCell ref="A241:H241"/>
+    <mergeCell ref="A196:H196"/>
+    <mergeCell ref="A192:H192"/>
+    <mergeCell ref="A221:H221"/>
+    <mergeCell ref="A211:H211"/>
+    <mergeCell ref="A217:H217"/>
+    <mergeCell ref="A237:H237"/>
+    <mergeCell ref="A231:H231"/>
+    <mergeCell ref="A227:H227"/>
+    <mergeCell ref="A116:H116"/>
+    <mergeCell ref="A145:H145"/>
+    <mergeCell ref="A97:H97"/>
+    <mergeCell ref="A121:H121"/>
+    <mergeCell ref="A102:H102"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A34:H34"/>
     <mergeCell ref="A207:H207"/>
     <mergeCell ref="A73:H73"/>
     <mergeCell ref="A156:H156"/>
@@ -7620,37 +7762,6 @@
     <mergeCell ref="A109:H109"/>
     <mergeCell ref="A162:H162"/>
     <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A116:H116"/>
-    <mergeCell ref="A145:H145"/>
-    <mergeCell ref="A97:H97"/>
-    <mergeCell ref="A121:H121"/>
-    <mergeCell ref="A102:H102"/>
-    <mergeCell ref="A249:H249"/>
-    <mergeCell ref="A152:H152"/>
-    <mergeCell ref="A202:H202"/>
-    <mergeCell ref="A245:H245"/>
-    <mergeCell ref="A241:H241"/>
-    <mergeCell ref="A196:H196"/>
-    <mergeCell ref="A192:H192"/>
-    <mergeCell ref="A221:H221"/>
-    <mergeCell ref="A211:H211"/>
-    <mergeCell ref="A217:H217"/>
-    <mergeCell ref="A237:H237"/>
-    <mergeCell ref="A231:H231"/>
-    <mergeCell ref="A227:H227"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="90" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/графики/график Ташкент.xlsx
+++ b/графики/график Ташкент.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D5AE2A-A185-4B18-A766-21F298B11173}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A05234B-F3AF-49A1-8218-B0E98D662B3F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -808,26 +808,32 @@
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -859,20 +865,14 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1172,19 +1172,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="68"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="70"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="71" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="44" t="s">
@@ -1205,12 +1205,12 @@
       <c r="G2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="72" t="s">
+      <c r="H2" s="74" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
@@ -1227,10 +1227,10 @@
       <c r="G3" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="73"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="70"/>
+      <c r="A4" s="72"/>
       <c r="B4" s="44" t="s">
         <v>6</v>
       </c>
@@ -1247,10 +1247,10 @@
       <c r="G4" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="73"/>
+      <c r="H4" s="75"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="70"/>
+      <c r="A5" s="72"/>
       <c r="B5" s="44" t="s">
         <v>19</v>
       </c>
@@ -1261,14 +1261,14 @@
         <v>9</v>
       </c>
       <c r="E5" s="46"/>
-      <c r="F5" s="63" t="s">
+      <c r="F5" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="64"/>
-      <c r="H5" s="73"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="75"/>
     </row>
     <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="70"/>
+      <c r="A6" s="72"/>
       <c r="B6" s="44" t="s">
         <v>15</v>
       </c>
@@ -1285,10 +1285,10 @@
       <c r="G6" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="73"/>
+      <c r="H6" s="75"/>
     </row>
     <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="71"/>
+      <c r="A7" s="73"/>
       <c r="B7" s="44" t="s">
         <v>26</v>
       </c>
@@ -1305,7 +1305,7 @@
       <c r="G7" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="74"/>
+      <c r="H7" s="76"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="47">
@@ -1446,15 +1446,15 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="58" t="s">
+      <c r="A14" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
       <c r="H14" s="61"/>
     </row>
     <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -1599,16 +1599,16 @@
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="58" t="s">
+      <c r="A20" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="59"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="62"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="77"/>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -1751,16 +1751,16 @@
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="58" t="s">
+      <c r="A26" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="59"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="62"/>
+      <c r="B26" s="60"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="77"/>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -1961,16 +1961,16 @@
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="58" t="s">
+      <c r="A34" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="59"/>
-      <c r="C34" s="59"/>
-      <c r="D34" s="59"/>
-      <c r="E34" s="60"/>
-      <c r="F34" s="59"/>
-      <c r="G34" s="59"/>
-      <c r="H34" s="62"/>
+      <c r="B34" s="60"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="60"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="60"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="77"/>
     </row>
     <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -2155,16 +2155,16 @@
       </c>
     </row>
     <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="58" t="s">
+      <c r="A41" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="59"/>
-      <c r="C41" s="59"/>
-      <c r="D41" s="59"/>
-      <c r="E41" s="60"/>
-      <c r="F41" s="59"/>
-      <c r="G41" s="59"/>
-      <c r="H41" s="62"/>
+      <c r="B41" s="60"/>
+      <c r="C41" s="60"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="62"/>
+      <c r="F41" s="60"/>
+      <c r="G41" s="60"/>
+      <c r="H41" s="77"/>
     </row>
     <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
@@ -2366,16 +2366,16 @@
       <c r="H48" s="12"/>
     </row>
     <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="58" t="s">
+      <c r="A49" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B49" s="59"/>
-      <c r="C49" s="59"/>
-      <c r="D49" s="59"/>
-      <c r="E49" s="60"/>
-      <c r="F49" s="59"/>
-      <c r="G49" s="59"/>
-      <c r="H49" s="62"/>
+      <c r="B49" s="60"/>
+      <c r="C49" s="60"/>
+      <c r="D49" s="60"/>
+      <c r="E49" s="62"/>
+      <c r="F49" s="60"/>
+      <c r="G49" s="60"/>
+      <c r="H49" s="77"/>
     </row>
     <row r="50" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
@@ -2490,16 +2490,16 @@
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="58" t="s">
+      <c r="A54" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B54" s="59"/>
-      <c r="C54" s="59"/>
-      <c r="D54" s="59"/>
-      <c r="E54" s="60"/>
-      <c r="F54" s="59"/>
-      <c r="G54" s="59"/>
-      <c r="H54" s="62"/>
+      <c r="B54" s="60"/>
+      <c r="C54" s="60"/>
+      <c r="D54" s="60"/>
+      <c r="E54" s="62"/>
+      <c r="F54" s="60"/>
+      <c r="G54" s="60"/>
+      <c r="H54" s="77"/>
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
@@ -2648,15 +2648,15 @@
       </c>
     </row>
     <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="58" t="s">
+      <c r="A61" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B61" s="59"/>
-      <c r="C61" s="59"/>
-      <c r="D61" s="59"/>
-      <c r="E61" s="59"/>
-      <c r="F61" s="59"/>
-      <c r="G61" s="59"/>
+      <c r="B61" s="60"/>
+      <c r="C61" s="60"/>
+      <c r="D61" s="60"/>
+      <c r="E61" s="60"/>
+      <c r="F61" s="60"/>
+      <c r="G61" s="60"/>
       <c r="H61" s="61"/>
     </row>
     <row r="62" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
@@ -2772,15 +2772,15 @@
       <c r="H65" s="10"/>
     </row>
     <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="58" t="s">
+      <c r="A66" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B66" s="59"/>
-      <c r="C66" s="59"/>
-      <c r="D66" s="59"/>
-      <c r="E66" s="59"/>
-      <c r="F66" s="59"/>
-      <c r="G66" s="59"/>
+      <c r="B66" s="60"/>
+      <c r="C66" s="60"/>
+      <c r="D66" s="60"/>
+      <c r="E66" s="60"/>
+      <c r="F66" s="60"/>
+      <c r="G66" s="60"/>
       <c r="H66" s="61"/>
     </row>
     <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2956,15 +2956,15 @@
       </c>
     </row>
     <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="58" t="s">
+      <c r="A73" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B73" s="59"/>
-      <c r="C73" s="59"/>
-      <c r="D73" s="59"/>
-      <c r="E73" s="59"/>
-      <c r="F73" s="59"/>
-      <c r="G73" s="59"/>
+      <c r="B73" s="60"/>
+      <c r="C73" s="60"/>
+      <c r="D73" s="60"/>
+      <c r="E73" s="60"/>
+      <c r="F73" s="60"/>
+      <c r="G73" s="60"/>
       <c r="H73" s="61"/>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -3084,15 +3084,15 @@
       <c r="H77" s="10"/>
     </row>
     <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="58" t="s">
+      <c r="A78" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B78" s="59"/>
-      <c r="C78" s="59"/>
-      <c r="D78" s="59"/>
-      <c r="E78" s="59"/>
-      <c r="F78" s="59"/>
-      <c r="G78" s="59"/>
+      <c r="B78" s="60"/>
+      <c r="C78" s="60"/>
+      <c r="D78" s="60"/>
+      <c r="E78" s="60"/>
+      <c r="F78" s="60"/>
+      <c r="G78" s="60"/>
       <c r="H78" s="61"/>
     </row>
     <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -3268,15 +3268,15 @@
       </c>
     </row>
     <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="58" t="s">
+      <c r="A85" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B85" s="59"/>
-      <c r="C85" s="59"/>
-      <c r="D85" s="59"/>
-      <c r="E85" s="59"/>
-      <c r="F85" s="59"/>
-      <c r="G85" s="59"/>
+      <c r="B85" s="60"/>
+      <c r="C85" s="60"/>
+      <c r="D85" s="60"/>
+      <c r="E85" s="60"/>
+      <c r="F85" s="60"/>
+      <c r="G85" s="60"/>
       <c r="H85" s="61"/>
     </row>
     <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -3395,15 +3395,15 @@
       <c r="H89" s="10"/>
     </row>
     <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="58" t="s">
+      <c r="A90" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B90" s="59"/>
-      <c r="C90" s="59"/>
-      <c r="D90" s="59"/>
-      <c r="E90" s="59"/>
-      <c r="F90" s="59"/>
-      <c r="G90" s="59"/>
+      <c r="B90" s="60"/>
+      <c r="C90" s="60"/>
+      <c r="D90" s="60"/>
+      <c r="E90" s="60"/>
+      <c r="F90" s="60"/>
+      <c r="G90" s="60"/>
       <c r="H90" s="61"/>
     </row>
     <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -3578,15 +3578,15 @@
       </c>
     </row>
     <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="58" t="s">
+      <c r="A97" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B97" s="59"/>
-      <c r="C97" s="59"/>
-      <c r="D97" s="59"/>
-      <c r="E97" s="59"/>
-      <c r="F97" s="59"/>
-      <c r="G97" s="59"/>
+      <c r="B97" s="60"/>
+      <c r="C97" s="60"/>
+      <c r="D97" s="60"/>
+      <c r="E97" s="60"/>
+      <c r="F97" s="60"/>
+      <c r="G97" s="60"/>
       <c r="H97" s="61"/>
     </row>
     <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -3703,15 +3703,15 @@
       <c r="H101" s="10"/>
     </row>
     <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="58" t="s">
+      <c r="A102" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B102" s="59"/>
-      <c r="C102" s="59"/>
-      <c r="D102" s="59"/>
-      <c r="E102" s="59"/>
-      <c r="F102" s="59"/>
-      <c r="G102" s="59"/>
+      <c r="B102" s="60"/>
+      <c r="C102" s="60"/>
+      <c r="D102" s="60"/>
+      <c r="E102" s="60"/>
+      <c r="F102" s="60"/>
+      <c r="G102" s="60"/>
       <c r="H102" s="61"/>
     </row>
     <row r="103" spans="1:8" ht="60" hidden="1" x14ac:dyDescent="0.25">
@@ -3890,15 +3890,15 @@
       <c r="H108" s="17"/>
     </row>
     <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="58" t="s">
+      <c r="A109" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B109" s="59"/>
-      <c r="C109" s="59"/>
-      <c r="D109" s="59"/>
-      <c r="E109" s="59"/>
-      <c r="F109" s="59"/>
-      <c r="G109" s="59"/>
+      <c r="B109" s="60"/>
+      <c r="C109" s="60"/>
+      <c r="D109" s="60"/>
+      <c r="E109" s="60"/>
+      <c r="F109" s="60"/>
+      <c r="G109" s="60"/>
       <c r="H109" s="61"/>
     </row>
     <row r="110" spans="1:8" ht="60" hidden="1" x14ac:dyDescent="0.25">
@@ -4073,15 +4073,15 @@
       <c r="H115" s="10"/>
     </row>
     <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="58" t="s">
+      <c r="A116" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B116" s="59"/>
-      <c r="C116" s="59"/>
-      <c r="D116" s="59"/>
-      <c r="E116" s="59"/>
-      <c r="F116" s="59"/>
-      <c r="G116" s="59"/>
+      <c r="B116" s="60"/>
+      <c r="C116" s="60"/>
+      <c r="D116" s="60"/>
+      <c r="E116" s="60"/>
+      <c r="F116" s="60"/>
+      <c r="G116" s="60"/>
       <c r="H116" s="61"/>
     </row>
     <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -4181,15 +4181,15 @@
       <c r="H120" s="10"/>
     </row>
     <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="58" t="s">
+      <c r="A121" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B121" s="59"/>
-      <c r="C121" s="59"/>
-      <c r="D121" s="59"/>
-      <c r="E121" s="59"/>
-      <c r="F121" s="59"/>
-      <c r="G121" s="59"/>
+      <c r="B121" s="60"/>
+      <c r="C121" s="60"/>
+      <c r="D121" s="60"/>
+      <c r="E121" s="60"/>
+      <c r="F121" s="60"/>
+      <c r="G121" s="60"/>
       <c r="H121" s="61"/>
     </row>
     <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -4364,15 +4364,15 @@
       <c r="H127" s="10"/>
     </row>
     <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="58" t="s">
+      <c r="A128" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B128" s="59"/>
-      <c r="C128" s="59"/>
-      <c r="D128" s="59"/>
-      <c r="E128" s="59"/>
-      <c r="F128" s="59"/>
-      <c r="G128" s="59"/>
+      <c r="B128" s="60"/>
+      <c r="C128" s="60"/>
+      <c r="D128" s="60"/>
+      <c r="E128" s="60"/>
+      <c r="F128" s="60"/>
+      <c r="G128" s="60"/>
       <c r="H128" s="61"/>
     </row>
     <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -4492,15 +4492,15 @@
       <c r="H132" s="10"/>
     </row>
     <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="58" t="s">
+      <c r="A133" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B133" s="59"/>
-      <c r="C133" s="59"/>
-      <c r="D133" s="59"/>
-      <c r="E133" s="59"/>
-      <c r="F133" s="59"/>
-      <c r="G133" s="59"/>
+      <c r="B133" s="60"/>
+      <c r="C133" s="60"/>
+      <c r="D133" s="60"/>
+      <c r="E133" s="60"/>
+      <c r="F133" s="60"/>
+      <c r="G133" s="60"/>
       <c r="H133" s="61"/>
     </row>
     <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -4680,15 +4680,15 @@
       </c>
     </row>
     <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="58" t="s">
+      <c r="A140" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B140" s="59"/>
-      <c r="C140" s="59"/>
-      <c r="D140" s="59"/>
-      <c r="E140" s="59"/>
-      <c r="F140" s="59"/>
-      <c r="G140" s="59"/>
+      <c r="B140" s="60"/>
+      <c r="C140" s="60"/>
+      <c r="D140" s="60"/>
+      <c r="E140" s="60"/>
+      <c r="F140" s="60"/>
+      <c r="G140" s="60"/>
       <c r="H140" s="61"/>
     </row>
     <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -4808,15 +4808,15 @@
       <c r="H144" s="10"/>
     </row>
     <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="58" t="s">
+      <c r="A145" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B145" s="59"/>
-      <c r="C145" s="59"/>
-      <c r="D145" s="59"/>
-      <c r="E145" s="60"/>
-      <c r="F145" s="59"/>
-      <c r="G145" s="59"/>
+      <c r="B145" s="60"/>
+      <c r="C145" s="60"/>
+      <c r="D145" s="60"/>
+      <c r="E145" s="62"/>
+      <c r="F145" s="60"/>
+      <c r="G145" s="60"/>
       <c r="H145" s="61"/>
     </row>
     <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -4996,15 +4996,15 @@
       </c>
     </row>
     <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="58" t="s">
+      <c r="A152" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B152" s="59"/>
-      <c r="C152" s="59"/>
-      <c r="D152" s="59"/>
-      <c r="E152" s="60"/>
-      <c r="F152" s="59"/>
-      <c r="G152" s="59"/>
+      <c r="B152" s="60"/>
+      <c r="C152" s="60"/>
+      <c r="D152" s="60"/>
+      <c r="E152" s="62"/>
+      <c r="F152" s="60"/>
+      <c r="G152" s="60"/>
       <c r="H152" s="61"/>
     </row>
     <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -5095,15 +5095,15 @@
       <c r="H155" s="10"/>
     </row>
     <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="58" t="s">
+      <c r="A156" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B156" s="59"/>
-      <c r="C156" s="59"/>
-      <c r="D156" s="59"/>
-      <c r="E156" s="60"/>
-      <c r="F156" s="59"/>
-      <c r="G156" s="59"/>
+      <c r="B156" s="60"/>
+      <c r="C156" s="60"/>
+      <c r="D156" s="60"/>
+      <c r="E156" s="62"/>
+      <c r="F156" s="60"/>
+      <c r="G156" s="60"/>
       <c r="H156" s="61"/>
     </row>
     <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -5257,15 +5257,15 @@
       </c>
     </row>
     <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="58" t="s">
+      <c r="A162" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B162" s="59"/>
-      <c r="C162" s="59"/>
-      <c r="D162" s="59"/>
-      <c r="E162" s="60"/>
-      <c r="F162" s="59"/>
-      <c r="G162" s="59"/>
+      <c r="B162" s="60"/>
+      <c r="C162" s="60"/>
+      <c r="D162" s="60"/>
+      <c r="E162" s="62"/>
+      <c r="F162" s="60"/>
+      <c r="G162" s="60"/>
       <c r="H162" s="61"/>
     </row>
     <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -5361,15 +5361,15 @@
       <c r="H165" s="10"/>
     </row>
     <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="58" t="s">
+      <c r="A166" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B166" s="59"/>
-      <c r="C166" s="59"/>
-      <c r="D166" s="59"/>
-      <c r="E166" s="60"/>
-      <c r="F166" s="59"/>
-      <c r="G166" s="59"/>
+      <c r="B166" s="60"/>
+      <c r="C166" s="60"/>
+      <c r="D166" s="60"/>
+      <c r="E166" s="62"/>
+      <c r="F166" s="60"/>
+      <c r="G166" s="60"/>
       <c r="H166" s="61"/>
     </row>
     <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -5523,15 +5523,15 @@
       </c>
     </row>
     <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="58" t="s">
+      <c r="A172" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B172" s="59"/>
-      <c r="C172" s="59"/>
-      <c r="D172" s="59"/>
-      <c r="E172" s="60"/>
-      <c r="F172" s="59"/>
-      <c r="G172" s="59"/>
+      <c r="B172" s="60"/>
+      <c r="C172" s="60"/>
+      <c r="D172" s="60"/>
+      <c r="E172" s="62"/>
+      <c r="F172" s="60"/>
+      <c r="G172" s="60"/>
       <c r="H172" s="61"/>
     </row>
     <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -5627,15 +5627,15 @@
       <c r="H175" s="10"/>
     </row>
     <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="58" t="s">
+      <c r="A176" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B176" s="59"/>
-      <c r="C176" s="59"/>
-      <c r="D176" s="59"/>
-      <c r="E176" s="60"/>
-      <c r="F176" s="59"/>
-      <c r="G176" s="59"/>
+      <c r="B176" s="60"/>
+      <c r="C176" s="60"/>
+      <c r="D176" s="60"/>
+      <c r="E176" s="62"/>
+      <c r="F176" s="60"/>
+      <c r="G176" s="60"/>
       <c r="H176" s="61"/>
     </row>
     <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -5790,15 +5790,15 @@
       </c>
     </row>
     <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="58" t="s">
+      <c r="A182" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B182" s="59"/>
-      <c r="C182" s="59"/>
-      <c r="D182" s="59"/>
-      <c r="E182" s="60"/>
-      <c r="F182" s="59"/>
-      <c r="G182" s="59"/>
+      <c r="B182" s="60"/>
+      <c r="C182" s="60"/>
+      <c r="D182" s="60"/>
+      <c r="E182" s="62"/>
+      <c r="F182" s="60"/>
+      <c r="G182" s="60"/>
       <c r="H182" s="61"/>
     </row>
     <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -5891,15 +5891,15 @@
       <c r="H185" s="10"/>
     </row>
     <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="58" t="s">
+      <c r="A186" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B186" s="59"/>
-      <c r="C186" s="59"/>
-      <c r="D186" s="59"/>
-      <c r="E186" s="60"/>
-      <c r="F186" s="59"/>
-      <c r="G186" s="59"/>
+      <c r="B186" s="60"/>
+      <c r="C186" s="60"/>
+      <c r="D186" s="60"/>
+      <c r="E186" s="62"/>
+      <c r="F186" s="60"/>
+      <c r="G186" s="60"/>
       <c r="H186" s="61"/>
     </row>
     <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -6052,15 +6052,15 @@
       </c>
     </row>
     <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="58" t="s">
+      <c r="A192" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B192" s="59"/>
-      <c r="C192" s="59"/>
-      <c r="D192" s="59"/>
-      <c r="E192" s="60"/>
-      <c r="F192" s="59"/>
-      <c r="G192" s="59"/>
+      <c r="B192" s="60"/>
+      <c r="C192" s="60"/>
+      <c r="D192" s="60"/>
+      <c r="E192" s="62"/>
+      <c r="F192" s="60"/>
+      <c r="G192" s="60"/>
       <c r="H192" s="61"/>
     </row>
     <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -6156,15 +6156,15 @@
       <c r="H195" s="10"/>
     </row>
     <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="58" t="s">
+      <c r="A196" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B196" s="59"/>
-      <c r="C196" s="59"/>
-      <c r="D196" s="59"/>
-      <c r="E196" s="60"/>
-      <c r="F196" s="59"/>
-      <c r="G196" s="59"/>
+      <c r="B196" s="60"/>
+      <c r="C196" s="60"/>
+      <c r="D196" s="60"/>
+      <c r="E196" s="62"/>
+      <c r="F196" s="60"/>
+      <c r="G196" s="60"/>
       <c r="H196" s="61"/>
     </row>
     <row r="197" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
@@ -6316,15 +6316,15 @@
       <c r="H201" s="30"/>
     </row>
     <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="58" t="s">
+      <c r="A202" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B202" s="59"/>
-      <c r="C202" s="59"/>
-      <c r="D202" s="59"/>
-      <c r="E202" s="60"/>
-      <c r="F202" s="59"/>
-      <c r="G202" s="59"/>
+      <c r="B202" s="60"/>
+      <c r="C202" s="60"/>
+      <c r="D202" s="60"/>
+      <c r="E202" s="62"/>
+      <c r="F202" s="60"/>
+      <c r="G202" s="60"/>
       <c r="H202" s="61"/>
     </row>
     <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -6444,15 +6444,15 @@
       <c r="H206" s="10"/>
     </row>
     <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="58" t="s">
+      <c r="A207" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B207" s="59"/>
-      <c r="C207" s="59"/>
-      <c r="D207" s="59"/>
-      <c r="E207" s="60"/>
-      <c r="F207" s="59"/>
-      <c r="G207" s="59"/>
+      <c r="B207" s="60"/>
+      <c r="C207" s="60"/>
+      <c r="D207" s="60"/>
+      <c r="E207" s="62"/>
+      <c r="F207" s="60"/>
+      <c r="G207" s="60"/>
       <c r="H207" s="61"/>
     </row>
     <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -6547,15 +6547,15 @@
       </c>
     </row>
     <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="58" t="s">
+      <c r="A211" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B211" s="59"/>
-      <c r="C211" s="59"/>
-      <c r="D211" s="59"/>
-      <c r="E211" s="60"/>
-      <c r="F211" s="59"/>
-      <c r="G211" s="59"/>
+      <c r="B211" s="60"/>
+      <c r="C211" s="60"/>
+      <c r="D211" s="60"/>
+      <c r="E211" s="62"/>
+      <c r="F211" s="60"/>
+      <c r="G211" s="60"/>
       <c r="H211" s="61"/>
     </row>
     <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -6684,15 +6684,15 @@
       <c r="H216" s="30"/>
     </row>
     <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="58" t="s">
+      <c r="A217" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B217" s="59"/>
-      <c r="C217" s="59"/>
-      <c r="D217" s="59"/>
-      <c r="E217" s="60"/>
-      <c r="F217" s="59"/>
-      <c r="G217" s="59"/>
+      <c r="B217" s="60"/>
+      <c r="C217" s="60"/>
+      <c r="D217" s="60"/>
+      <c r="E217" s="62"/>
+      <c r="F217" s="60"/>
+      <c r="G217" s="60"/>
       <c r="H217" s="61"/>
     </row>
     <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -6785,15 +6785,15 @@
       </c>
     </row>
     <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="58" t="s">
+      <c r="A221" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B221" s="59"/>
-      <c r="C221" s="59"/>
-      <c r="D221" s="59"/>
-      <c r="E221" s="60"/>
-      <c r="F221" s="59"/>
-      <c r="G221" s="59"/>
+      <c r="B221" s="60"/>
+      <c r="C221" s="60"/>
+      <c r="D221" s="60"/>
+      <c r="E221" s="62"/>
+      <c r="F221" s="60"/>
+      <c r="G221" s="60"/>
       <c r="H221" s="61"/>
     </row>
     <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -6938,15 +6938,15 @@
       <c r="H226" s="30"/>
     </row>
     <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="58" t="s">
+      <c r="A227" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B227" s="59"/>
-      <c r="C227" s="59"/>
-      <c r="D227" s="59"/>
-      <c r="E227" s="60"/>
-      <c r="F227" s="59"/>
-      <c r="G227" s="59"/>
+      <c r="B227" s="60"/>
+      <c r="C227" s="60"/>
+      <c r="D227" s="60"/>
+      <c r="E227" s="62"/>
+      <c r="F227" s="60"/>
+      <c r="G227" s="60"/>
       <c r="H227" s="61"/>
     </row>
     <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -7041,15 +7041,15 @@
       </c>
     </row>
     <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="58" t="s">
+      <c r="A231" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B231" s="59"/>
-      <c r="C231" s="59"/>
-      <c r="D231" s="59"/>
-      <c r="E231" s="60"/>
-      <c r="F231" s="59"/>
-      <c r="G231" s="59"/>
+      <c r="B231" s="60"/>
+      <c r="C231" s="60"/>
+      <c r="D231" s="60"/>
+      <c r="E231" s="62"/>
+      <c r="F231" s="60"/>
+      <c r="G231" s="60"/>
       <c r="H231" s="61"/>
     </row>
     <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -7195,16 +7195,16 @@
       </c>
     </row>
     <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="75" t="s">
+      <c r="A237" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="B237" s="76"/>
-      <c r="C237" s="76"/>
-      <c r="D237" s="76"/>
-      <c r="E237" s="76"/>
-      <c r="F237" s="76"/>
-      <c r="G237" s="76"/>
-      <c r="H237" s="77"/>
+      <c r="B237" s="64"/>
+      <c r="C237" s="64"/>
+      <c r="D237" s="64"/>
+      <c r="E237" s="64"/>
+      <c r="F237" s="64"/>
+      <c r="G237" s="64"/>
+      <c r="H237" s="65"/>
     </row>
     <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="39">
@@ -7295,16 +7295,16 @@
       </c>
     </row>
     <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="75" t="s">
+      <c r="A241" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="B241" s="76"/>
-      <c r="C241" s="76"/>
-      <c r="D241" s="76"/>
-      <c r="E241" s="78"/>
-      <c r="F241" s="76"/>
-      <c r="G241" s="76"/>
-      <c r="H241" s="77"/>
+      <c r="B241" s="64"/>
+      <c r="C241" s="64"/>
+      <c r="D241" s="64"/>
+      <c r="E241" s="66"/>
+      <c r="F241" s="64"/>
+      <c r="G241" s="64"/>
+      <c r="H241" s="65"/>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="39">
@@ -7381,14 +7381,14 @@
       <c r="H244" s="40"/>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A245" s="75"/>
-      <c r="B245" s="76"/>
-      <c r="C245" s="76"/>
-      <c r="D245" s="76"/>
-      <c r="E245" s="76"/>
-      <c r="F245" s="76"/>
-      <c r="G245" s="76"/>
-      <c r="H245" s="77"/>
+      <c r="A245" s="63"/>
+      <c r="B245" s="64"/>
+      <c r="C245" s="64"/>
+      <c r="D245" s="64"/>
+      <c r="E245" s="64"/>
+      <c r="F245" s="64"/>
+      <c r="G245" s="64"/>
+      <c r="H245" s="65"/>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="39">
@@ -7469,13 +7469,13 @@
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A249" s="58"/>
-      <c r="B249" s="59"/>
-      <c r="C249" s="59"/>
-      <c r="D249" s="59"/>
-      <c r="E249" s="59"/>
-      <c r="F249" s="59"/>
-      <c r="G249" s="59"/>
+      <c r="A249" s="59"/>
+      <c r="B249" s="60"/>
+      <c r="C249" s="60"/>
+      <c r="D249" s="60"/>
+      <c r="E249" s="60"/>
+      <c r="F249" s="60"/>
+      <c r="G249" s="60"/>
       <c r="H249" s="61"/>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
@@ -7586,7 +7586,7 @@
       <c r="B254" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="C254" s="79" t="s">
+      <c r="C254" s="58" t="s">
         <v>75</v>
       </c>
       <c r="D254" s="53">
@@ -7604,13 +7604,13 @@
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A255" s="58"/>
-      <c r="B255" s="59"/>
-      <c r="C255" s="59"/>
-      <c r="D255" s="59"/>
-      <c r="E255" s="59"/>
-      <c r="F255" s="59"/>
-      <c r="G255" s="59"/>
+      <c r="A255" s="59"/>
+      <c r="B255" s="60"/>
+      <c r="C255" s="60"/>
+      <c r="D255" s="60"/>
+      <c r="E255" s="60"/>
+      <c r="F255" s="60"/>
+      <c r="G255" s="60"/>
       <c r="H255" s="61"/>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
@@ -7627,12 +7627,14 @@
       <c r="D256" s="36">
         <v>46042</v>
       </c>
-      <c r="E256" s="37"/>
+      <c r="E256" s="37">
+        <v>3036</v>
+      </c>
       <c r="F256" s="36">
-        <v>46042</v>
+        <v>46049</v>
       </c>
       <c r="G256" s="36">
-        <v>46042</v>
+        <v>46049</v>
       </c>
       <c r="H256" s="10"/>
     </row>
@@ -7714,39 +7716,6 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="48">
-    <mergeCell ref="A255:H255"/>
-    <mergeCell ref="A249:H249"/>
-    <mergeCell ref="A152:H152"/>
-    <mergeCell ref="A202:H202"/>
-    <mergeCell ref="A245:H245"/>
-    <mergeCell ref="A241:H241"/>
-    <mergeCell ref="A196:H196"/>
-    <mergeCell ref="A192:H192"/>
-    <mergeCell ref="A221:H221"/>
-    <mergeCell ref="A211:H211"/>
-    <mergeCell ref="A217:H217"/>
-    <mergeCell ref="A237:H237"/>
-    <mergeCell ref="A231:H231"/>
-    <mergeCell ref="A227:H227"/>
-    <mergeCell ref="A116:H116"/>
-    <mergeCell ref="A145:H145"/>
-    <mergeCell ref="A97:H97"/>
-    <mergeCell ref="A121:H121"/>
-    <mergeCell ref="A102:H102"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A207:H207"/>
     <mergeCell ref="A73:H73"/>
     <mergeCell ref="A156:H156"/>
     <mergeCell ref="A186:H186"/>
@@ -7762,6 +7731,39 @@
     <mergeCell ref="A109:H109"/>
     <mergeCell ref="A162:H162"/>
     <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A116:H116"/>
+    <mergeCell ref="A145:H145"/>
+    <mergeCell ref="A97:H97"/>
+    <mergeCell ref="A121:H121"/>
+    <mergeCell ref="A102:H102"/>
+    <mergeCell ref="A255:H255"/>
+    <mergeCell ref="A249:H249"/>
+    <mergeCell ref="A152:H152"/>
+    <mergeCell ref="A202:H202"/>
+    <mergeCell ref="A245:H245"/>
+    <mergeCell ref="A241:H241"/>
+    <mergeCell ref="A196:H196"/>
+    <mergeCell ref="A192:H192"/>
+    <mergeCell ref="A221:H221"/>
+    <mergeCell ref="A211:H211"/>
+    <mergeCell ref="A217:H217"/>
+    <mergeCell ref="A237:H237"/>
+    <mergeCell ref="A231:H231"/>
+    <mergeCell ref="A227:H227"/>
+    <mergeCell ref="A207:H207"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="90" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/графики/график Ташкент.xlsx
+++ b/графики/график Ташкент.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A05234B-F3AF-49A1-8218-B0E98D662B3F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F0026B0-A5AF-4347-9CF4-38C5AD7402E1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="82">
   <si>
     <t>Контракт</t>
   </si>
@@ -333,10 +333,16 @@
     <t>07,01,26 сделали дозаказ</t>
   </si>
   <si>
-    <t>Шувалова перенсла погрузку с 19,01 на 26,01</t>
-  </si>
-  <si>
     <t>отмена + перенос на следующую неделю (Шувалова)</t>
+  </si>
+  <si>
+    <t>21,01,26</t>
+  </si>
+  <si>
+    <t>22,01,26 сделали дозаказ на 500кг</t>
+  </si>
+  <si>
+    <t>Шувалова отменила (сделали новый заказ 21,01,26)</t>
   </si>
 </sst>
 </file>
@@ -823,17 +829,14 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -865,14 +868,17 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1157,7 +1163,7 @@
   <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H259"/>
+  <dimension ref="A1:H260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="3" customWidth="1"/>
@@ -1172,19 +1178,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="70"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="70" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="44" t="s">
@@ -1205,12 +1211,12 @@
       <c r="G2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="74" t="s">
+      <c r="H2" s="73" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="72"/>
+      <c r="A3" s="71"/>
       <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
@@ -1227,10 +1233,10 @@
       <c r="G3" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="75"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
+      <c r="A4" s="71"/>
       <c r="B4" s="44" t="s">
         <v>6</v>
       </c>
@@ -1247,10 +1253,10 @@
       <c r="G4" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="75"/>
+      <c r="H4" s="74"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
+      <c r="A5" s="71"/>
       <c r="B5" s="44" t="s">
         <v>19</v>
       </c>
@@ -1261,14 +1267,14 @@
         <v>9</v>
       </c>
       <c r="E5" s="46"/>
-      <c r="F5" s="78" t="s">
+      <c r="F5" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="79"/>
-      <c r="H5" s="75"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="74"/>
     </row>
     <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
+      <c r="A6" s="71"/>
       <c r="B6" s="44" t="s">
         <v>15</v>
       </c>
@@ -1285,10 +1291,10 @@
       <c r="G6" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="75"/>
+      <c r="H6" s="74"/>
     </row>
     <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="73"/>
+      <c r="A7" s="72"/>
       <c r="B7" s="44" t="s">
         <v>26</v>
       </c>
@@ -1305,7 +1311,7 @@
       <c r="G7" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="76"/>
+      <c r="H7" s="75"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="47">
@@ -1608,7 +1614,7 @@
       <c r="E20" s="62"/>
       <c r="F20" s="60"/>
       <c r="G20" s="60"/>
-      <c r="H20" s="77"/>
+      <c r="H20" s="63"/>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -1760,7 +1766,7 @@
       <c r="E26" s="62"/>
       <c r="F26" s="60"/>
       <c r="G26" s="60"/>
-      <c r="H26" s="77"/>
+      <c r="H26" s="63"/>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -1970,7 +1976,7 @@
       <c r="E34" s="62"/>
       <c r="F34" s="60"/>
       <c r="G34" s="60"/>
-      <c r="H34" s="77"/>
+      <c r="H34" s="63"/>
     </row>
     <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -2164,7 +2170,7 @@
       <c r="E41" s="62"/>
       <c r="F41" s="60"/>
       <c r="G41" s="60"/>
-      <c r="H41" s="77"/>
+      <c r="H41" s="63"/>
     </row>
     <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
@@ -2375,7 +2381,7 @@
       <c r="E49" s="62"/>
       <c r="F49" s="60"/>
       <c r="G49" s="60"/>
-      <c r="H49" s="77"/>
+      <c r="H49" s="63"/>
     </row>
     <row r="50" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
@@ -2499,7 +2505,7 @@
       <c r="E54" s="62"/>
       <c r="F54" s="60"/>
       <c r="G54" s="60"/>
-      <c r="H54" s="77"/>
+      <c r="H54" s="63"/>
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
@@ -7195,16 +7201,16 @@
       </c>
     </row>
     <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="63" t="s">
+      <c r="A237" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B237" s="64"/>
-      <c r="C237" s="64"/>
-      <c r="D237" s="64"/>
-      <c r="E237" s="64"/>
-      <c r="F237" s="64"/>
-      <c r="G237" s="64"/>
-      <c r="H237" s="65"/>
+      <c r="B237" s="77"/>
+      <c r="C237" s="77"/>
+      <c r="D237" s="77"/>
+      <c r="E237" s="77"/>
+      <c r="F237" s="77"/>
+      <c r="G237" s="77"/>
+      <c r="H237" s="78"/>
     </row>
     <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="39">
@@ -7295,16 +7301,16 @@
       </c>
     </row>
     <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="63" t="s">
+      <c r="A241" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B241" s="64"/>
-      <c r="C241" s="64"/>
-      <c r="D241" s="64"/>
-      <c r="E241" s="66"/>
-      <c r="F241" s="64"/>
-      <c r="G241" s="64"/>
-      <c r="H241" s="65"/>
+      <c r="B241" s="77"/>
+      <c r="C241" s="77"/>
+      <c r="D241" s="77"/>
+      <c r="E241" s="79"/>
+      <c r="F241" s="77"/>
+      <c r="G241" s="77"/>
+      <c r="H241" s="78"/>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="39">
@@ -7355,11 +7361,11 @@
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A244" s="39">
+      <c r="A244" s="2">
         <f>MAX(A235:A243)+1</f>
         <v>195</v>
       </c>
-      <c r="B244" s="38" t="s">
+      <c r="B244" s="9" t="s">
         <v>26</v>
       </c>
       <c r="C244" s="36">
@@ -7369,7 +7375,7 @@
       <c r="D244" s="36">
         <v>46017</v>
       </c>
-      <c r="E244" s="37">
+      <c r="E244" s="4">
         <v>3133</v>
       </c>
       <c r="F244" s="36">
@@ -7378,17 +7384,17 @@
       <c r="G244" s="36">
         <v>46034</v>
       </c>
-      <c r="H244" s="40"/>
+      <c r="H244" s="10"/>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A245" s="63"/>
-      <c r="B245" s="64"/>
-      <c r="C245" s="64"/>
-      <c r="D245" s="64"/>
-      <c r="E245" s="64"/>
-      <c r="F245" s="64"/>
-      <c r="G245" s="64"/>
-      <c r="H245" s="65"/>
+      <c r="A245" s="76"/>
+      <c r="B245" s="77"/>
+      <c r="C245" s="77"/>
+      <c r="D245" s="77"/>
+      <c r="E245" s="77"/>
+      <c r="F245" s="77"/>
+      <c r="G245" s="77"/>
+      <c r="H245" s="78"/>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="39">
@@ -7504,30 +7510,28 @@
       <c r="H250" s="10"/>
     </row>
     <row r="251" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A251" s="2">
+      <c r="A251" s="51">
         <f t="shared" ref="A251:A254" si="264">MAX(A239:A250)+1</f>
         <v>200</v>
       </c>
-      <c r="B251" s="38" t="s">
+      <c r="B251" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="C251" s="36">
+      <c r="C251" s="53">
         <v>46034</v>
       </c>
-      <c r="D251" s="36">
+      <c r="D251" s="53">
         <v>46035</v>
       </c>
-      <c r="E251" s="37">
-        <v>2085</v>
-      </c>
-      <c r="F251" s="15">
+      <c r="E251" s="54"/>
+      <c r="F251" s="53">
         <v>46048</v>
       </c>
-      <c r="G251" s="36">
+      <c r="G251" s="53">
         <v>46048</v>
       </c>
-      <c r="H251" s="17" t="s">
-        <v>78</v>
+      <c r="H251" s="55" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="252" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -7600,7 +7604,7 @@
         <v>46041</v>
       </c>
       <c r="H254" s="55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
@@ -7628,7 +7632,8 @@
         <v>46042</v>
       </c>
       <c r="E256" s="37">
-        <v>3036</v>
+        <f>3036+500</f>
+        <v>3536</v>
       </c>
       <c r="F256" s="36">
         <v>46049</v>
@@ -7636,59 +7641,63 @@
       <c r="G256" s="36">
         <v>46049</v>
       </c>
-      <c r="H256" s="10"/>
+      <c r="H256" s="10" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
+        <f>MAX(A245:A256)+1</f>
+        <v>205</v>
+      </c>
+      <c r="B257" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C257" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="D257" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="E257" s="37">
+        <v>2301</v>
+      </c>
+      <c r="F257" s="36">
+        <v>46048</v>
+      </c>
+      <c r="G257" s="36">
+        <v>46048</v>
+      </c>
+      <c r="H257" s="10"/>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A258" s="2">
         <f>MAX(A246:A256)+1</f>
         <v>205</v>
       </c>
-      <c r="B257" s="9" t="s">
+      <c r="B258" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C257" s="36">
+      <c r="C258" s="36">
         <v>46041</v>
       </c>
-      <c r="D257" s="36">
+      <c r="D258" s="36">
         <v>46042</v>
       </c>
-      <c r="E257" s="37"/>
-      <c r="F257" s="36"/>
-      <c r="G257" s="36"/>
-      <c r="H257" s="10" t="s">
+      <c r="E258" s="37"/>
+      <c r="F258" s="36"/>
+      <c r="G258" s="36"/>
+      <c r="H258" s="10" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A258" s="2">
-        <f>MAX(A247:A257)+1</f>
-        <v>206</v>
-      </c>
-      <c r="B258" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C258" s="36">
-        <v>46044</v>
-      </c>
-      <c r="D258" s="36">
-        <v>46045</v>
-      </c>
-      <c r="E258" s="37"/>
-      <c r="F258" s="36">
-        <v>46050</v>
-      </c>
-      <c r="G258" s="36">
-        <v>46051</v>
-      </c>
-      <c r="H258" s="10"/>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
-        <f>MAX(A248:A258)+1</f>
-        <v>207</v>
+        <f>MAX(A247:A258)+1</f>
+        <v>206</v>
       </c>
       <c r="B259" s="9" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C259" s="36">
         <v>46044</v>
@@ -7698,12 +7707,35 @@
       </c>
       <c r="E259" s="37"/>
       <c r="F259" s="36">
+        <v>46050</v>
+      </c>
+      <c r="G259" s="36">
+        <v>46051</v>
+      </c>
+      <c r="H259" s="10"/>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A260" s="2">
+        <f>MAX(A248:A259)+1</f>
+        <v>207</v>
+      </c>
+      <c r="B260" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C260" s="36">
+        <v>46044</v>
+      </c>
+      <c r="D260" s="36">
+        <v>46045</v>
+      </c>
+      <c r="E260" s="37"/>
+      <c r="F260" s="36">
         <v>46055</v>
       </c>
-      <c r="G259" s="36">
+      <c r="G260" s="36">
         <v>46056</v>
       </c>
-      <c r="H259" s="10"/>
+      <c r="H260" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A8:H244" xr:uid="{9D5F3532-A341-428E-AFDB-DF9AAA83E1F5}">
@@ -7716,35 +7748,9 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="48">
-    <mergeCell ref="A73:H73"/>
-    <mergeCell ref="A156:H156"/>
-    <mergeCell ref="A186:H186"/>
-    <mergeCell ref="A182:H182"/>
-    <mergeCell ref="A176:H176"/>
-    <mergeCell ref="A172:H172"/>
-    <mergeCell ref="A166:H166"/>
-    <mergeCell ref="A90:H90"/>
-    <mergeCell ref="A85:H85"/>
-    <mergeCell ref="A128:H128"/>
-    <mergeCell ref="A133:H133"/>
-    <mergeCell ref="A140:H140"/>
-    <mergeCell ref="A109:H109"/>
-    <mergeCell ref="A162:H162"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A116:H116"/>
+    <mergeCell ref="A231:H231"/>
+    <mergeCell ref="A227:H227"/>
+    <mergeCell ref="A207:H207"/>
     <mergeCell ref="A145:H145"/>
     <mergeCell ref="A97:H97"/>
     <mergeCell ref="A121:H121"/>
@@ -7761,9 +7767,35 @@
     <mergeCell ref="A211:H211"/>
     <mergeCell ref="A217:H217"/>
     <mergeCell ref="A237:H237"/>
-    <mergeCell ref="A231:H231"/>
-    <mergeCell ref="A227:H227"/>
-    <mergeCell ref="A207:H207"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A156:H156"/>
+    <mergeCell ref="A186:H186"/>
+    <mergeCell ref="A182:H182"/>
+    <mergeCell ref="A176:H176"/>
+    <mergeCell ref="A172:H172"/>
+    <mergeCell ref="A166:H166"/>
+    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A85:H85"/>
+    <mergeCell ref="A128:H128"/>
+    <mergeCell ref="A133:H133"/>
+    <mergeCell ref="A140:H140"/>
+    <mergeCell ref="A109:H109"/>
+    <mergeCell ref="A162:H162"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A116:H116"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="90" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/графики/график Ташкент.xlsx
+++ b/графики/график Ташкент.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F0026B0-A5AF-4347-9CF4-38C5AD7402E1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6114CB1E-7FD8-4A13-B1B8-763C47BBE828}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$8:$H$244</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$8:$H$254</definedName>
   </definedNames>
   <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="82">
   <si>
     <t>Контракт</t>
   </si>
@@ -823,20 +823,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -868,17 +871,14 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1163,7 +1163,7 @@
   <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H260"/>
+  <dimension ref="A1:H264"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="3" customWidth="1"/>
@@ -1178,19 +1178,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="69"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="70"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="71" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="44" t="s">
@@ -1211,12 +1211,12 @@
       <c r="G2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="73" t="s">
+      <c r="H2" s="74" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="71"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
@@ -1233,10 +1233,10 @@
       <c r="G3" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="74"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="71"/>
+      <c r="A4" s="72"/>
       <c r="B4" s="44" t="s">
         <v>6</v>
       </c>
@@ -1253,10 +1253,10 @@
       <c r="G4" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="74"/>
+      <c r="H4" s="75"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="71"/>
+      <c r="A5" s="72"/>
       <c r="B5" s="44" t="s">
         <v>19</v>
       </c>
@@ -1267,14 +1267,14 @@
         <v>9</v>
       </c>
       <c r="E5" s="46"/>
-      <c r="F5" s="64" t="s">
+      <c r="F5" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="65"/>
-      <c r="H5" s="74"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="75"/>
     </row>
     <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="71"/>
+      <c r="A6" s="72"/>
       <c r="B6" s="44" t="s">
         <v>15</v>
       </c>
@@ -1291,10 +1291,10 @@
       <c r="G6" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="74"/>
+      <c r="H6" s="75"/>
     </row>
     <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
+      <c r="A7" s="73"/>
       <c r="B7" s="44" t="s">
         <v>26</v>
       </c>
@@ -1311,7 +1311,7 @@
       <c r="G7" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="75"/>
+      <c r="H7" s="76"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="47">
@@ -1461,7 +1461,7 @@
       <c r="E14" s="60"/>
       <c r="F14" s="60"/>
       <c r="G14" s="60"/>
-      <c r="H14" s="61"/>
+      <c r="H14" s="62"/>
     </row>
     <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -1611,10 +1611,10 @@
       <c r="B20" s="60"/>
       <c r="C20" s="60"/>
       <c r="D20" s="60"/>
-      <c r="E20" s="62"/>
+      <c r="E20" s="61"/>
       <c r="F20" s="60"/>
       <c r="G20" s="60"/>
-      <c r="H20" s="63"/>
+      <c r="H20" s="77"/>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -1763,10 +1763,10 @@
       <c r="B26" s="60"/>
       <c r="C26" s="60"/>
       <c r="D26" s="60"/>
-      <c r="E26" s="62"/>
+      <c r="E26" s="61"/>
       <c r="F26" s="60"/>
       <c r="G26" s="60"/>
-      <c r="H26" s="63"/>
+      <c r="H26" s="77"/>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -1973,10 +1973,10 @@
       <c r="B34" s="60"/>
       <c r="C34" s="60"/>
       <c r="D34" s="60"/>
-      <c r="E34" s="62"/>
+      <c r="E34" s="61"/>
       <c r="F34" s="60"/>
       <c r="G34" s="60"/>
-      <c r="H34" s="63"/>
+      <c r="H34" s="77"/>
     </row>
     <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -2167,10 +2167,10 @@
       <c r="B41" s="60"/>
       <c r="C41" s="60"/>
       <c r="D41" s="60"/>
-      <c r="E41" s="62"/>
+      <c r="E41" s="61"/>
       <c r="F41" s="60"/>
       <c r="G41" s="60"/>
-      <c r="H41" s="63"/>
+      <c r="H41" s="77"/>
     </row>
     <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
@@ -2378,10 +2378,10 @@
       <c r="B49" s="60"/>
       <c r="C49" s="60"/>
       <c r="D49" s="60"/>
-      <c r="E49" s="62"/>
+      <c r="E49" s="61"/>
       <c r="F49" s="60"/>
       <c r="G49" s="60"/>
-      <c r="H49" s="63"/>
+      <c r="H49" s="77"/>
     </row>
     <row r="50" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
@@ -2502,10 +2502,10 @@
       <c r="B54" s="60"/>
       <c r="C54" s="60"/>
       <c r="D54" s="60"/>
-      <c r="E54" s="62"/>
+      <c r="E54" s="61"/>
       <c r="F54" s="60"/>
       <c r="G54" s="60"/>
-      <c r="H54" s="63"/>
+      <c r="H54" s="77"/>
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
@@ -2663,7 +2663,7 @@
       <c r="E61" s="60"/>
       <c r="F61" s="60"/>
       <c r="G61" s="60"/>
-      <c r="H61" s="61"/>
+      <c r="H61" s="62"/>
     </row>
     <row r="62" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
@@ -2787,7 +2787,7 @@
       <c r="E66" s="60"/>
       <c r="F66" s="60"/>
       <c r="G66" s="60"/>
-      <c r="H66" s="61"/>
+      <c r="H66" s="62"/>
     </row>
     <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
@@ -2971,7 +2971,7 @@
       <c r="E73" s="60"/>
       <c r="F73" s="60"/>
       <c r="G73" s="60"/>
-      <c r="H73" s="61"/>
+      <c r="H73" s="62"/>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
@@ -3099,7 +3099,7 @@
       <c r="E78" s="60"/>
       <c r="F78" s="60"/>
       <c r="G78" s="60"/>
-      <c r="H78" s="61"/>
+      <c r="H78" s="62"/>
     </row>
     <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
@@ -3283,7 +3283,7 @@
       <c r="E85" s="60"/>
       <c r="F85" s="60"/>
       <c r="G85" s="60"/>
-      <c r="H85" s="61"/>
+      <c r="H85" s="62"/>
     </row>
     <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
@@ -3410,7 +3410,7 @@
       <c r="E90" s="60"/>
       <c r="F90" s="60"/>
       <c r="G90" s="60"/>
-      <c r="H90" s="61"/>
+      <c r="H90" s="62"/>
     </row>
     <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
@@ -3593,7 +3593,7 @@
       <c r="E97" s="60"/>
       <c r="F97" s="60"/>
       <c r="G97" s="60"/>
-      <c r="H97" s="61"/>
+      <c r="H97" s="62"/>
     </row>
     <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
@@ -3718,7 +3718,7 @@
       <c r="E102" s="60"/>
       <c r="F102" s="60"/>
       <c r="G102" s="60"/>
-      <c r="H102" s="61"/>
+      <c r="H102" s="62"/>
     </row>
     <row r="103" spans="1:8" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
@@ -3905,7 +3905,7 @@
       <c r="E109" s="60"/>
       <c r="F109" s="60"/>
       <c r="G109" s="60"/>
-      <c r="H109" s="61"/>
+      <c r="H109" s="62"/>
     </row>
     <row r="110" spans="1:8" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
@@ -4088,7 +4088,7 @@
       <c r="E116" s="60"/>
       <c r="F116" s="60"/>
       <c r="G116" s="60"/>
-      <c r="H116" s="61"/>
+      <c r="H116" s="62"/>
     </row>
     <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
@@ -4196,7 +4196,7 @@
       <c r="E121" s="60"/>
       <c r="F121" s="60"/>
       <c r="G121" s="60"/>
-      <c r="H121" s="61"/>
+      <c r="H121" s="62"/>
     </row>
     <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
@@ -4379,7 +4379,7 @@
       <c r="E128" s="60"/>
       <c r="F128" s="60"/>
       <c r="G128" s="60"/>
-      <c r="H128" s="61"/>
+      <c r="H128" s="62"/>
     </row>
     <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
@@ -4507,7 +4507,7 @@
       <c r="E133" s="60"/>
       <c r="F133" s="60"/>
       <c r="G133" s="60"/>
-      <c r="H133" s="61"/>
+      <c r="H133" s="62"/>
     </row>
     <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
@@ -4695,7 +4695,7 @@
       <c r="E140" s="60"/>
       <c r="F140" s="60"/>
       <c r="G140" s="60"/>
-      <c r="H140" s="61"/>
+      <c r="H140" s="62"/>
     </row>
     <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
@@ -4820,10 +4820,10 @@
       <c r="B145" s="60"/>
       <c r="C145" s="60"/>
       <c r="D145" s="60"/>
-      <c r="E145" s="62"/>
+      <c r="E145" s="61"/>
       <c r="F145" s="60"/>
       <c r="G145" s="60"/>
-      <c r="H145" s="61"/>
+      <c r="H145" s="62"/>
     </row>
     <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
@@ -5008,10 +5008,10 @@
       <c r="B152" s="60"/>
       <c r="C152" s="60"/>
       <c r="D152" s="60"/>
-      <c r="E152" s="62"/>
+      <c r="E152" s="61"/>
       <c r="F152" s="60"/>
       <c r="G152" s="60"/>
-      <c r="H152" s="61"/>
+      <c r="H152" s="62"/>
     </row>
     <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
@@ -5107,10 +5107,10 @@
       <c r="B156" s="60"/>
       <c r="C156" s="60"/>
       <c r="D156" s="60"/>
-      <c r="E156" s="62"/>
+      <c r="E156" s="61"/>
       <c r="F156" s="60"/>
       <c r="G156" s="60"/>
-      <c r="H156" s="61"/>
+      <c r="H156" s="62"/>
     </row>
     <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
@@ -5269,10 +5269,10 @@
       <c r="B162" s="60"/>
       <c r="C162" s="60"/>
       <c r="D162" s="60"/>
-      <c r="E162" s="62"/>
+      <c r="E162" s="61"/>
       <c r="F162" s="60"/>
       <c r="G162" s="60"/>
-      <c r="H162" s="61"/>
+      <c r="H162" s="62"/>
     </row>
     <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
@@ -5373,10 +5373,10 @@
       <c r="B166" s="60"/>
       <c r="C166" s="60"/>
       <c r="D166" s="60"/>
-      <c r="E166" s="62"/>
+      <c r="E166" s="61"/>
       <c r="F166" s="60"/>
       <c r="G166" s="60"/>
-      <c r="H166" s="61"/>
+      <c r="H166" s="62"/>
     </row>
     <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
@@ -5535,10 +5535,10 @@
       <c r="B172" s="60"/>
       <c r="C172" s="60"/>
       <c r="D172" s="60"/>
-      <c r="E172" s="62"/>
+      <c r="E172" s="61"/>
       <c r="F172" s="60"/>
       <c r="G172" s="60"/>
-      <c r="H172" s="61"/>
+      <c r="H172" s="62"/>
     </row>
     <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
@@ -5639,10 +5639,10 @@
       <c r="B176" s="60"/>
       <c r="C176" s="60"/>
       <c r="D176" s="60"/>
-      <c r="E176" s="62"/>
+      <c r="E176" s="61"/>
       <c r="F176" s="60"/>
       <c r="G176" s="60"/>
-      <c r="H176" s="61"/>
+      <c r="H176" s="62"/>
     </row>
     <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
@@ -5802,10 +5802,10 @@
       <c r="B182" s="60"/>
       <c r="C182" s="60"/>
       <c r="D182" s="60"/>
-      <c r="E182" s="62"/>
+      <c r="E182" s="61"/>
       <c r="F182" s="60"/>
       <c r="G182" s="60"/>
-      <c r="H182" s="61"/>
+      <c r="H182" s="62"/>
     </row>
     <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
@@ -5903,10 +5903,10 @@
       <c r="B186" s="60"/>
       <c r="C186" s="60"/>
       <c r="D186" s="60"/>
-      <c r="E186" s="62"/>
+      <c r="E186" s="61"/>
       <c r="F186" s="60"/>
       <c r="G186" s="60"/>
-      <c r="H186" s="61"/>
+      <c r="H186" s="62"/>
     </row>
     <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
@@ -6064,10 +6064,10 @@
       <c r="B192" s="60"/>
       <c r="C192" s="60"/>
       <c r="D192" s="60"/>
-      <c r="E192" s="62"/>
+      <c r="E192" s="61"/>
       <c r="F192" s="60"/>
       <c r="G192" s="60"/>
-      <c r="H192" s="61"/>
+      <c r="H192" s="62"/>
     </row>
     <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
@@ -6168,10 +6168,10 @@
       <c r="B196" s="60"/>
       <c r="C196" s="60"/>
       <c r="D196" s="60"/>
-      <c r="E196" s="62"/>
+      <c r="E196" s="61"/>
       <c r="F196" s="60"/>
       <c r="G196" s="60"/>
-      <c r="H196" s="61"/>
+      <c r="H196" s="62"/>
     </row>
     <row r="197" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
@@ -6328,10 +6328,10 @@
       <c r="B202" s="60"/>
       <c r="C202" s="60"/>
       <c r="D202" s="60"/>
-      <c r="E202" s="62"/>
+      <c r="E202" s="61"/>
       <c r="F202" s="60"/>
       <c r="G202" s="60"/>
-      <c r="H202" s="61"/>
+      <c r="H202" s="62"/>
     </row>
     <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
@@ -6456,10 +6456,10 @@
       <c r="B207" s="60"/>
       <c r="C207" s="60"/>
       <c r="D207" s="60"/>
-      <c r="E207" s="62"/>
+      <c r="E207" s="61"/>
       <c r="F207" s="60"/>
       <c r="G207" s="60"/>
-      <c r="H207" s="61"/>
+      <c r="H207" s="62"/>
     </row>
     <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
@@ -6559,10 +6559,10 @@
       <c r="B211" s="60"/>
       <c r="C211" s="60"/>
       <c r="D211" s="60"/>
-      <c r="E211" s="62"/>
+      <c r="E211" s="61"/>
       <c r="F211" s="60"/>
       <c r="G211" s="60"/>
-      <c r="H211" s="61"/>
+      <c r="H211" s="62"/>
     </row>
     <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
@@ -6696,10 +6696,10 @@
       <c r="B217" s="60"/>
       <c r="C217" s="60"/>
       <c r="D217" s="60"/>
-      <c r="E217" s="62"/>
+      <c r="E217" s="61"/>
       <c r="F217" s="60"/>
       <c r="G217" s="60"/>
-      <c r="H217" s="61"/>
+      <c r="H217" s="62"/>
     </row>
     <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
@@ -6797,10 +6797,10 @@
       <c r="B221" s="60"/>
       <c r="C221" s="60"/>
       <c r="D221" s="60"/>
-      <c r="E221" s="62"/>
+      <c r="E221" s="61"/>
       <c r="F221" s="60"/>
       <c r="G221" s="60"/>
-      <c r="H221" s="61"/>
+      <c r="H221" s="62"/>
     </row>
     <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
@@ -6950,10 +6950,10 @@
       <c r="B227" s="60"/>
       <c r="C227" s="60"/>
       <c r="D227" s="60"/>
-      <c r="E227" s="62"/>
+      <c r="E227" s="61"/>
       <c r="F227" s="60"/>
       <c r="G227" s="60"/>
-      <c r="H227" s="61"/>
+      <c r="H227" s="62"/>
     </row>
     <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
@@ -7053,10 +7053,10 @@
       <c r="B231" s="60"/>
       <c r="C231" s="60"/>
       <c r="D231" s="60"/>
-      <c r="E231" s="62"/>
+      <c r="E231" s="61"/>
       <c r="F231" s="60"/>
       <c r="G231" s="60"/>
-      <c r="H231" s="61"/>
+      <c r="H231" s="62"/>
     </row>
     <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
@@ -7201,16 +7201,16 @@
       </c>
     </row>
     <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="76" t="s">
+      <c r="A237" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="B237" s="77"/>
-      <c r="C237" s="77"/>
-      <c r="D237" s="77"/>
-      <c r="E237" s="77"/>
-      <c r="F237" s="77"/>
-      <c r="G237" s="77"/>
-      <c r="H237" s="78"/>
+      <c r="B237" s="64"/>
+      <c r="C237" s="64"/>
+      <c r="D237" s="64"/>
+      <c r="E237" s="64"/>
+      <c r="F237" s="64"/>
+      <c r="G237" s="64"/>
+      <c r="H237" s="65"/>
     </row>
     <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="39">
@@ -7301,18 +7301,18 @@
       </c>
     </row>
     <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="76" t="s">
+      <c r="A241" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="B241" s="77"/>
-      <c r="C241" s="77"/>
-      <c r="D241" s="77"/>
-      <c r="E241" s="79"/>
-      <c r="F241" s="77"/>
-      <c r="G241" s="77"/>
-      <c r="H241" s="78"/>
-    </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B241" s="64"/>
+      <c r="C241" s="64"/>
+      <c r="D241" s="64"/>
+      <c r="E241" s="66"/>
+      <c r="F241" s="64"/>
+      <c r="G241" s="64"/>
+      <c r="H241" s="65"/>
+    </row>
+    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="39">
         <f>MAX(A232:A241)+1</f>
         <v>193</v>
@@ -7339,7 +7339,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="243" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <f>MAX(A233:A242)+1</f>
         <v>194</v>
@@ -7360,7 +7360,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <f>MAX(A235:A243)+1</f>
         <v>195</v>
@@ -7386,17 +7386,19 @@
       </c>
       <c r="H244" s="10"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A245" s="76"/>
-      <c r="B245" s="77"/>
-      <c r="C245" s="77"/>
-      <c r="D245" s="77"/>
-      <c r="E245" s="77"/>
-      <c r="F245" s="77"/>
-      <c r="G245" s="77"/>
-      <c r="H245" s="78"/>
-    </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A245" s="63" t="s">
+        <v>25</v>
+      </c>
+      <c r="B245" s="64"/>
+      <c r="C245" s="64"/>
+      <c r="D245" s="64"/>
+      <c r="E245" s="64"/>
+      <c r="F245" s="64"/>
+      <c r="G245" s="64"/>
+      <c r="H245" s="65"/>
+    </row>
+    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="39">
         <f>MAX(A235:A245)+1</f>
         <v>196</v>
@@ -7424,7 +7426,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <f>MAX(A236:A246)+1</f>
         <v>197</v>
@@ -7449,7 +7451,7 @@
       </c>
       <c r="H247" s="43"/>
     </row>
-    <row r="248" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="51">
         <f>MAX(A236:A247)+1</f>
         <v>198</v>
@@ -7474,15 +7476,17 @@
         <v>76</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A249" s="59"/>
+    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A249" s="59" t="s">
+        <v>25</v>
+      </c>
       <c r="B249" s="60"/>
       <c r="C249" s="60"/>
       <c r="D249" s="60"/>
       <c r="E249" s="60"/>
       <c r="F249" s="60"/>
       <c r="G249" s="60"/>
-      <c r="H249" s="61"/>
+      <c r="H249" s="62"/>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
@@ -7615,7 +7619,7 @@
       <c r="E255" s="60"/>
       <c r="F255" s="60"/>
       <c r="G255" s="60"/>
-      <c r="H255" s="61"/>
+      <c r="H255" s="62"/>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
@@ -7647,7 +7651,7 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
-        <f>MAX(A245:A256)+1</f>
+        <f t="shared" ref="A257:A260" si="265">MAX(A245:A256)+1</f>
         <v>205</v>
       </c>
       <c r="B257" s="38" t="s">
@@ -7672,8 +7676,8 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
-        <f>MAX(A246:A256)+1</f>
-        <v>205</v>
+        <f t="shared" si="265"/>
+        <v>206</v>
       </c>
       <c r="B258" s="9" t="s">
         <v>19</v>
@@ -7693,8 +7697,8 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
-        <f>MAX(A247:A258)+1</f>
-        <v>206</v>
+        <f t="shared" si="265"/>
+        <v>207</v>
       </c>
       <c r="B259" s="9" t="s">
         <v>18</v>
@@ -7705,7 +7709,9 @@
       <c r="D259" s="36">
         <v>46045</v>
       </c>
-      <c r="E259" s="37"/>
+      <c r="E259" s="37">
+        <v>7829</v>
+      </c>
       <c r="F259" s="36">
         <v>46050</v>
       </c>
@@ -7716,8 +7722,8 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
-        <f>MAX(A248:A259)+1</f>
-        <v>207</v>
+        <f t="shared" si="265"/>
+        <v>208</v>
       </c>
       <c r="B260" s="9" t="s">
         <v>26</v>
@@ -7728,7 +7734,9 @@
       <c r="D260" s="36">
         <v>46045</v>
       </c>
-      <c r="E260" s="37"/>
+      <c r="E260" s="37">
+        <v>2697</v>
+      </c>
       <c r="F260" s="36">
         <v>46055</v>
       </c>
@@ -7737,49 +7745,97 @@
       </c>
       <c r="H260" s="10"/>
     </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A261" s="59"/>
+      <c r="B261" s="60"/>
+      <c r="C261" s="60"/>
+      <c r="D261" s="60"/>
+      <c r="E261" s="60"/>
+      <c r="F261" s="60"/>
+      <c r="G261" s="60"/>
+      <c r="H261" s="62"/>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A262" s="2">
+        <f>MAX(A250:A261)+1</f>
+        <v>209</v>
+      </c>
+      <c r="B262" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C262" s="36">
+        <v>46048</v>
+      </c>
+      <c r="D262" s="36">
+        <v>46049</v>
+      </c>
+      <c r="E262" s="37"/>
+      <c r="F262" s="36">
+        <v>46056</v>
+      </c>
+      <c r="G262" s="36">
+        <v>46056</v>
+      </c>
+      <c r="H262" s="10"/>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A263" s="2">
+        <f t="shared" ref="A263:A264" si="266">MAX(A251:A262)+1</f>
+        <v>210</v>
+      </c>
+      <c r="B263" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C263" s="36">
+        <v>46048</v>
+      </c>
+      <c r="D263" s="36">
+        <v>46049</v>
+      </c>
+      <c r="E263" s="37"/>
+      <c r="F263" s="36"/>
+      <c r="G263" s="36"/>
+      <c r="H263" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A264" s="2">
+        <f t="shared" si="266"/>
+        <v>211</v>
+      </c>
+      <c r="B264" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C264" s="36">
+        <v>46051</v>
+      </c>
+      <c r="D264" s="36">
+        <v>46052</v>
+      </c>
+      <c r="E264" s="37"/>
+      <c r="F264" s="36">
+        <v>46057</v>
+      </c>
+      <c r="G264" s="36">
+        <v>46058</v>
+      </c>
+      <c r="H264" s="10"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A8:H244" xr:uid="{9D5F3532-A341-428E-AFDB-DF9AAA83E1F5}">
+  <autoFilter ref="A8:H254" xr:uid="{9D5F3532-A341-428E-AFDB-DF9AAA83E1F5}">
     <filterColumn colId="0">
       <filters>
-        <filter val="193"/>
-        <filter val="194"/>
-        <filter val="195"/>
+        <filter val="199"/>
+        <filter val="200"/>
+        <filter val="201"/>
+        <filter val="202"/>
+        <filter val="203"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <mergeCells count="48">
-    <mergeCell ref="A231:H231"/>
-    <mergeCell ref="A227:H227"/>
-    <mergeCell ref="A207:H207"/>
-    <mergeCell ref="A145:H145"/>
-    <mergeCell ref="A97:H97"/>
-    <mergeCell ref="A121:H121"/>
-    <mergeCell ref="A102:H102"/>
-    <mergeCell ref="A255:H255"/>
-    <mergeCell ref="A249:H249"/>
-    <mergeCell ref="A152:H152"/>
-    <mergeCell ref="A202:H202"/>
-    <mergeCell ref="A245:H245"/>
-    <mergeCell ref="A241:H241"/>
-    <mergeCell ref="A196:H196"/>
-    <mergeCell ref="A192:H192"/>
-    <mergeCell ref="A221:H221"/>
-    <mergeCell ref="A211:H211"/>
-    <mergeCell ref="A217:H217"/>
-    <mergeCell ref="A237:H237"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A34:H34"/>
+  <mergeCells count="49">
+    <mergeCell ref="A261:H261"/>
     <mergeCell ref="A73:H73"/>
     <mergeCell ref="A156:H156"/>
     <mergeCell ref="A186:H186"/>
@@ -7796,6 +7852,38 @@
     <mergeCell ref="A162:H162"/>
     <mergeCell ref="A78:H78"/>
     <mergeCell ref="A116:H116"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A255:H255"/>
+    <mergeCell ref="A249:H249"/>
+    <mergeCell ref="A152:H152"/>
+    <mergeCell ref="A202:H202"/>
+    <mergeCell ref="A245:H245"/>
+    <mergeCell ref="A241:H241"/>
+    <mergeCell ref="A196:H196"/>
+    <mergeCell ref="A192:H192"/>
+    <mergeCell ref="A221:H221"/>
+    <mergeCell ref="A211:H211"/>
+    <mergeCell ref="A217:H217"/>
+    <mergeCell ref="A237:H237"/>
+    <mergeCell ref="A231:H231"/>
+    <mergeCell ref="A227:H227"/>
+    <mergeCell ref="A207:H207"/>
+    <mergeCell ref="A145:H145"/>
+    <mergeCell ref="A97:H97"/>
+    <mergeCell ref="A121:H121"/>
+    <mergeCell ref="A102:H102"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="90" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/графики/график Ташкент.xlsx
+++ b/графики/график Ташкент.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6114CB1E-7FD8-4A13-B1B8-763C47BBE828}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6021600A-9AE5-4574-AD37-E650C42C8183}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -823,23 +823,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -871,14 +868,17 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1178,19 +1178,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="70"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="70" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="44" t="s">
@@ -1211,12 +1211,12 @@
       <c r="G2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="74" t="s">
+      <c r="H2" s="73" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="72"/>
+      <c r="A3" s="71"/>
       <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
@@ -1233,10 +1233,10 @@
       <c r="G3" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="75"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
+      <c r="A4" s="71"/>
       <c r="B4" s="44" t="s">
         <v>6</v>
       </c>
@@ -1253,10 +1253,10 @@
       <c r="G4" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="75"/>
+      <c r="H4" s="74"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
+      <c r="A5" s="71"/>
       <c r="B5" s="44" t="s">
         <v>19</v>
       </c>
@@ -1267,14 +1267,14 @@
         <v>9</v>
       </c>
       <c r="E5" s="46"/>
-      <c r="F5" s="78" t="s">
+      <c r="F5" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="79"/>
-      <c r="H5" s="75"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="74"/>
     </row>
     <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
+      <c r="A6" s="71"/>
       <c r="B6" s="44" t="s">
         <v>15</v>
       </c>
@@ -1291,10 +1291,10 @@
       <c r="G6" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="75"/>
+      <c r="H6" s="74"/>
     </row>
     <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="73"/>
+      <c r="A7" s="72"/>
       <c r="B7" s="44" t="s">
         <v>26</v>
       </c>
@@ -1311,7 +1311,7 @@
       <c r="G7" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="76"/>
+      <c r="H7" s="75"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="47">
@@ -1461,7 +1461,7 @@
       <c r="E14" s="60"/>
       <c r="F14" s="60"/>
       <c r="G14" s="60"/>
-      <c r="H14" s="62"/>
+      <c r="H14" s="61"/>
     </row>
     <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -1611,10 +1611,10 @@
       <c r="B20" s="60"/>
       <c r="C20" s="60"/>
       <c r="D20" s="60"/>
-      <c r="E20" s="61"/>
+      <c r="E20" s="62"/>
       <c r="F20" s="60"/>
       <c r="G20" s="60"/>
-      <c r="H20" s="77"/>
+      <c r="H20" s="63"/>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -1763,10 +1763,10 @@
       <c r="B26" s="60"/>
       <c r="C26" s="60"/>
       <c r="D26" s="60"/>
-      <c r="E26" s="61"/>
+      <c r="E26" s="62"/>
       <c r="F26" s="60"/>
       <c r="G26" s="60"/>
-      <c r="H26" s="77"/>
+      <c r="H26" s="63"/>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -1973,10 +1973,10 @@
       <c r="B34" s="60"/>
       <c r="C34" s="60"/>
       <c r="D34" s="60"/>
-      <c r="E34" s="61"/>
+      <c r="E34" s="62"/>
       <c r="F34" s="60"/>
       <c r="G34" s="60"/>
-      <c r="H34" s="77"/>
+      <c r="H34" s="63"/>
     </row>
     <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -2167,10 +2167,10 @@
       <c r="B41" s="60"/>
       <c r="C41" s="60"/>
       <c r="D41" s="60"/>
-      <c r="E41" s="61"/>
+      <c r="E41" s="62"/>
       <c r="F41" s="60"/>
       <c r="G41" s="60"/>
-      <c r="H41" s="77"/>
+      <c r="H41" s="63"/>
     </row>
     <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
@@ -2378,10 +2378,10 @@
       <c r="B49" s="60"/>
       <c r="C49" s="60"/>
       <c r="D49" s="60"/>
-      <c r="E49" s="61"/>
+      <c r="E49" s="62"/>
       <c r="F49" s="60"/>
       <c r="G49" s="60"/>
-      <c r="H49" s="77"/>
+      <c r="H49" s="63"/>
     </row>
     <row r="50" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
@@ -2502,10 +2502,10 @@
       <c r="B54" s="60"/>
       <c r="C54" s="60"/>
       <c r="D54" s="60"/>
-      <c r="E54" s="61"/>
+      <c r="E54" s="62"/>
       <c r="F54" s="60"/>
       <c r="G54" s="60"/>
-      <c r="H54" s="77"/>
+      <c r="H54" s="63"/>
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
@@ -2663,7 +2663,7 @@
       <c r="E61" s="60"/>
       <c r="F61" s="60"/>
       <c r="G61" s="60"/>
-      <c r="H61" s="62"/>
+      <c r="H61" s="61"/>
     </row>
     <row r="62" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
@@ -2787,7 +2787,7 @@
       <c r="E66" s="60"/>
       <c r="F66" s="60"/>
       <c r="G66" s="60"/>
-      <c r="H66" s="62"/>
+      <c r="H66" s="61"/>
     </row>
     <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
@@ -2971,7 +2971,7 @@
       <c r="E73" s="60"/>
       <c r="F73" s="60"/>
       <c r="G73" s="60"/>
-      <c r="H73" s="62"/>
+      <c r="H73" s="61"/>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
@@ -3099,7 +3099,7 @@
       <c r="E78" s="60"/>
       <c r="F78" s="60"/>
       <c r="G78" s="60"/>
-      <c r="H78" s="62"/>
+      <c r="H78" s="61"/>
     </row>
     <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
@@ -3283,7 +3283,7 @@
       <c r="E85" s="60"/>
       <c r="F85" s="60"/>
       <c r="G85" s="60"/>
-      <c r="H85" s="62"/>
+      <c r="H85" s="61"/>
     </row>
     <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
@@ -3410,7 +3410,7 @@
       <c r="E90" s="60"/>
       <c r="F90" s="60"/>
       <c r="G90" s="60"/>
-      <c r="H90" s="62"/>
+      <c r="H90" s="61"/>
     </row>
     <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
@@ -3593,7 +3593,7 @@
       <c r="E97" s="60"/>
       <c r="F97" s="60"/>
       <c r="G97" s="60"/>
-      <c r="H97" s="62"/>
+      <c r="H97" s="61"/>
     </row>
     <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
@@ -3718,7 +3718,7 @@
       <c r="E102" s="60"/>
       <c r="F102" s="60"/>
       <c r="G102" s="60"/>
-      <c r="H102" s="62"/>
+      <c r="H102" s="61"/>
     </row>
     <row r="103" spans="1:8" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
@@ -3905,7 +3905,7 @@
       <c r="E109" s="60"/>
       <c r="F109" s="60"/>
       <c r="G109" s="60"/>
-      <c r="H109" s="62"/>
+      <c r="H109" s="61"/>
     </row>
     <row r="110" spans="1:8" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
@@ -4088,7 +4088,7 @@
       <c r="E116" s="60"/>
       <c r="F116" s="60"/>
       <c r="G116" s="60"/>
-      <c r="H116" s="62"/>
+      <c r="H116" s="61"/>
     </row>
     <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
@@ -4196,7 +4196,7 @@
       <c r="E121" s="60"/>
       <c r="F121" s="60"/>
       <c r="G121" s="60"/>
-      <c r="H121" s="62"/>
+      <c r="H121" s="61"/>
     </row>
     <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
@@ -4379,7 +4379,7 @@
       <c r="E128" s="60"/>
       <c r="F128" s="60"/>
       <c r="G128" s="60"/>
-      <c r="H128" s="62"/>
+      <c r="H128" s="61"/>
     </row>
     <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
@@ -4507,7 +4507,7 @@
       <c r="E133" s="60"/>
       <c r="F133" s="60"/>
       <c r="G133" s="60"/>
-      <c r="H133" s="62"/>
+      <c r="H133" s="61"/>
     </row>
     <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
@@ -4695,7 +4695,7 @@
       <c r="E140" s="60"/>
       <c r="F140" s="60"/>
       <c r="G140" s="60"/>
-      <c r="H140" s="62"/>
+      <c r="H140" s="61"/>
     </row>
     <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
@@ -4820,10 +4820,10 @@
       <c r="B145" s="60"/>
       <c r="C145" s="60"/>
       <c r="D145" s="60"/>
-      <c r="E145" s="61"/>
+      <c r="E145" s="62"/>
       <c r="F145" s="60"/>
       <c r="G145" s="60"/>
-      <c r="H145" s="62"/>
+      <c r="H145" s="61"/>
     </row>
     <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
@@ -5008,10 +5008,10 @@
       <c r="B152" s="60"/>
       <c r="C152" s="60"/>
       <c r="D152" s="60"/>
-      <c r="E152" s="61"/>
+      <c r="E152" s="62"/>
       <c r="F152" s="60"/>
       <c r="G152" s="60"/>
-      <c r="H152" s="62"/>
+      <c r="H152" s="61"/>
     </row>
     <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
@@ -5107,10 +5107,10 @@
       <c r="B156" s="60"/>
       <c r="C156" s="60"/>
       <c r="D156" s="60"/>
-      <c r="E156" s="61"/>
+      <c r="E156" s="62"/>
       <c r="F156" s="60"/>
       <c r="G156" s="60"/>
-      <c r="H156" s="62"/>
+      <c r="H156" s="61"/>
     </row>
     <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
@@ -5269,10 +5269,10 @@
       <c r="B162" s="60"/>
       <c r="C162" s="60"/>
       <c r="D162" s="60"/>
-      <c r="E162" s="61"/>
+      <c r="E162" s="62"/>
       <c r="F162" s="60"/>
       <c r="G162" s="60"/>
-      <c r="H162" s="62"/>
+      <c r="H162" s="61"/>
     </row>
     <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
@@ -5373,10 +5373,10 @@
       <c r="B166" s="60"/>
       <c r="C166" s="60"/>
       <c r="D166" s="60"/>
-      <c r="E166" s="61"/>
+      <c r="E166" s="62"/>
       <c r="F166" s="60"/>
       <c r="G166" s="60"/>
-      <c r="H166" s="62"/>
+      <c r="H166" s="61"/>
     </row>
     <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
@@ -5535,10 +5535,10 @@
       <c r="B172" s="60"/>
       <c r="C172" s="60"/>
       <c r="D172" s="60"/>
-      <c r="E172" s="61"/>
+      <c r="E172" s="62"/>
       <c r="F172" s="60"/>
       <c r="G172" s="60"/>
-      <c r="H172" s="62"/>
+      <c r="H172" s="61"/>
     </row>
     <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
@@ -5639,10 +5639,10 @@
       <c r="B176" s="60"/>
       <c r="C176" s="60"/>
       <c r="D176" s="60"/>
-      <c r="E176" s="61"/>
+      <c r="E176" s="62"/>
       <c r="F176" s="60"/>
       <c r="G176" s="60"/>
-      <c r="H176" s="62"/>
+      <c r="H176" s="61"/>
     </row>
     <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
@@ -5802,10 +5802,10 @@
       <c r="B182" s="60"/>
       <c r="C182" s="60"/>
       <c r="D182" s="60"/>
-      <c r="E182" s="61"/>
+      <c r="E182" s="62"/>
       <c r="F182" s="60"/>
       <c r="G182" s="60"/>
-      <c r="H182" s="62"/>
+      <c r="H182" s="61"/>
     </row>
     <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
@@ -5903,10 +5903,10 @@
       <c r="B186" s="60"/>
       <c r="C186" s="60"/>
       <c r="D186" s="60"/>
-      <c r="E186" s="61"/>
+      <c r="E186" s="62"/>
       <c r="F186" s="60"/>
       <c r="G186" s="60"/>
-      <c r="H186" s="62"/>
+      <c r="H186" s="61"/>
     </row>
     <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
@@ -6064,10 +6064,10 @@
       <c r="B192" s="60"/>
       <c r="C192" s="60"/>
       <c r="D192" s="60"/>
-      <c r="E192" s="61"/>
+      <c r="E192" s="62"/>
       <c r="F192" s="60"/>
       <c r="G192" s="60"/>
-      <c r="H192" s="62"/>
+      <c r="H192" s="61"/>
     </row>
     <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
@@ -6168,10 +6168,10 @@
       <c r="B196" s="60"/>
       <c r="C196" s="60"/>
       <c r="D196" s="60"/>
-      <c r="E196" s="61"/>
+      <c r="E196" s="62"/>
       <c r="F196" s="60"/>
       <c r="G196" s="60"/>
-      <c r="H196" s="62"/>
+      <c r="H196" s="61"/>
     </row>
     <row r="197" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
@@ -6328,10 +6328,10 @@
       <c r="B202" s="60"/>
       <c r="C202" s="60"/>
       <c r="D202" s="60"/>
-      <c r="E202" s="61"/>
+      <c r="E202" s="62"/>
       <c r="F202" s="60"/>
       <c r="G202" s="60"/>
-      <c r="H202" s="62"/>
+      <c r="H202" s="61"/>
     </row>
     <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
@@ -6456,10 +6456,10 @@
       <c r="B207" s="60"/>
       <c r="C207" s="60"/>
       <c r="D207" s="60"/>
-      <c r="E207" s="61"/>
+      <c r="E207" s="62"/>
       <c r="F207" s="60"/>
       <c r="G207" s="60"/>
-      <c r="H207" s="62"/>
+      <c r="H207" s="61"/>
     </row>
     <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
@@ -6559,10 +6559,10 @@
       <c r="B211" s="60"/>
       <c r="C211" s="60"/>
       <c r="D211" s="60"/>
-      <c r="E211" s="61"/>
+      <c r="E211" s="62"/>
       <c r="F211" s="60"/>
       <c r="G211" s="60"/>
-      <c r="H211" s="62"/>
+      <c r="H211" s="61"/>
     </row>
     <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
@@ -6696,10 +6696,10 @@
       <c r="B217" s="60"/>
       <c r="C217" s="60"/>
       <c r="D217" s="60"/>
-      <c r="E217" s="61"/>
+      <c r="E217" s="62"/>
       <c r="F217" s="60"/>
       <c r="G217" s="60"/>
-      <c r="H217" s="62"/>
+      <c r="H217" s="61"/>
     </row>
     <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
@@ -6797,10 +6797,10 @@
       <c r="B221" s="60"/>
       <c r="C221" s="60"/>
       <c r="D221" s="60"/>
-      <c r="E221" s="61"/>
+      <c r="E221" s="62"/>
       <c r="F221" s="60"/>
       <c r="G221" s="60"/>
-      <c r="H221" s="62"/>
+      <c r="H221" s="61"/>
     </row>
     <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
@@ -6950,10 +6950,10 @@
       <c r="B227" s="60"/>
       <c r="C227" s="60"/>
       <c r="D227" s="60"/>
-      <c r="E227" s="61"/>
+      <c r="E227" s="62"/>
       <c r="F227" s="60"/>
       <c r="G227" s="60"/>
-      <c r="H227" s="62"/>
+      <c r="H227" s="61"/>
     </row>
     <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
@@ -7053,10 +7053,10 @@
       <c r="B231" s="60"/>
       <c r="C231" s="60"/>
       <c r="D231" s="60"/>
-      <c r="E231" s="61"/>
+      <c r="E231" s="62"/>
       <c r="F231" s="60"/>
       <c r="G231" s="60"/>
-      <c r="H231" s="62"/>
+      <c r="H231" s="61"/>
     </row>
     <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
@@ -7201,16 +7201,16 @@
       </c>
     </row>
     <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="63" t="s">
+      <c r="A237" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B237" s="64"/>
-      <c r="C237" s="64"/>
-      <c r="D237" s="64"/>
-      <c r="E237" s="64"/>
-      <c r="F237" s="64"/>
-      <c r="G237" s="64"/>
-      <c r="H237" s="65"/>
+      <c r="B237" s="77"/>
+      <c r="C237" s="77"/>
+      <c r="D237" s="77"/>
+      <c r="E237" s="77"/>
+      <c r="F237" s="77"/>
+      <c r="G237" s="77"/>
+      <c r="H237" s="78"/>
     </row>
     <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="39">
@@ -7301,16 +7301,16 @@
       </c>
     </row>
     <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="63" t="s">
+      <c r="A241" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B241" s="64"/>
-      <c r="C241" s="64"/>
-      <c r="D241" s="64"/>
-      <c r="E241" s="66"/>
-      <c r="F241" s="64"/>
-      <c r="G241" s="64"/>
-      <c r="H241" s="65"/>
+      <c r="B241" s="77"/>
+      <c r="C241" s="77"/>
+      <c r="D241" s="77"/>
+      <c r="E241" s="79"/>
+      <c r="F241" s="77"/>
+      <c r="G241" s="77"/>
+      <c r="H241" s="78"/>
     </row>
     <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="39">
@@ -7387,16 +7387,16 @@
       <c r="H244" s="10"/>
     </row>
     <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A245" s="63" t="s">
+      <c r="A245" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B245" s="64"/>
-      <c r="C245" s="64"/>
-      <c r="D245" s="64"/>
-      <c r="E245" s="64"/>
-      <c r="F245" s="64"/>
-      <c r="G245" s="64"/>
-      <c r="H245" s="65"/>
+      <c r="B245" s="77"/>
+      <c r="C245" s="77"/>
+      <c r="D245" s="77"/>
+      <c r="E245" s="77"/>
+      <c r="F245" s="77"/>
+      <c r="G245" s="77"/>
+      <c r="H245" s="78"/>
     </row>
     <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="39">
@@ -7486,7 +7486,7 @@
       <c r="E249" s="60"/>
       <c r="F249" s="60"/>
       <c r="G249" s="60"/>
-      <c r="H249" s="62"/>
+      <c r="H249" s="61"/>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
@@ -7619,7 +7619,7 @@
       <c r="E255" s="60"/>
       <c r="F255" s="60"/>
       <c r="G255" s="60"/>
-      <c r="H255" s="62"/>
+      <c r="H255" s="61"/>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
@@ -7753,7 +7753,7 @@
       <c r="E261" s="60"/>
       <c r="F261" s="60"/>
       <c r="G261" s="60"/>
-      <c r="H261" s="62"/>
+      <c r="H261" s="61"/>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
@@ -7769,7 +7769,9 @@
       <c r="D262" s="36">
         <v>46049</v>
       </c>
-      <c r="E262" s="37"/>
+      <c r="E262" s="37">
+        <v>2768</v>
+      </c>
       <c r="F262" s="36">
         <v>46056</v>
       </c>
@@ -7835,6 +7837,39 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="49">
+    <mergeCell ref="A145:H145"/>
+    <mergeCell ref="A97:H97"/>
+    <mergeCell ref="A121:H121"/>
+    <mergeCell ref="A102:H102"/>
+    <mergeCell ref="A255:H255"/>
+    <mergeCell ref="A249:H249"/>
+    <mergeCell ref="A152:H152"/>
+    <mergeCell ref="A202:H202"/>
+    <mergeCell ref="A245:H245"/>
+    <mergeCell ref="A241:H241"/>
+    <mergeCell ref="A196:H196"/>
+    <mergeCell ref="A192:H192"/>
+    <mergeCell ref="A221:H221"/>
+    <mergeCell ref="A211:H211"/>
+    <mergeCell ref="A217:H217"/>
+    <mergeCell ref="A237:H237"/>
+    <mergeCell ref="A231:H231"/>
+    <mergeCell ref="A227:H227"/>
+    <mergeCell ref="A207:H207"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A116:H116"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A34:H34"/>
     <mergeCell ref="A261:H261"/>
     <mergeCell ref="A73:H73"/>
     <mergeCell ref="A156:H156"/>
@@ -7851,39 +7886,6 @@
     <mergeCell ref="A109:H109"/>
     <mergeCell ref="A162:H162"/>
     <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A116:H116"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A255:H255"/>
-    <mergeCell ref="A249:H249"/>
-    <mergeCell ref="A152:H152"/>
-    <mergeCell ref="A202:H202"/>
-    <mergeCell ref="A245:H245"/>
-    <mergeCell ref="A241:H241"/>
-    <mergeCell ref="A196:H196"/>
-    <mergeCell ref="A192:H192"/>
-    <mergeCell ref="A221:H221"/>
-    <mergeCell ref="A211:H211"/>
-    <mergeCell ref="A217:H217"/>
-    <mergeCell ref="A237:H237"/>
-    <mergeCell ref="A231:H231"/>
-    <mergeCell ref="A227:H227"/>
-    <mergeCell ref="A207:H207"/>
-    <mergeCell ref="A145:H145"/>
-    <mergeCell ref="A97:H97"/>
-    <mergeCell ref="A121:H121"/>
-    <mergeCell ref="A102:H102"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="90" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/графики/график Ташкент.xlsx
+++ b/графики/график Ташкент.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6021600A-9AE5-4574-AD37-E650C42C8183}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B639CE42-D006-4E3F-833A-9CCC6DF178CC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -832,12 +832,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -866,6 +860,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1178,19 +1178,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="69"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="67"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="68" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="44" t="s">
@@ -1211,12 +1211,12 @@
       <c r="G2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="73" t="s">
+      <c r="H2" s="71" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="71"/>
+      <c r="A3" s="69"/>
       <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
@@ -1233,10 +1233,10 @@
       <c r="G3" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="74"/>
+      <c r="H3" s="72"/>
     </row>
     <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="71"/>
+      <c r="A4" s="69"/>
       <c r="B4" s="44" t="s">
         <v>6</v>
       </c>
@@ -1253,10 +1253,10 @@
       <c r="G4" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="74"/>
+      <c r="H4" s="72"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="71"/>
+      <c r="A5" s="69"/>
       <c r="B5" s="44" t="s">
         <v>19</v>
       </c>
@@ -1267,14 +1267,14 @@
         <v>9</v>
       </c>
       <c r="E5" s="46"/>
-      <c r="F5" s="64" t="s">
+      <c r="F5" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="65"/>
-      <c r="H5" s="74"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="72"/>
     </row>
     <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="71"/>
+      <c r="A6" s="69"/>
       <c r="B6" s="44" t="s">
         <v>15</v>
       </c>
@@ -1291,10 +1291,10 @@
       <c r="G6" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="74"/>
+      <c r="H6" s="72"/>
     </row>
     <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
+      <c r="A7" s="70"/>
       <c r="B7" s="44" t="s">
         <v>26</v>
       </c>
@@ -1311,7 +1311,7 @@
       <c r="G7" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="75"/>
+      <c r="H7" s="73"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="47">
@@ -7837,10 +7837,6 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="49">
-    <mergeCell ref="A145:H145"/>
-    <mergeCell ref="A97:H97"/>
-    <mergeCell ref="A121:H121"/>
-    <mergeCell ref="A102:H102"/>
     <mergeCell ref="A255:H255"/>
     <mergeCell ref="A249:H249"/>
     <mergeCell ref="A152:H152"/>
@@ -7853,6 +7849,12 @@
     <mergeCell ref="A211:H211"/>
     <mergeCell ref="A217:H217"/>
     <mergeCell ref="A237:H237"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A145:H145"/>
+    <mergeCell ref="A97:H97"/>
+    <mergeCell ref="A121:H121"/>
+    <mergeCell ref="A102:H102"/>
+    <mergeCell ref="A162:H162"/>
     <mergeCell ref="A231:H231"/>
     <mergeCell ref="A227:H227"/>
     <mergeCell ref="A207:H207"/>
@@ -7868,7 +7870,7 @@
     <mergeCell ref="A66:H66"/>
     <mergeCell ref="A61:H61"/>
     <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A78:H78"/>
     <mergeCell ref="A34:H34"/>
     <mergeCell ref="A261:H261"/>
     <mergeCell ref="A73:H73"/>
@@ -7884,8 +7886,6 @@
     <mergeCell ref="A133:H133"/>
     <mergeCell ref="A140:H140"/>
     <mergeCell ref="A109:H109"/>
-    <mergeCell ref="A162:H162"/>
-    <mergeCell ref="A78:H78"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="90" fitToHeight="0" orientation="landscape" r:id="rId1"/>
